--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,6 +178,9 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -328,6 +331,9 @@
     <t>2021-04-26</t>
   </si>
   <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -665,6 +671,9 @@
   </si>
   <si>
     <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P283"/>
+  <dimension ref="A1:P284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1083,7 +1092,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1119,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1133,7 +1142,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1169,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1183,7 +1192,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1219,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1233,7 +1242,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1269,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1283,7 +1292,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1319,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1333,7 +1342,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1369,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1383,7 +1392,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1419,7 +1428,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1433,7 +1442,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1469,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1483,7 +1492,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1519,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1533,7 +1542,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1569,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1583,7 +1592,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1619,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1633,7 +1642,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1669,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1683,7 +1692,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1719,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1733,7 +1742,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1769,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1783,7 +1792,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1819,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1833,7 +1842,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1869,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1883,7 +1892,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1919,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1933,7 +1942,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1969,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1983,7 +1992,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2019,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2033,7 +2042,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2069,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2083,7 +2092,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2119,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2133,7 +2142,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2169,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2183,7 +2192,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2219,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2233,7 +2242,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2269,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2283,7 +2292,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2319,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2333,7 +2342,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2369,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2383,7 +2392,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2419,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2433,7 +2442,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2469,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2483,7 +2492,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2519,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2533,7 +2542,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2569,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2619,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2633,7 +2642,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2669,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2719,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2769,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2783,7 +2792,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2819,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2833,7 +2842,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2869,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2883,7 +2892,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2919,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2933,7 +2942,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2969,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2983,7 +2992,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3019,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3033,7 +3042,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3069,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3083,7 +3092,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3119,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3133,7 +3142,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3169,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3183,7 +3192,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3219,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3233,7 +3242,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3269,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3283,7 +3292,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3319,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3333,7 +3342,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3369,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3383,7 +3392,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3419,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3433,7 +3442,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3469,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3483,7 +3492,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3519,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3533,7 +3542,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3569,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3583,7 +3592,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3619,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3669,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3719,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3733,7 +3742,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3769,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3819,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3869,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3883,7 +3892,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3919,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3969,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4019,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4033,7 +4042,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4069,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4119,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4133,7 +4142,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4169,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4219,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4233,7 +4242,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4269,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4319,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4333,7 +4342,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4369,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4419,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4433,7 +4442,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4469,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4519,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4533,7 +4542,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4569,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4583,7 +4592,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4619,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4669,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4683,7 +4692,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4719,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4733,7 +4742,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4769,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4819,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4833,7 +4842,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4869,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4883,7 +4892,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4919,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4969,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4983,7 +4992,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5019,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5033,7 +5042,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5069,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5119,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5133,7 +5142,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5169,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5183,7 +5192,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5219,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5269,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5283,7 +5292,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5319,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5333,7 +5342,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5369,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5419,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5433,7 +5442,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5469,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5483,7 +5492,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5519,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5569,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5583,7 +5592,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5619,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5633,7 +5642,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5669,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5719,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5733,7 +5742,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5769,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5783,7 +5792,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5819,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5833,7 +5842,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5869,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5883,7 +5892,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5919,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5933,7 +5942,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5969,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5983,7 +5992,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6019,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6033,7 +6042,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6069,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6083,7 +6092,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6119,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6133,7 +6142,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6169,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6183,7 +6192,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6219,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6233,7 +6242,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6269,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6283,7 +6292,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6319,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6333,7 +6342,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6369,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6383,7 +6392,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6419,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6433,7 +6442,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6469,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6483,7 +6492,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6519,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6533,7 +6542,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6569,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6583,7 +6592,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6619,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6633,7 +6642,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6669,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6683,7 +6692,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6719,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6733,7 +6742,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6769,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6783,7 +6792,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6819,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6833,7 +6842,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6869,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6883,7 +6892,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6919,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6933,7 +6942,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6969,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6983,7 +6992,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7019,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7033,7 +7042,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7069,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7083,7 +7092,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7119,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7133,7 +7142,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7169,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7183,7 +7192,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7219,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7233,7 +7242,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7269,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7283,7 +7292,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7319,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7333,7 +7342,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7369,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7383,7 +7392,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7419,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7433,7 +7442,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7469,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7483,7 +7492,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7519,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7533,7 +7542,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7569,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7583,7 +7592,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7619,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7633,7 +7642,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7669,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7683,7 +7692,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7719,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7733,7 +7742,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7769,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7783,7 +7792,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7819,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7833,7 +7842,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7869,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7883,7 +7892,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7919,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7933,7 +7942,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7969,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7983,7 +7992,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8019,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8033,7 +8042,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8069,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8083,7 +8092,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8119,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8133,7 +8142,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8169,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8183,7 +8192,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8219,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8233,7 +8242,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8269,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8283,7 +8292,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8319,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8333,7 +8342,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8369,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8383,7 +8392,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8419,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8433,7 +8442,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8469,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8483,7 +8492,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8519,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8533,7 +8542,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8569,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8583,7 +8592,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8619,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8633,7 +8642,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8669,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8683,7 +8692,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8719,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8733,7 +8742,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8769,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8783,7 +8792,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8819,7 +8828,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8833,7 +8842,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8869,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8883,7 +8892,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8933,7 +8942,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8969,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8983,7 +8992,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9019,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9033,7 +9042,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9069,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9083,7 +9092,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9119,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9133,7 +9142,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9169,7 +9178,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9183,7 +9192,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9219,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9233,7 +9242,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9269,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9283,7 +9292,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9319,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9333,7 +9342,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9369,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9383,7 +9392,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9419,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9433,7 +9442,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9469,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9483,7 +9492,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9519,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9533,7 +9542,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9569,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9583,7 +9592,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9619,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9633,7 +9642,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9669,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9683,7 +9692,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9719,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9733,7 +9742,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9769,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9783,7 +9792,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9819,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9833,7 +9842,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9869,7 +9878,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9883,7 +9892,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9919,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9933,7 +9942,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9969,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -9983,7 +9992,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10019,7 +10028,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10033,7 +10042,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10069,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10083,7 +10092,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10119,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10133,7 +10142,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10169,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10183,7 +10192,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10219,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10233,7 +10242,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10269,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10283,7 +10292,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10319,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10333,7 +10342,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10369,7 +10378,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10383,7 +10392,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10419,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10433,7 +10442,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10469,7 +10478,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10483,7 +10492,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10519,7 +10528,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10533,7 +10542,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10569,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10583,7 +10592,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10619,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10633,7 +10642,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10669,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10683,7 +10692,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10719,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10733,7 +10742,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10769,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10819,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10869,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10883,7 +10892,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10919,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10969,7 +10978,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11019,7 +11028,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11033,7 +11042,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11069,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11119,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11169,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11183,7 +11192,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11219,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11269,7 +11278,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11283,7 +11292,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11319,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11333,7 +11342,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11369,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11419,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11433,7 +11442,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11469,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11483,7 +11492,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11519,7 +11528,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11569,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11583,7 +11592,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11619,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11633,7 +11642,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11669,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11719,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11733,7 +11742,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11769,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11783,7 +11792,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11819,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11869,7 +11878,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11883,7 +11892,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11919,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11933,7 +11942,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11969,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12019,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12033,7 +12042,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12069,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12083,7 +12092,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12119,7 +12128,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12169,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12183,7 +12192,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12219,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12233,7 +12242,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12269,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12319,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12333,7 +12342,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12369,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12419,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12433,7 +12442,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12469,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12519,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12533,7 +12542,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12569,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12619,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12633,7 +12642,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12669,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12719,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12733,7 +12742,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12769,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12819,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12869,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12883,7 +12892,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12919,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12933,7 +12942,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12969,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -12983,7 +12992,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13019,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13033,7 +13042,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13069,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13083,7 +13092,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13119,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13133,7 +13142,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13169,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13183,7 +13192,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13219,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13233,7 +13242,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13269,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13283,7 +13292,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13319,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13333,7 +13342,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13369,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13383,7 +13392,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13419,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13433,7 +13442,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13469,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13483,7 +13492,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13519,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13533,7 +13542,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13569,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13583,7 +13592,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13619,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13633,7 +13642,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13669,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13683,7 +13692,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13719,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13733,7 +13742,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13769,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13783,7 +13792,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13833,7 +13842,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13883,7 +13892,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13933,7 +13942,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13969,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -13983,7 +13992,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14019,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14033,7 +14042,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14069,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14083,7 +14092,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14119,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14133,7 +14142,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14169,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14183,7 +14192,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14219,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14233,7 +14242,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14269,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14283,7 +14292,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14319,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14333,7 +14342,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14369,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14383,7 +14392,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14419,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14433,7 +14442,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14469,7 +14478,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14483,7 +14492,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14519,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14569,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14619,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14669,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14719,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14769,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14783,7 +14792,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14819,7 +14828,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14833,7 +14842,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14869,7 +14878,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14883,7 +14892,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14919,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14933,7 +14942,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14969,7 +14978,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -14983,7 +14992,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15019,7 +15028,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15033,7 +15042,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15069,7 +15078,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15083,7 +15092,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15119,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15133,7 +15142,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15169,7 +15178,57 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>216</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16">
+      <c r="A284" s="1">
+        <v>0</v>
+      </c>
+      <c r="B284" t="s">
+        <v>54</v>
+      </c>
+      <c r="C284">
+        <v>18.31833037024829</v>
+      </c>
+      <c r="D284" t="s">
+        <v>105</v>
+      </c>
+      <c r="E284">
+        <v>18.80561155371556</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>0.02686166962975171</v>
+      </c>
+      <c r="H284">
+        <v>0.02771438844628444</v>
+      </c>
+      <c r="I284">
+        <v>0.487281183467271</v>
+      </c>
+      <c r="J284">
+        <v>0.246917319638827</v>
+      </c>
+      <c r="K284">
+        <v>17.3</v>
+      </c>
+      <c r="L284">
+        <v>22.59</v>
+      </c>
+      <c r="M284">
+        <v>18.04</v>
+      </c>
+      <c r="N284">
+        <v>23.26</v>
+      </c>
+      <c r="O284">
+        <v>1</v>
+      </c>
+      <c r="P284" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -331,7 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15195,7 +15195,7 @@
         <v>105</v>
       </c>
       <c r="E284">
-        <v>18.80561155371556</v>
+        <v>18.44524163207222</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -15204,10 +15204,10 @@
         <v>0.02686166962975171</v>
       </c>
       <c r="H284">
-        <v>0.02771438844628444</v>
+        <v>0.02729475836792778</v>
       </c>
       <c r="I284">
-        <v>0.487281183467271</v>
+        <v>0.1269112618239312</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15219,10 +15219,10 @@
         <v>22.59</v>
       </c>
       <c r="M284">
-        <v>18.04</v>
+        <v>17.92</v>
       </c>
       <c r="N284">
-        <v>23.26</v>
+        <v>22.87</v>
       </c>
       <c r="O284">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="223">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,9 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -331,7 +334,10 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-08-05</t>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -674,6 +680,9 @@
   </si>
   <si>
     <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P284"/>
+  <dimension ref="A1:P285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1092,7 +1101,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1128,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1142,7 +1151,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1178,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1192,7 +1201,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1228,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1242,7 +1251,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1278,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1292,7 +1301,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1328,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1342,7 +1351,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1378,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1392,7 +1401,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1428,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1442,7 +1451,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1478,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1492,7 +1501,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1528,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1542,7 +1551,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1578,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1592,7 +1601,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1628,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1642,7 +1651,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1678,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1692,7 +1701,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1728,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1742,7 +1751,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1778,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1792,7 +1801,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1828,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1842,7 +1851,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1878,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1892,7 +1901,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1928,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1942,7 +1951,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1978,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1992,7 +2001,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2028,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2042,7 +2051,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2078,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2092,7 +2101,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2128,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2142,7 +2151,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2178,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2192,7 +2201,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2228,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2242,7 +2251,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2278,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2292,7 +2301,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2328,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2342,7 +2351,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2378,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2392,7 +2401,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2428,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2442,7 +2451,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2478,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2492,7 +2501,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2528,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2542,7 +2551,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2578,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2628,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2642,7 +2651,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2678,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2728,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2778,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2792,7 +2801,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2828,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2842,7 +2851,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2878,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2892,7 +2901,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2928,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2942,7 +2951,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2978,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2992,7 +3001,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3028,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3042,7 +3051,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3078,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3092,7 +3101,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3128,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3142,7 +3151,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3178,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3192,7 +3201,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3228,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3242,7 +3251,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3278,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3292,7 +3301,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3328,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3342,7 +3351,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3378,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3392,7 +3401,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3428,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3442,7 +3451,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3478,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3492,7 +3501,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3528,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3542,7 +3551,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3578,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3592,7 +3601,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3628,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3678,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3728,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3742,7 +3751,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3778,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3828,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3878,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3892,7 +3901,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3928,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3978,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4028,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4042,7 +4051,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4078,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4128,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4142,7 +4151,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4178,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4228,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4242,7 +4251,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4278,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4328,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4342,7 +4351,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4378,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4428,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4442,7 +4451,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4478,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4528,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4542,7 +4551,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4578,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4592,7 +4601,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4628,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4678,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4692,7 +4701,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4728,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4742,7 +4751,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4778,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4828,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4842,7 +4851,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4878,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4892,7 +4901,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4928,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4978,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4992,7 +5001,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5028,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5042,7 +5051,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5078,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5128,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5142,7 +5151,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5178,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5192,7 +5201,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5228,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5278,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5292,7 +5301,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5328,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5342,7 +5351,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5378,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5428,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5442,7 +5451,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5478,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5492,7 +5501,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5528,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5578,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5592,7 +5601,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5628,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5642,7 +5651,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5678,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5728,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5742,7 +5751,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5778,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5792,7 +5801,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5828,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5842,7 +5851,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5878,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5892,7 +5901,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5928,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5942,7 +5951,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5978,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5992,7 +6001,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6028,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6042,7 +6051,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6078,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6092,7 +6101,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6128,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6142,7 +6151,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6178,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6192,7 +6201,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6228,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6242,7 +6251,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6278,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6292,7 +6301,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6328,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6342,7 +6351,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6378,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6392,7 +6401,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6428,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6442,7 +6451,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6478,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6492,7 +6501,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6528,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6542,7 +6551,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6578,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6592,7 +6601,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6628,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6642,7 +6651,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6678,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6692,7 +6701,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6728,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6742,7 +6751,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6778,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6792,7 +6801,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6828,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6842,7 +6851,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6878,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6892,7 +6901,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6928,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6942,7 +6951,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6978,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6992,7 +7001,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7028,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7042,7 +7051,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7078,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7092,7 +7101,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7128,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7142,7 +7151,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7178,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7192,7 +7201,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7228,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7242,7 +7251,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7278,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7292,7 +7301,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7328,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7342,7 +7351,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7378,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7392,7 +7401,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7428,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7442,7 +7451,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7478,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7492,7 +7501,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7528,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7542,7 +7551,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7578,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7592,7 +7601,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7628,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7642,7 +7651,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7678,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7692,7 +7701,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7728,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7742,7 +7751,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7778,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7792,7 +7801,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7828,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7842,7 +7851,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7878,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7892,7 +7901,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7928,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7942,7 +7951,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7978,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7992,7 +8001,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8028,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8042,7 +8051,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8078,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8092,7 +8101,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8128,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8142,7 +8151,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8178,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8192,7 +8201,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8228,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8242,7 +8251,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8278,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8292,7 +8301,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8328,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8342,7 +8351,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8378,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8392,7 +8401,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8428,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8442,7 +8451,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8478,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8492,7 +8501,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8528,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8542,7 +8551,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8578,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8592,7 +8601,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8628,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8642,7 +8651,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8678,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8692,7 +8701,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8728,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8742,7 +8751,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8778,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8792,7 +8801,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8828,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8842,7 +8851,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8878,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8892,7 +8901,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8942,7 +8951,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8978,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8992,7 +9001,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9028,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9042,7 +9051,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9078,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9092,7 +9101,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9128,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9142,7 +9151,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9178,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9192,7 +9201,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9228,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9242,7 +9251,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9278,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9292,7 +9301,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9328,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9342,7 +9351,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9378,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9392,7 +9401,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9428,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9442,7 +9451,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9478,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9492,7 +9501,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9528,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9542,7 +9551,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9578,7 +9587,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9592,7 +9601,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9628,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9642,7 +9651,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9678,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9692,7 +9701,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9728,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9742,7 +9751,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9778,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9792,7 +9801,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9828,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9842,7 +9851,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9878,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9892,7 +9901,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9928,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9942,7 +9951,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9978,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -9992,7 +10001,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10028,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10042,7 +10051,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10078,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10092,7 +10101,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10128,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10142,7 +10151,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10178,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10192,7 +10201,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10228,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10242,7 +10251,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10278,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10292,7 +10301,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10328,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10342,7 +10351,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10378,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10392,7 +10401,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10428,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10442,7 +10451,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10478,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10492,7 +10501,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10528,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10542,7 +10551,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10578,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10592,7 +10601,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10628,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10642,7 +10651,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10678,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10692,7 +10701,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10728,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10742,7 +10751,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10778,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10828,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10878,7 +10887,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10892,7 +10901,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10928,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10978,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11028,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11042,7 +11051,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11078,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11128,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11178,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11192,7 +11201,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11228,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11278,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11292,7 +11301,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11328,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11342,7 +11351,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11378,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11428,7 +11437,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11442,7 +11451,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11478,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11492,7 +11501,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11528,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11578,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11592,7 +11601,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11628,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11642,7 +11651,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11678,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11728,7 +11737,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11742,7 +11751,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11778,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11792,7 +11801,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11828,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11878,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11892,7 +11901,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11928,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11942,7 +11951,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11978,7 +11987,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12028,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12042,7 +12051,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12078,7 +12087,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12092,7 +12101,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12128,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12178,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12192,7 +12201,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12228,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12242,7 +12251,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12278,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12328,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12342,7 +12351,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12378,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12428,7 +12437,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12442,7 +12451,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12478,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12528,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12542,7 +12551,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12578,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12628,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12642,7 +12651,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12678,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12728,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12742,7 +12751,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12778,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12828,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12878,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12892,7 +12901,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12928,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12942,7 +12951,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12978,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -12992,7 +13001,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13028,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13042,7 +13051,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13078,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13092,7 +13101,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13128,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13142,7 +13151,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13178,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13192,7 +13201,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13228,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13242,7 +13251,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13278,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13292,7 +13301,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13328,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13342,7 +13351,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13378,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13392,7 +13401,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13428,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13442,7 +13451,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13478,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13492,7 +13501,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13528,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13542,7 +13551,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13578,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13592,7 +13601,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13628,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13642,7 +13651,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13678,7 +13687,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13692,7 +13701,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13728,7 +13737,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13742,7 +13751,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13778,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13792,7 +13801,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13842,7 +13851,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13892,7 +13901,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13942,7 +13951,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13978,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -13992,7 +14001,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14028,7 +14037,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14042,7 +14051,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14078,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14092,7 +14101,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14128,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14142,7 +14151,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14178,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14192,7 +14201,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14228,7 +14237,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14242,7 +14251,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14278,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14292,7 +14301,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14328,7 +14337,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14342,7 +14351,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14378,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14392,7 +14401,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14428,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14442,7 +14451,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14478,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14492,7 +14501,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14528,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14578,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14628,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14678,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14728,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14778,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14792,7 +14801,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14828,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14842,7 +14851,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14878,7 +14887,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14892,7 +14901,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14928,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14942,7 +14951,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14978,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -14992,7 +15001,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15028,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15042,7 +15051,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15078,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15092,7 +15101,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15128,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15142,7 +15151,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15178,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15192,10 +15201,10 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E284">
-        <v>18.44524163207222</v>
+        <v>19.02610478257335</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -15204,10 +15213,10 @@
         <v>0.02686166962975171</v>
       </c>
       <c r="H284">
-        <v>0.02729475836792778</v>
+        <v>0.02801389521742665</v>
       </c>
       <c r="I284">
-        <v>0.1269112618239312</v>
+        <v>0.7077744123250582</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15219,16 +15228,66 @@
         <v>22.59</v>
       </c>
       <c r="M284">
-        <v>17.92</v>
+        <v>18.2</v>
       </c>
       <c r="N284">
+        <v>23.52</v>
+      </c>
+      <c r="O284">
+        <v>1</v>
+      </c>
+      <c r="P284" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16">
+      <c r="A285" s="1">
+        <v>0</v>
+      </c>
+      <c r="B285" t="s">
+        <v>55</v>
+      </c>
+      <c r="C285">
+        <v>15.92097689295545</v>
+      </c>
+      <c r="D285" t="s">
+        <v>107</v>
+      </c>
+      <c r="E285">
+        <v>15.03870722998351</v>
+      </c>
+      <c r="F285">
+        <v>-1</v>
+      </c>
+      <c r="G285">
+        <v>0.03255902310704455</v>
+      </c>
+      <c r="H285">
+        <v>0.03070129277001649</v>
+      </c>
+      <c r="I285">
+        <v>0.8822696629719431</v>
+      </c>
+      <c r="J285">
+        <v>0.4601229594604285</v>
+      </c>
+      <c r="K285">
+        <v>18.08</v>
+      </c>
+      <c r="L285">
+        <v>24.24</v>
+      </c>
+      <c r="M285">
+        <v>17.02</v>
+      </c>
+      <c r="N285">
         <v>22.87</v>
       </c>
-      <c r="O284">
-        <v>1</v>
-      </c>
-      <c r="P284" t="s">
-        <v>219</v>
+      <c r="O285">
+        <v>1</v>
+      </c>
+      <c r="P285" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="227">
   <si>
     <t>trade_time</t>
   </si>
@@ -184,6 +184,9 @@
     <t>2021-07-23</t>
   </si>
   <si>
+    <t>2021-08-05</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -334,12 +337,15 @@
     <t>2021-04-26</t>
   </si>
   <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -683,6 +689,12 @@
   </si>
   <si>
     <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P285"/>
+  <dimension ref="A1:P287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1101,7 +1113,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1137,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1151,7 +1163,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1187,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1201,7 +1213,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1237,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1251,7 +1263,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1287,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1301,7 +1313,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1337,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1351,7 +1363,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1387,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1401,7 +1413,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1437,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1451,7 +1463,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1487,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1501,7 +1513,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1537,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1551,7 +1563,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1587,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1601,7 +1613,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1637,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1651,7 +1663,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1687,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1701,7 +1713,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1737,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1751,7 +1763,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1787,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1801,7 +1813,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1837,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1851,7 +1863,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1887,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1901,7 +1913,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1937,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1951,7 +1963,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1987,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2001,7 +2013,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2037,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2051,7 +2063,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2087,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2101,7 +2113,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2137,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2151,7 +2163,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2187,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2201,7 +2213,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2237,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2251,7 +2263,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2287,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2301,7 +2313,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2337,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2351,7 +2363,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2387,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2401,7 +2413,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2437,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2451,7 +2463,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2487,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2501,7 +2513,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2537,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2551,7 +2563,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2587,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2637,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2651,7 +2663,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2687,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2737,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2787,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2801,7 +2813,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2837,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2851,7 +2863,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2887,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2901,7 +2913,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2937,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2951,7 +2963,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2987,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3001,7 +3013,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3037,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3051,7 +3063,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3087,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3101,7 +3113,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3137,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3151,7 +3163,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3187,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3201,7 +3213,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3237,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3251,7 +3263,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3287,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3301,7 +3313,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3337,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3351,7 +3363,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3387,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3401,7 +3413,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3437,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3451,7 +3463,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3487,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3501,7 +3513,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3537,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3551,7 +3563,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3587,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3601,7 +3613,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3637,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3687,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3737,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3751,7 +3763,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3787,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3837,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3887,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3901,7 +3913,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3937,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3987,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4037,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4051,7 +4063,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4087,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4137,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4151,7 +4163,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4187,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4237,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4251,7 +4263,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4287,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4337,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4351,7 +4363,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4387,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4437,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4451,7 +4463,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4487,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4537,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4551,7 +4563,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4587,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4601,7 +4613,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4637,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4687,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4701,7 +4713,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4737,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4751,7 +4763,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4787,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4837,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4851,7 +4863,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4887,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4901,7 +4913,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4937,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4987,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5001,7 +5013,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5037,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5051,7 +5063,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5087,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5137,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5151,7 +5163,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5187,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5201,7 +5213,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5237,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5287,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5301,7 +5313,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5337,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5351,7 +5363,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5387,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5437,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5451,7 +5463,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5487,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5501,7 +5513,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5537,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5587,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5601,7 +5613,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5637,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5651,7 +5663,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5687,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5737,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5751,7 +5763,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5787,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5801,7 +5813,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5837,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5851,7 +5863,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5887,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5901,7 +5913,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5937,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5951,7 +5963,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5987,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6001,7 +6013,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6037,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6051,7 +6063,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6087,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6101,7 +6113,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6137,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6151,7 +6163,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6187,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6201,7 +6213,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6237,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6251,7 +6263,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6287,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6301,7 +6313,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6337,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6351,7 +6363,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6387,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6401,7 +6413,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6437,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6451,7 +6463,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6487,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6501,7 +6513,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6537,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6551,7 +6563,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6587,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6601,7 +6613,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6637,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6651,7 +6663,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6687,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6701,7 +6713,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6737,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6751,7 +6763,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6787,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6801,7 +6813,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6837,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6851,7 +6863,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6887,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6901,7 +6913,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6937,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6951,7 +6963,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6987,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7001,7 +7013,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7037,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7051,7 +7063,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7087,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7101,7 +7113,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7137,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7151,7 +7163,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7187,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7201,7 +7213,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7237,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7251,7 +7263,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7287,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7301,7 +7313,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7337,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7351,7 +7363,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7387,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7401,7 +7413,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7437,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7451,7 +7463,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7487,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7501,7 +7513,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7537,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7551,7 +7563,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7587,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7601,7 +7613,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7637,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7651,7 +7663,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7687,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7701,7 +7713,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7737,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7751,7 +7763,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7787,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7801,7 +7813,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7837,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7851,7 +7863,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7887,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7901,7 +7913,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7937,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7951,7 +7963,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7987,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8001,7 +8013,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8037,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8051,7 +8063,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8087,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8101,7 +8113,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8137,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8151,7 +8163,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8187,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8201,7 +8213,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8237,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8251,7 +8263,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8287,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8301,7 +8313,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8337,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8351,7 +8363,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8387,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8401,7 +8413,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8437,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8451,7 +8463,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8487,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8501,7 +8513,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8537,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8551,7 +8563,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8587,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8601,7 +8613,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8637,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8651,7 +8663,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8687,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8701,7 +8713,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8737,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8751,7 +8763,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8787,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8801,7 +8813,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8837,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8851,7 +8863,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8887,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8901,7 +8913,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8951,7 +8963,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8987,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9001,7 +9013,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9037,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9051,7 +9063,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9087,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9101,7 +9113,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9137,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9151,7 +9163,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9187,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9201,7 +9213,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9237,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9251,7 +9263,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9287,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9301,7 +9313,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9337,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9351,7 +9363,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9387,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9401,7 +9413,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9437,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9451,7 +9463,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9487,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9501,7 +9513,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9537,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9551,7 +9563,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9587,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9601,7 +9613,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9637,7 +9649,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9651,7 +9663,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9687,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9701,7 +9713,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9737,7 +9749,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9751,7 +9763,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9787,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9801,7 +9813,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9837,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9851,7 +9863,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9887,7 +9899,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9901,7 +9913,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9937,7 +9949,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9951,7 +9963,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9987,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10001,7 +10013,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10037,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10051,7 +10063,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10087,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10101,7 +10113,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10137,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10151,7 +10163,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10187,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10201,7 +10213,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10237,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10251,7 +10263,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10287,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10301,7 +10313,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10337,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10351,7 +10363,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10387,7 +10399,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10401,7 +10413,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10437,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10451,7 +10463,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10487,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10501,7 +10513,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10537,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10551,7 +10563,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10587,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10601,7 +10613,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10637,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10651,7 +10663,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10687,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10701,7 +10713,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10737,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10751,7 +10763,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10787,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10837,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10887,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10901,7 +10913,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10937,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10987,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11037,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11051,7 +11063,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11087,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11137,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11187,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11201,7 +11213,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11237,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11287,7 +11299,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11301,7 +11313,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11337,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11351,7 +11363,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11387,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11437,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11451,7 +11463,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11487,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11501,7 +11513,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11537,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11587,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11601,7 +11613,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11637,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11651,7 +11663,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11687,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11737,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11751,7 +11763,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11787,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11801,7 +11813,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11837,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11887,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11901,7 +11913,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11937,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11951,7 +11963,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11987,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12037,7 +12049,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12051,7 +12063,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12087,7 +12099,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12101,7 +12113,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12137,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12187,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12201,7 +12213,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12237,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12251,7 +12263,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12287,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12337,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12351,7 +12363,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12387,7 +12399,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12437,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12451,7 +12463,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12487,7 +12499,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12537,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12551,7 +12563,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12587,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12637,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12651,7 +12663,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12687,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12737,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12751,7 +12763,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12787,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12837,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12887,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12901,7 +12913,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12937,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12951,7 +12963,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12987,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13001,7 +13013,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13037,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13051,7 +13063,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13087,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13101,7 +13113,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13137,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13151,7 +13163,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13187,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13201,7 +13213,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13237,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13251,7 +13263,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13287,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13301,7 +13313,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13337,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13351,7 +13363,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13387,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13401,7 +13413,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13437,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13451,7 +13463,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13487,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13501,7 +13513,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13537,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13551,7 +13563,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13587,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13601,7 +13613,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13637,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13651,7 +13663,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13687,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13701,7 +13713,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13737,7 +13749,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13751,7 +13763,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13787,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13801,7 +13813,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13851,7 +13863,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13901,7 +13913,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13951,7 +13963,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13987,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14001,7 +14013,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14037,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14051,7 +14063,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14087,7 +14099,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14101,7 +14113,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14137,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14151,7 +14163,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14187,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14201,7 +14213,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14237,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14251,7 +14263,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14287,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14301,7 +14313,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14337,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14351,7 +14363,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14387,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14401,7 +14413,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14437,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14451,7 +14463,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14487,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14501,7 +14513,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14537,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14587,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14637,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14687,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14737,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14787,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14801,7 +14813,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14837,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14851,7 +14863,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14887,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14901,7 +14913,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14937,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14951,7 +14963,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14987,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15001,7 +15013,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15037,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15051,7 +15063,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15087,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15101,7 +15113,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15137,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15151,7 +15163,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15187,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15201,10 +15213,10 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E284">
-        <v>19.02610478257335</v>
+        <v>19.21190627946725</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -15213,10 +15225,10 @@
         <v>0.02686166962975171</v>
       </c>
       <c r="H284">
-        <v>0.02801389521742665</v>
+        <v>0.02832809372053275</v>
       </c>
       <c r="I284">
-        <v>0.7077744123250582</v>
+        <v>0.8935759092189635</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15228,16 +15240,16 @@
         <v>22.59</v>
       </c>
       <c r="M284">
-        <v>18.2</v>
+        <v>18.46</v>
       </c>
       <c r="N284">
-        <v>23.52</v>
+        <v>23.77</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15251,7 +15263,7 @@
         <v>15.92097689295545</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E285">
         <v>15.03870722998351</v>
@@ -15287,7 +15299,107 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>222</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16">
+      <c r="A286" s="1">
+        <v>0</v>
+      </c>
+      <c r="B286" t="s">
+        <v>56</v>
+      </c>
+      <c r="C286">
+        <v>13.25394266548507</v>
+      </c>
+      <c r="D286" t="s">
+        <v>109</v>
+      </c>
+      <c r="E286">
+        <v>13.75369176963328</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286">
+        <v>0.03248605733451494</v>
+      </c>
+      <c r="H286">
+        <v>0.03328630823036672</v>
+      </c>
+      <c r="I286">
+        <v>0.4997491041482043</v>
+      </c>
+      <c r="J286">
+        <v>0.536610342327842</v>
+      </c>
+      <c r="K286">
+        <v>17.92</v>
+      </c>
+      <c r="L286">
+        <v>22.87</v>
+      </c>
+      <c r="M286">
+        <v>18.2</v>
+      </c>
+      <c r="N286">
+        <v>23.52</v>
+      </c>
+      <c r="O286">
+        <v>1</v>
+      </c>
+      <c r="P286" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16">
+      <c r="A287" s="1">
+        <v>0</v>
+      </c>
+      <c r="B287" t="s">
+        <v>56</v>
+      </c>
+      <c r="C287">
+        <v>11.23974705483469</v>
+      </c>
+      <c r="D287" t="s">
+        <v>109</v>
+      </c>
+      <c r="E287">
+        <v>11.70802435256648</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287">
+        <v>0.03450025294516532</v>
+      </c>
+      <c r="H287">
+        <v>0.03533197564743353</v>
+      </c>
+      <c r="I287">
+        <v>0.4682772977317917</v>
+      </c>
+      <c r="J287">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K287">
+        <v>17.92</v>
+      </c>
+      <c r="L287">
+        <v>22.87</v>
+      </c>
+      <c r="M287">
+        <v>18.2</v>
+      </c>
+      <c r="N287">
+        <v>23.52</v>
+      </c>
+      <c r="O287">
+        <v>1</v>
+      </c>
+      <c r="P287" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="227">
   <si>
     <t>trade_time</t>
   </si>
@@ -1052,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P287"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15360,28 +15360,28 @@
         <v>56</v>
       </c>
       <c r="C287">
-        <v>11.23974705483469</v>
+        <v>11.55767866138674</v>
       </c>
       <c r="D287" t="s">
         <v>109</v>
       </c>
       <c r="E287">
-        <v>11.70802435256648</v>
+        <v>12.03092364047091</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03450025294516532</v>
+        <v>0.03418232133861326</v>
       </c>
       <c r="H287">
-        <v>0.03533197564743353</v>
+        <v>0.03500907635952909</v>
       </c>
       <c r="I287">
-        <v>0.4682772977317917</v>
+        <v>0.4732449790841677</v>
       </c>
       <c r="J287">
-        <v>0.6490096509578859</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K287">
         <v>17.92</v>
@@ -15399,6 +15399,56 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>56</v>
+      </c>
+      <c r="C288">
+        <v>11.23974705483469</v>
+      </c>
+      <c r="D288" t="s">
+        <v>109</v>
+      </c>
+      <c r="E288">
+        <v>11.70802435256648</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>0.03450025294516532</v>
+      </c>
+      <c r="H288">
+        <v>0.03533197564743353</v>
+      </c>
+      <c r="I288">
+        <v>0.4682772977317917</v>
+      </c>
+      <c r="J288">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K288">
+        <v>17.92</v>
+      </c>
+      <c r="L288">
+        <v>22.87</v>
+      </c>
+      <c r="M288">
+        <v>18.2</v>
+      </c>
+      <c r="N288">
+        <v>23.52</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
         <v>226</v>
       </c>
     </row>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -340,7 +340,7 @@
     <t>2021-08-10</t>
   </si>
   <si>
-    <t>2021-07-28</t>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-08-09</t>
@@ -689,9 +689,6 @@
   </si>
   <si>
     <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1052,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15266,7 +15263,7 @@
         <v>108</v>
       </c>
       <c r="E285">
-        <v>15.03870722998351</v>
+        <v>15.1799342810648</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15275,10 +15272,10 @@
         <v>0.03255902310704455</v>
       </c>
       <c r="H285">
-        <v>0.03070129277001649</v>
+        <v>0.0306400657189352</v>
       </c>
       <c r="I285">
-        <v>0.8822696629719431</v>
+        <v>0.7410426118906521</v>
       </c>
       <c r="J285">
         <v>0.4601229594604285</v>
@@ -15290,10 +15287,10 @@
         <v>24.24</v>
       </c>
       <c r="M285">
-        <v>17.02</v>
+        <v>16.8</v>
       </c>
       <c r="N285">
-        <v>22.87</v>
+        <v>22.91</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15349,7 +15346,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15360,28 +15357,28 @@
         <v>56</v>
       </c>
       <c r="C287">
-        <v>11.55767866138674</v>
+        <v>11.23974705483469</v>
       </c>
       <c r="D287" t="s">
         <v>109</v>
       </c>
       <c r="E287">
-        <v>12.03092364047091</v>
+        <v>11.70802435256648</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03418232133861326</v>
+        <v>0.03450025294516532</v>
       </c>
       <c r="H287">
-        <v>0.03500907635952909</v>
+        <v>0.03533197564743353</v>
       </c>
       <c r="I287">
-        <v>0.4732449790841677</v>
+        <v>0.4682772977317917</v>
       </c>
       <c r="J287">
-        <v>0.6312679318422579</v>
+        <v>0.6490096509578859</v>
       </c>
       <c r="K287">
         <v>17.92</v>
@@ -15399,57 +15396,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16">
-      <c r="A288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B288" t="s">
-        <v>56</v>
-      </c>
-      <c r="C288">
-        <v>11.23974705483469</v>
-      </c>
-      <c r="D288" t="s">
-        <v>109</v>
-      </c>
-      <c r="E288">
-        <v>11.70802435256648</v>
-      </c>
-      <c r="F288">
-        <v>1</v>
-      </c>
-      <c r="G288">
-        <v>0.03450025294516532</v>
-      </c>
-      <c r="H288">
-        <v>0.03533197564743353</v>
-      </c>
-      <c r="I288">
-        <v>0.4682772977317917</v>
-      </c>
-      <c r="J288">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K288">
-        <v>17.92</v>
-      </c>
-      <c r="L288">
-        <v>22.87</v>
-      </c>
-      <c r="M288">
-        <v>18.2</v>
-      </c>
-      <c r="N288">
-        <v>23.52</v>
-      </c>
-      <c r="O288">
-        <v>1</v>
-      </c>
-      <c r="P288" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -1049,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P287"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15357,28 +15357,28 @@
         <v>56</v>
       </c>
       <c r="C287">
-        <v>11.23974705483469</v>
+        <v>11.55767866138674</v>
       </c>
       <c r="D287" t="s">
         <v>109</v>
       </c>
       <c r="E287">
-        <v>11.70802435256648</v>
+        <v>12.03092364047091</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03450025294516532</v>
+        <v>0.03418232133861326</v>
       </c>
       <c r="H287">
-        <v>0.03533197564743353</v>
+        <v>0.03500907635952909</v>
       </c>
       <c r="I287">
-        <v>0.4682772977317917</v>
+        <v>0.4732449790841677</v>
       </c>
       <c r="J287">
-        <v>0.6490096509578859</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K287">
         <v>17.92</v>
@@ -15396,6 +15396,56 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>56</v>
+      </c>
+      <c r="C288">
+        <v>11.23974705483469</v>
+      </c>
+      <c r="D288" t="s">
+        <v>109</v>
+      </c>
+      <c r="E288">
+        <v>11.70802435256648</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>0.03450025294516532</v>
+      </c>
+      <c r="H288">
+        <v>0.03533197564743353</v>
+      </c>
+      <c r="I288">
+        <v>0.4682772977317917</v>
+      </c>
+      <c r="J288">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K288">
+        <v>17.92</v>
+      </c>
+      <c r="L288">
+        <v>22.87</v>
+      </c>
+      <c r="M288">
+        <v>18.2</v>
+      </c>
+      <c r="N288">
+        <v>23.52</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
         <v>225</v>
       </c>
     </row>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,12 +181,6 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -340,12 +334,6 @@
     <t>2021-08-10</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -686,12 +674,6 @@
   </si>
   <si>
     <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1110,7 +1092,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1146,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1160,7 +1142,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1196,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1210,7 +1192,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1246,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1260,7 +1242,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1296,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1310,7 +1292,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1346,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1360,7 +1342,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1396,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1410,7 +1392,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1446,7 +1428,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1460,7 +1442,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1496,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1510,7 +1492,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1546,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1560,7 +1542,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1596,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1610,7 +1592,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1646,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1660,7 +1642,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1696,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1710,7 +1692,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1746,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1760,7 +1742,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1796,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1810,7 +1792,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1846,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1860,7 +1842,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1896,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1910,7 +1892,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1946,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1960,7 +1942,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1996,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2010,7 +1992,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2046,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2060,7 +2042,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2096,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2110,7 +2092,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2146,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2160,7 +2142,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2196,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2210,7 +2192,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2246,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2260,7 +2242,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2296,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2310,7 +2292,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2346,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2360,7 +2342,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2396,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2410,7 +2392,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2446,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2460,7 +2442,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2496,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2510,7 +2492,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2546,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2560,7 +2542,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2596,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2660,7 +2642,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2696,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,7 +2792,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2846,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2860,7 +2842,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2896,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2910,7 +2892,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2946,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2960,7 +2942,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2996,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3010,7 +2992,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3046,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3060,7 +3042,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3096,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3110,7 +3092,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3146,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3160,7 +3142,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3196,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3210,7 +3192,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3246,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3260,7 +3242,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3296,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3310,7 +3292,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3346,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3360,7 +3342,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3396,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3410,7 +3392,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3446,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3460,7 +3442,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3496,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3510,7 +3492,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3546,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3560,7 +3542,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3596,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3610,7 +3592,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3646,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3760,7 +3742,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3796,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3910,7 +3892,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3946,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4060,7 +4042,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4096,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4160,7 +4142,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4196,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4260,7 +4242,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4296,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4360,7 +4342,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4396,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4460,7 +4442,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4496,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4560,7 +4542,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4596,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4610,7 +4592,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4646,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4710,7 +4692,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4746,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4760,7 +4742,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4796,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4860,7 +4842,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4896,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4910,7 +4892,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4946,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5010,7 +4992,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5046,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5060,7 +5042,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5096,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5160,7 +5142,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5196,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5210,7 +5192,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5246,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5310,7 +5292,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5346,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5360,7 +5342,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5396,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5460,7 +5442,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5496,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5510,7 +5492,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5546,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5610,7 +5592,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5646,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5660,7 +5642,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5696,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5760,7 +5742,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5796,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5810,7 +5792,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5846,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5860,7 +5842,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5896,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5910,7 +5892,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5946,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5960,7 +5942,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5996,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6010,7 +5992,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6046,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6060,7 +6042,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6096,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6110,7 +6092,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6146,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6160,7 +6142,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6196,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6210,7 +6192,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6246,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6260,7 +6242,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6296,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6310,7 +6292,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6346,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6360,7 +6342,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6396,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6410,7 +6392,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6446,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6460,7 +6442,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6496,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6510,7 +6492,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6546,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6560,7 +6542,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6596,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6610,7 +6592,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6646,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6660,7 +6642,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6696,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6710,7 +6692,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6746,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6760,7 +6742,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6796,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6810,7 +6792,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6846,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6860,7 +6842,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6896,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6910,7 +6892,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6946,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,7 +6942,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6996,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7010,7 +6992,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7046,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7060,7 +7042,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7096,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7110,7 +7092,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7146,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,7 +7142,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7196,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7210,7 +7192,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7246,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7260,7 +7242,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7296,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7310,7 +7292,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7346,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7360,7 +7342,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7396,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7410,7 +7392,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7446,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7460,7 +7442,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7496,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7510,7 +7492,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7546,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7560,7 +7542,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7596,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7610,7 +7592,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7646,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7660,7 +7642,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7696,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7710,7 +7692,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7746,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7760,7 +7742,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7796,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7810,7 +7792,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7846,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7860,7 +7842,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7896,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7910,7 +7892,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7946,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7960,7 +7942,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7996,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8010,7 +7992,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8046,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8060,7 +8042,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8096,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8110,7 +8092,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8146,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8160,7 +8142,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8196,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8210,7 +8192,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8246,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8260,7 +8242,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8296,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8310,7 +8292,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8346,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8360,7 +8342,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8396,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8410,7 +8392,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8446,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8460,7 +8442,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8496,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8510,7 +8492,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8546,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8560,7 +8542,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8596,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8610,7 +8592,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8646,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8660,7 +8642,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8696,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8710,7 +8692,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8746,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8760,7 +8742,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8796,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8810,7 +8792,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8846,7 +8828,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8860,7 +8842,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8896,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8910,7 +8892,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8960,7 +8942,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8996,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9010,7 +8992,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9046,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9060,7 +9042,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9096,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9110,7 +9092,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9146,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9160,7 +9142,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9196,7 +9178,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9210,7 +9192,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9246,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9260,7 +9242,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9296,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9310,7 +9292,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9346,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9360,7 +9342,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9396,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9410,7 +9392,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9446,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9460,7 +9442,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9496,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9510,7 +9492,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9546,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9560,7 +9542,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9596,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9610,7 +9592,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9646,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9660,7 +9642,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9696,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9710,7 +9692,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9746,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9760,7 +9742,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9796,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9810,7 +9792,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9846,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9860,7 +9842,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9896,7 +9878,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9910,7 +9892,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9946,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9960,7 +9942,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9996,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10010,7 +9992,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10046,7 +10028,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10060,7 +10042,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10096,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10110,7 +10092,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10146,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10160,7 +10142,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10196,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10210,7 +10192,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10246,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10260,7 +10242,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10296,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10310,7 +10292,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10346,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10360,7 +10342,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10396,7 +10378,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10410,7 +10392,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10446,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10460,7 +10442,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10496,7 +10478,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10510,7 +10492,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10546,7 +10528,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10560,7 +10542,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10596,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10610,7 +10592,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10646,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10660,7 +10642,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10696,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10710,7 +10692,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10746,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10760,7 +10742,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10796,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10910,7 +10892,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10946,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +10978,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11028,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11060,7 +11042,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11096,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11210,7 +11192,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11246,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11278,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11310,7 +11292,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11346,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11360,7 +11342,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11396,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11460,7 +11442,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11496,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11510,7 +11492,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11546,7 +11528,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11610,7 +11592,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11646,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11660,7 +11642,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11696,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11760,7 +11742,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11796,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11810,7 +11792,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11846,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11878,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11910,7 +11892,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11946,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11960,7 +11942,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11996,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12060,7 +12042,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12096,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12110,7 +12092,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12146,7 +12128,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12210,7 +12192,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12246,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12260,7 +12242,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12296,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12360,7 +12342,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12396,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12460,7 +12442,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12496,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12560,7 +12542,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12596,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12660,7 +12642,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12696,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12760,7 +12742,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12796,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12910,7 +12892,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12946,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12960,7 +12942,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12996,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13010,7 +12992,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13046,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13060,7 +13042,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13096,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13110,7 +13092,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13146,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13160,7 +13142,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13196,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13210,7 +13192,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13246,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13260,7 +13242,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13296,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13310,7 +13292,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13346,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13360,7 +13342,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13396,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13410,7 +13392,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13446,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13460,7 +13442,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13496,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13510,7 +13492,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13546,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13560,7 +13542,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13596,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13610,7 +13592,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13646,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13660,7 +13642,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13696,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13710,7 +13692,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13746,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13760,7 +13742,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13796,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13810,7 +13792,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13860,7 +13842,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13910,7 +13892,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13960,7 +13942,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13996,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14010,7 +13992,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14046,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14060,7 +14042,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14096,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14110,7 +14092,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14146,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14160,7 +14142,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14196,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14210,7 +14192,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14246,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14260,7 +14242,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14296,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14310,7 +14292,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14346,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14360,7 +14342,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14396,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14410,7 +14392,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14446,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14460,7 +14442,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14496,7 +14478,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14510,7 +14492,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14546,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14596,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14646,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14696,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14746,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14796,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14810,7 +14792,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14846,7 +14828,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14860,7 +14842,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14896,7 +14878,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14910,7 +14892,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14946,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14960,7 +14942,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14996,7 +14978,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15010,7 +14992,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15046,7 +15028,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15060,7 +15042,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15096,7 +15078,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15110,7 +15092,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15146,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15160,7 +15142,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15196,7 +15178,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15210,7 +15192,7 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E284">
         <v>19.21190627946725</v>
@@ -15246,207 +15228,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16">
-      <c r="A285" s="1">
-        <v>0</v>
-      </c>
-      <c r="B285" t="s">
-        <v>55</v>
-      </c>
-      <c r="C285">
-        <v>15.92097689295545</v>
-      </c>
-      <c r="D285" t="s">
-        <v>108</v>
-      </c>
-      <c r="E285">
-        <v>15.1799342810648</v>
-      </c>
-      <c r="F285">
-        <v>-1</v>
-      </c>
-      <c r="G285">
-        <v>0.03255902310704455</v>
-      </c>
-      <c r="H285">
-        <v>0.0306400657189352</v>
-      </c>
-      <c r="I285">
-        <v>0.7410426118906521</v>
-      </c>
-      <c r="J285">
-        <v>0.4601229594604285</v>
-      </c>
-      <c r="K285">
-        <v>18.08</v>
-      </c>
-      <c r="L285">
-        <v>24.24</v>
-      </c>
-      <c r="M285">
-        <v>16.8</v>
-      </c>
-      <c r="N285">
-        <v>22.91</v>
-      </c>
-      <c r="O285">
-        <v>1</v>
-      </c>
-      <c r="P285" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16">
-      <c r="A286" s="1">
-        <v>0</v>
-      </c>
-      <c r="B286" t="s">
-        <v>56</v>
-      </c>
-      <c r="C286">
-        <v>13.25394266548507</v>
-      </c>
-      <c r="D286" t="s">
-        <v>109</v>
-      </c>
-      <c r="E286">
-        <v>13.75369176963328</v>
-      </c>
-      <c r="F286">
-        <v>1</v>
-      </c>
-      <c r="G286">
-        <v>0.03248605733451494</v>
-      </c>
-      <c r="H286">
-        <v>0.03328630823036672</v>
-      </c>
-      <c r="I286">
-        <v>0.4997491041482043</v>
-      </c>
-      <c r="J286">
-        <v>0.536610342327842</v>
-      </c>
-      <c r="K286">
-        <v>17.92</v>
-      </c>
-      <c r="L286">
-        <v>22.87</v>
-      </c>
-      <c r="M286">
-        <v>18.2</v>
-      </c>
-      <c r="N286">
-        <v>23.52</v>
-      </c>
-      <c r="O286">
-        <v>1</v>
-      </c>
-      <c r="P286" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16">
-      <c r="A287" s="1">
-        <v>0</v>
-      </c>
-      <c r="B287" t="s">
-        <v>56</v>
-      </c>
-      <c r="C287">
-        <v>11.55767866138674</v>
-      </c>
-      <c r="D287" t="s">
-        <v>109</v>
-      </c>
-      <c r="E287">
-        <v>12.03092364047091</v>
-      </c>
-      <c r="F287">
-        <v>1</v>
-      </c>
-      <c r="G287">
-        <v>0.03418232133861326</v>
-      </c>
-      <c r="H287">
-        <v>0.03500907635952909</v>
-      </c>
-      <c r="I287">
-        <v>0.4732449790841677</v>
-      </c>
-      <c r="J287">
-        <v>0.6312679318422579</v>
-      </c>
-      <c r="K287">
-        <v>17.92</v>
-      </c>
-      <c r="L287">
-        <v>22.87</v>
-      </c>
-      <c r="M287">
-        <v>18.2</v>
-      </c>
-      <c r="N287">
-        <v>23.52</v>
-      </c>
-      <c r="O287">
-        <v>1</v>
-      </c>
-      <c r="P287" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16">
-      <c r="A288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B288" t="s">
-        <v>56</v>
-      </c>
-      <c r="C288">
-        <v>11.23974705483469</v>
-      </c>
-      <c r="D288" t="s">
-        <v>109</v>
-      </c>
-      <c r="E288">
-        <v>11.70802435256648</v>
-      </c>
-      <c r="F288">
-        <v>1</v>
-      </c>
-      <c r="G288">
-        <v>0.03450025294516532</v>
-      </c>
-      <c r="H288">
-        <v>0.03533197564743353</v>
-      </c>
-      <c r="I288">
-        <v>0.4682772977317917</v>
-      </c>
-      <c r="J288">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K288">
-        <v>17.92</v>
-      </c>
-      <c r="L288">
-        <v>22.87</v>
-      </c>
-      <c r="M288">
-        <v>18.2</v>
-      </c>
-      <c r="N288">
-        <v>23.52</v>
-      </c>
-      <c r="O288">
-        <v>1</v>
-      </c>
-      <c r="P288" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="227">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,9 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-08-18</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
     <t>2021-08-10</t>
   </si>
   <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -674,6 +680,21 @@
   </si>
   <si>
     <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P284"/>
+  <dimension ref="A1:P291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1092,7 +1113,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1128,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1142,7 +1163,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1178,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1192,7 +1213,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1228,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1242,7 +1263,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1278,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1292,7 +1313,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1328,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1342,7 +1363,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1378,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1392,7 +1413,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1428,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1442,7 +1463,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1478,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1492,7 +1513,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1528,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1542,7 +1563,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1578,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1592,7 +1613,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1628,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1642,7 +1663,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1678,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1692,7 +1713,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1728,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1742,7 +1763,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1778,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1792,7 +1813,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1828,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1842,7 +1863,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1878,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1892,7 +1913,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1928,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1942,7 +1963,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1978,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1992,7 +2013,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2028,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2042,7 +2063,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2078,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2092,7 +2113,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2128,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2142,7 +2163,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2178,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2192,7 +2213,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2228,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2242,7 +2263,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2278,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2292,7 +2313,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2328,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2342,7 +2363,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2378,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2392,7 +2413,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2428,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2442,7 +2463,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2478,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2492,7 +2513,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2528,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2542,7 +2563,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2578,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2628,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2642,7 +2663,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2678,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2728,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2778,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2792,7 +2813,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2828,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2842,7 +2863,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2878,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2892,7 +2913,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2928,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2942,7 +2963,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2978,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2992,7 +3013,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3028,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3042,7 +3063,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3078,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3092,7 +3113,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3128,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3142,7 +3163,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3178,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3192,7 +3213,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3228,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3242,7 +3263,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3278,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3292,7 +3313,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3328,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3342,7 +3363,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3378,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3392,7 +3413,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3428,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3442,7 +3463,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3478,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3492,7 +3513,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3528,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3542,7 +3563,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3578,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3592,7 +3613,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3628,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3678,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3728,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3742,7 +3763,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3778,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3828,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3878,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3892,7 +3913,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3928,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3978,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4028,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4042,7 +4063,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4078,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4128,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4142,7 +4163,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4178,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4228,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4242,7 +4263,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4278,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4328,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4342,7 +4363,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4378,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4428,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4442,7 +4463,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4478,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4528,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4542,7 +4563,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4578,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4592,7 +4613,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4628,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4678,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4692,7 +4713,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4728,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4742,7 +4763,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4778,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4828,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4842,7 +4863,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4878,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4892,7 +4913,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4928,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4978,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4992,7 +5013,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5028,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5042,7 +5063,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5078,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5128,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5142,7 +5163,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5178,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5192,7 +5213,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5228,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5278,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5292,7 +5313,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5328,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5342,7 +5363,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5378,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5428,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5442,7 +5463,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5478,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5492,7 +5513,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5528,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5578,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5592,7 +5613,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5628,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5642,7 +5663,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5678,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5728,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5742,7 +5763,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5778,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5792,7 +5813,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5828,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5842,7 +5863,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5878,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5892,7 +5913,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5928,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5942,7 +5963,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5978,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5992,7 +6013,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6028,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6042,7 +6063,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6078,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6092,7 +6113,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6128,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6142,7 +6163,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6178,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6192,7 +6213,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6228,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6242,7 +6263,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6278,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6292,7 +6313,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6328,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6342,7 +6363,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6378,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6392,7 +6413,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6428,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6442,7 +6463,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6478,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6492,7 +6513,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6528,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6542,7 +6563,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6578,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6592,7 +6613,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6628,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6642,7 +6663,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6678,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6692,7 +6713,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6728,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6742,7 +6763,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6778,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6792,7 +6813,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6828,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6842,7 +6863,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6878,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6892,7 +6913,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6928,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6942,7 +6963,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6978,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6992,7 +7013,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7028,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7042,7 +7063,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7078,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7092,7 +7113,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7128,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7142,7 +7163,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7178,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7192,7 +7213,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7228,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7242,7 +7263,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7278,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7292,7 +7313,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7328,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7342,7 +7363,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7378,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7392,7 +7413,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7428,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7442,7 +7463,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7478,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7492,7 +7513,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7528,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7542,7 +7563,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7578,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7592,7 +7613,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7628,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7642,7 +7663,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7678,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7692,7 +7713,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7728,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7742,7 +7763,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7778,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7792,7 +7813,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7828,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7842,7 +7863,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7878,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7892,7 +7913,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7928,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7942,7 +7963,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7978,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7992,7 +8013,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8028,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8042,7 +8063,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8078,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8092,7 +8113,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8128,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8142,7 +8163,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8178,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8192,7 +8213,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8228,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8242,7 +8263,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8278,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8292,7 +8313,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8328,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8342,7 +8363,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8378,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8392,7 +8413,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8428,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8442,7 +8463,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8478,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8492,7 +8513,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8528,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8542,7 +8563,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8578,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8592,7 +8613,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8628,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8642,7 +8663,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8678,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8692,7 +8713,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8728,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8742,7 +8763,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8778,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8792,7 +8813,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8828,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8842,7 +8863,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8878,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8892,7 +8913,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8942,7 +8963,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8978,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8992,7 +9013,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9028,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9042,7 +9063,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9078,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9092,7 +9113,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9128,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9142,7 +9163,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9178,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9192,7 +9213,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9228,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9242,7 +9263,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9278,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9292,7 +9313,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9328,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9342,7 +9363,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9378,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9392,7 +9413,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9428,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9442,7 +9463,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9478,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9492,7 +9513,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9528,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9542,7 +9563,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9578,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9592,7 +9613,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9628,7 +9649,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9642,7 +9663,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9678,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9692,7 +9713,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9728,7 +9749,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9742,7 +9763,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9778,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9792,7 +9813,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9828,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9842,7 +9863,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9878,7 +9899,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9892,7 +9913,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9928,7 +9949,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9942,7 +9963,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9978,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -9992,7 +10013,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10028,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10042,7 +10063,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10078,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10092,7 +10113,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10128,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10142,7 +10163,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10178,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10192,7 +10213,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10228,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10242,7 +10263,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10278,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10292,7 +10313,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10328,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10342,7 +10363,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10378,7 +10399,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10392,7 +10413,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10428,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10442,7 +10463,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10478,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10492,7 +10513,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10528,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10542,7 +10563,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10578,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10592,7 +10613,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10628,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10642,7 +10663,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10678,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10692,7 +10713,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10728,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10742,7 +10763,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10778,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10828,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10878,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10892,7 +10913,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10928,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10978,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11028,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11042,7 +11063,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11078,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11128,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11178,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11192,7 +11213,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11228,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11278,7 +11299,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11292,7 +11313,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11328,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11342,7 +11363,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11378,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11428,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11442,7 +11463,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11478,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11492,7 +11513,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11528,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11578,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11592,7 +11613,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11628,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11642,7 +11663,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11678,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11728,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11742,7 +11763,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11778,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11792,7 +11813,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11828,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11878,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11892,7 +11913,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11928,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11942,7 +11963,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11978,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12028,7 +12049,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12042,7 +12063,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12078,7 +12099,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12092,7 +12113,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12128,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12178,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12192,7 +12213,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12228,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12242,7 +12263,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12278,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12328,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12342,7 +12363,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12378,7 +12399,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12428,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12442,7 +12463,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12478,7 +12499,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12528,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12542,7 +12563,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12578,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12628,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12642,7 +12663,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12678,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12728,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12742,7 +12763,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12778,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12828,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12878,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12892,7 +12913,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12928,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12942,7 +12963,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12978,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -12992,7 +13013,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13028,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13042,7 +13063,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13078,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13092,7 +13113,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13128,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13142,7 +13163,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13178,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13192,7 +13213,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13228,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13242,7 +13263,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13278,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13292,7 +13313,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13328,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13342,7 +13363,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13378,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13392,7 +13413,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13428,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13442,7 +13463,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13478,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13492,7 +13513,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13528,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13542,7 +13563,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13578,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13592,7 +13613,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13628,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13642,7 +13663,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13678,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13692,7 +13713,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13728,7 +13749,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13742,7 +13763,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13778,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13792,7 +13813,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13842,7 +13863,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13892,7 +13913,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13942,7 +13963,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13978,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -13992,7 +14013,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14028,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14042,7 +14063,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14078,7 +14099,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14092,7 +14113,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14128,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14142,7 +14163,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14178,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14192,7 +14213,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14228,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14242,7 +14263,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14278,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14292,7 +14313,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14328,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14342,7 +14363,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14378,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14392,7 +14413,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14428,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14442,7 +14463,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14478,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14492,7 +14513,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14528,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14578,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14628,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14678,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14728,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14778,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14792,7 +14813,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14828,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14842,7 +14863,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14878,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14892,7 +14913,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14928,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14942,7 +14963,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14978,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -14992,7 +15013,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15028,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15042,7 +15063,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15078,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15092,7 +15113,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15128,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15142,7 +15163,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15178,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15192,7 +15213,7 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E284">
         <v>19.21190627946725</v>
@@ -15228,7 +15249,357 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>219</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16">
+      <c r="A285" s="1">
+        <v>1</v>
+      </c>
+      <c r="B285" t="s">
+        <v>55</v>
+      </c>
+      <c r="C285">
+        <v>20.48449573097064</v>
+      </c>
+      <c r="D285" t="s">
+        <v>107</v>
+      </c>
+      <c r="E285">
+        <v>19.94363258046951</v>
+      </c>
+      <c r="F285">
+        <v>-1</v>
+      </c>
+      <c r="G285">
+        <v>0.03001550426902936</v>
+      </c>
+      <c r="H285">
+        <v>0.02933636741953049</v>
+      </c>
+      <c r="I285">
+        <v>0.5408631505011279</v>
+      </c>
+      <c r="J285">
+        <v>0.246917319638827</v>
+      </c>
+      <c r="K285">
+        <v>19.3</v>
+      </c>
+      <c r="L285">
+        <v>25.25</v>
+      </c>
+      <c r="M285">
+        <v>19.02</v>
+      </c>
+      <c r="N285">
+        <v>24.64</v>
+      </c>
+      <c r="O285">
+        <v>1</v>
+      </c>
+      <c r="P285" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16">
+      <c r="A286" s="1">
+        <v>0</v>
+      </c>
+      <c r="B286" t="s">
+        <v>55</v>
+      </c>
+      <c r="C286">
+        <v>16.36962688241373</v>
+      </c>
+      <c r="D286" t="s">
+        <v>107</v>
+      </c>
+      <c r="E286">
+        <v>15.88846131106265</v>
+      </c>
+      <c r="F286">
+        <v>-1</v>
+      </c>
+      <c r="G286">
+        <v>0.03413037311758627</v>
+      </c>
+      <c r="H286">
+        <v>0.03339153868893735</v>
+      </c>
+      <c r="I286">
+        <v>0.4811655713510792</v>
+      </c>
+      <c r="J286">
+        <v>0.4601229594604285</v>
+      </c>
+      <c r="K286">
+        <v>19.3</v>
+      </c>
+      <c r="L286">
+        <v>25.25</v>
+      </c>
+      <c r="M286">
+        <v>19.02</v>
+      </c>
+      <c r="N286">
+        <v>24.64</v>
+      </c>
+      <c r="O286">
+        <v>1</v>
+      </c>
+      <c r="P286" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16">
+      <c r="A287" s="1">
+        <v>0</v>
+      </c>
+      <c r="B287" t="s">
+        <v>55</v>
+      </c>
+      <c r="C287">
+        <v>15.83273115942659</v>
+      </c>
+      <c r="D287" t="s">
+        <v>107</v>
+      </c>
+      <c r="E287">
+        <v>15.35935474882351</v>
+      </c>
+      <c r="F287">
+        <v>-1</v>
+      </c>
+      <c r="G287">
+        <v>0.03466726884057342</v>
+      </c>
+      <c r="H287">
+        <v>0.0339206452511765</v>
+      </c>
+      <c r="I287">
+        <v>0.4733764106030787</v>
+      </c>
+      <c r="J287">
+        <v>0.4879413907032856</v>
+      </c>
+      <c r="K287">
+        <v>19.3</v>
+      </c>
+      <c r="L287">
+        <v>25.25</v>
+      </c>
+      <c r="M287">
+        <v>19.02</v>
+      </c>
+      <c r="N287">
+        <v>24.64</v>
+      </c>
+      <c r="O287">
+        <v>1</v>
+      </c>
+      <c r="P287" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>55</v>
+      </c>
+      <c r="C288">
+        <v>15.33566012693453</v>
+      </c>
+      <c r="D288" t="s">
+        <v>107</v>
+      </c>
+      <c r="E288">
+        <v>14.86949510954896</v>
+      </c>
+      <c r="F288">
+        <v>-1</v>
+      </c>
+      <c r="G288">
+        <v>0.03516433987306546</v>
+      </c>
+      <c r="H288">
+        <v>0.03441050489045105</v>
+      </c>
+      <c r="I288">
+        <v>0.4661650173855776</v>
+      </c>
+      <c r="J288">
+        <v>0.513696366480076</v>
+      </c>
+      <c r="K288">
+        <v>19.3</v>
+      </c>
+      <c r="L288">
+        <v>25.25</v>
+      </c>
+      <c r="M288">
+        <v>19.02</v>
+      </c>
+      <c r="N288">
+        <v>24.64</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16">
+      <c r="A289" s="1">
+        <v>0</v>
+      </c>
+      <c r="B289" t="s">
+        <v>55</v>
+      </c>
+      <c r="C289">
+        <v>14.89342039307265</v>
+      </c>
+      <c r="D289" t="s">
+        <v>107</v>
+      </c>
+      <c r="E289">
+        <v>14.43367128892445</v>
+      </c>
+      <c r="F289">
+        <v>-1</v>
+      </c>
+      <c r="G289">
+        <v>0.03560657960692735</v>
+      </c>
+      <c r="H289">
+        <v>0.03484632871107556</v>
+      </c>
+      <c r="I289">
+        <v>0.4597491041482034</v>
+      </c>
+      <c r="J289">
+        <v>0.536610342327842</v>
+      </c>
+      <c r="K289">
+        <v>19.3</v>
+      </c>
+      <c r="L289">
+        <v>25.25</v>
+      </c>
+      <c r="M289">
+        <v>19.02</v>
+      </c>
+      <c r="N289">
+        <v>24.64</v>
+      </c>
+      <c r="O289">
+        <v>1</v>
+      </c>
+      <c r="P289" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16">
+      <c r="A290" s="1">
+        <v>0</v>
+      </c>
+      <c r="B290" t="s">
+        <v>55</v>
+      </c>
+      <c r="C290">
+        <v>13.06652891544442</v>
+      </c>
+      <c r="D290" t="s">
+        <v>107</v>
+      </c>
+      <c r="E290">
+        <v>12.63328393636026</v>
+      </c>
+      <c r="F290">
+        <v>-1</v>
+      </c>
+      <c r="G290">
+        <v>0.03743347108455558</v>
+      </c>
+      <c r="H290">
+        <v>0.03664671606363974</v>
+      </c>
+      <c r="I290">
+        <v>0.433244979084165</v>
+      </c>
+      <c r="J290">
+        <v>0.6312679318422579</v>
+      </c>
+      <c r="K290">
+        <v>19.3</v>
+      </c>
+      <c r="L290">
+        <v>25.25</v>
+      </c>
+      <c r="M290">
+        <v>19.02</v>
+      </c>
+      <c r="N290">
+        <v>24.64</v>
+      </c>
+      <c r="O290">
+        <v>1</v>
+      </c>
+      <c r="P290" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16">
+      <c r="A291" s="1">
+        <v>0</v>
+      </c>
+      <c r="B291" t="s">
+        <v>55</v>
+      </c>
+      <c r="C291">
+        <v>12.7241137365128</v>
+      </c>
+      <c r="D291" t="s">
+        <v>107</v>
+      </c>
+      <c r="E291">
+        <v>12.29583643878101</v>
+      </c>
+      <c r="F291">
+        <v>-1</v>
+      </c>
+      <c r="G291">
+        <v>0.03777588626348719</v>
+      </c>
+      <c r="H291">
+        <v>0.036984163561219</v>
+      </c>
+      <c r="I291">
+        <v>0.4282772977317908</v>
+      </c>
+      <c r="J291">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K291">
+        <v>19.3</v>
+      </c>
+      <c r="L291">
+        <v>25.25</v>
+      </c>
+      <c r="M291">
+        <v>19.02</v>
+      </c>
+      <c r="N291">
+        <v>24.64</v>
+      </c>
+      <c r="O291">
+        <v>1</v>
+      </c>
+      <c r="P291" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -334,10 +334,10 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
+    <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-23</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15216,7 +15216,7 @@
         <v>106</v>
       </c>
       <c r="E284">
-        <v>19.21190627946725</v>
+        <v>19.49746116193226</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -15225,10 +15225,10 @@
         <v>0.02686166962975171</v>
       </c>
       <c r="H284">
-        <v>0.02832809372053275</v>
+        <v>0.02870253883806774</v>
       </c>
       <c r="I284">
-        <v>0.8935759092189635</v>
+        <v>1.179130791683974</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15240,10 +15240,10 @@
         <v>22.59</v>
       </c>
       <c r="M284">
-        <v>18.46</v>
+        <v>18.64</v>
       </c>
       <c r="N284">
-        <v>23.77</v>
+        <v>24.1</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15266,7 +15266,7 @@
         <v>107</v>
       </c>
       <c r="E285">
-        <v>19.94363258046951</v>
+        <v>19.61511226704287</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15275,10 +15275,10 @@
         <v>0.03001550426902936</v>
       </c>
       <c r="H285">
-        <v>0.02933636741953049</v>
+        <v>0.02924488773295713</v>
       </c>
       <c r="I285">
-        <v>0.5408631505011279</v>
+        <v>0.8693834639277647</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15290,10 +15290,10 @@
         <v>25.25</v>
       </c>
       <c r="M285">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N285">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15316,7 +15316,7 @@
         <v>107</v>
       </c>
       <c r="E286">
-        <v>15.88846131106265</v>
+        <v>15.45760229052164</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15325,10 +15325,10 @@
         <v>0.03413037311758627</v>
       </c>
       <c r="H286">
-        <v>0.03339153868893735</v>
+        <v>0.03340239770947836</v>
       </c>
       <c r="I286">
-        <v>0.4811655713510792</v>
+        <v>0.9120245918920862</v>
       </c>
       <c r="J286">
         <v>0.4601229594604285</v>
@@ -15340,10 +15340,10 @@
         <v>25.25</v>
       </c>
       <c r="M286">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N286">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         <v>107</v>
       </c>
       <c r="E287">
-        <v>15.35935474882351</v>
+        <v>14.91514288128593</v>
       </c>
       <c r="F287">
         <v>-1</v>
@@ -15375,10 +15375,10 @@
         <v>0.03466726884057342</v>
       </c>
       <c r="H287">
-        <v>0.0339206452511765</v>
+        <v>0.03394485711871407</v>
       </c>
       <c r="I287">
-        <v>0.4733764106030787</v>
+        <v>0.9175882781406575</v>
       </c>
       <c r="J287">
         <v>0.4879413907032856</v>
@@ -15390,10 +15390,10 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N287">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15416,7 +15416,7 @@
         <v>107</v>
       </c>
       <c r="E288">
-        <v>14.86949510954896</v>
+        <v>14.41292085363852</v>
       </c>
       <c r="F288">
         <v>-1</v>
@@ -15425,10 +15425,10 @@
         <v>0.03516433987306546</v>
       </c>
       <c r="H288">
-        <v>0.03441050489045105</v>
+        <v>0.03444707914636148</v>
       </c>
       <c r="I288">
-        <v>0.4661650173855776</v>
+        <v>0.9227392732960151</v>
       </c>
       <c r="J288">
         <v>0.513696366480076</v>
@@ -15440,10 +15440,10 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N288">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15466,7 +15466,7 @@
         <v>107</v>
       </c>
       <c r="E289">
-        <v>14.43367128892445</v>
+        <v>13.96609832460708</v>
       </c>
       <c r="F289">
         <v>-1</v>
@@ -15475,10 +15475,10 @@
         <v>0.03560657960692735</v>
       </c>
       <c r="H289">
-        <v>0.03484632871107556</v>
+        <v>0.03489390167539292</v>
       </c>
       <c r="I289">
-        <v>0.4597491041482034</v>
+        <v>0.9273220684655676</v>
       </c>
       <c r="J289">
         <v>0.536610342327842</v>
@@ -15490,10 +15490,10 @@
         <v>25.25</v>
       </c>
       <c r="M289">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N289">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15516,7 +15516,7 @@
         <v>107</v>
       </c>
       <c r="E290">
-        <v>12.63328393636026</v>
+        <v>12.12027532907597</v>
       </c>
       <c r="F290">
         <v>-1</v>
@@ -15525,10 +15525,10 @@
         <v>0.03743347108455558</v>
       </c>
       <c r="H290">
-        <v>0.03664671606363974</v>
+        <v>0.03673972467092403</v>
       </c>
       <c r="I290">
-        <v>0.433244979084165</v>
+        <v>0.9462535863684511</v>
       </c>
       <c r="J290">
         <v>0.6312679318422579</v>
@@ -15540,10 +15540,10 @@
         <v>25.25</v>
       </c>
       <c r="M290">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N290">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O290">
         <v>1</v>
@@ -15566,7 +15566,7 @@
         <v>107</v>
       </c>
       <c r="E291">
-        <v>12.29583643878101</v>
+        <v>11.77431180632123</v>
       </c>
       <c r="F291">
         <v>-1</v>
@@ -15575,10 +15575,10 @@
         <v>0.03777588626348719</v>
       </c>
       <c r="H291">
-        <v>0.036984163561219</v>
+        <v>0.03708568819367878</v>
       </c>
       <c r="I291">
-        <v>0.4282772977317908</v>
+        <v>0.9498019301915761</v>
       </c>
       <c r="J291">
         <v>0.6490096509578859</v>
@@ -15590,10 +15590,10 @@
         <v>25.25</v>
       </c>
       <c r="M291">
-        <v>19.02</v>
+        <v>19.5</v>
       </c>
       <c r="N291">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="O291">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
   <si>
     <t>trade_time</t>
   </si>
@@ -337,7 +337,13 @@
     <t>2021-08-13</t>
   </si>
   <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
     <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -1149,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1199,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1249,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1299,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1349,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1399,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1449,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1499,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1549,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1599,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1649,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1699,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1749,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1799,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1849,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1899,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1949,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1999,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2049,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2099,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2149,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2199,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2249,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2299,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2349,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2399,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2449,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2499,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2549,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2599,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2649,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2699,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2749,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2799,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2849,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2899,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2949,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2999,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3049,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3099,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3149,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3199,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3249,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3299,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3349,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3399,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3449,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3499,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3549,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3599,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3649,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3699,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3749,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3799,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3849,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3899,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3949,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3999,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4049,7 +4055,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4099,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4149,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4199,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4249,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4299,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4349,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4399,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4449,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4499,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4549,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4599,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4649,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4699,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4749,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4799,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4849,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4899,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4949,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4999,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5049,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5099,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5149,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5199,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5249,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5299,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5349,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5399,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5449,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5499,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5549,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5599,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5649,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5699,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5749,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5799,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5849,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5899,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5949,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5999,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6049,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6099,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6149,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6199,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6249,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6299,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6349,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6399,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6449,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6499,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6549,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6599,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6649,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6699,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6749,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6799,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6849,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6899,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6949,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6999,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7049,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7099,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7149,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7199,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7249,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7299,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7349,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7399,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7449,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7499,7 +7505,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7549,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7599,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7649,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7699,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7749,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7799,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7849,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7899,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7949,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7999,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8049,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8099,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8149,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8199,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8249,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8299,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8349,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8399,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8449,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8499,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8549,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8599,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8649,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8699,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8749,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8799,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8849,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8899,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9149,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9199,7 +9205,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9249,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9299,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9349,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9399,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9449,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9499,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9549,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9599,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9649,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9699,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9749,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9799,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9849,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9899,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9949,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9999,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10049,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10099,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10149,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10199,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10249,7 +10255,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10299,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10349,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10399,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10449,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10499,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10549,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10599,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10649,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10699,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10749,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10799,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10849,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10899,7 +10905,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10949,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10999,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11049,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11099,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11149,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11199,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11249,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11299,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11349,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11399,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11449,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11499,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11549,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11599,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11649,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11699,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11749,7 +11755,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11799,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11849,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11899,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11949,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11999,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12049,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12099,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12149,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12199,7 +12205,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12249,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12299,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12349,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12399,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12449,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12499,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12549,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12599,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12649,7 +12655,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12699,7 +12705,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12749,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12799,7 +12805,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12849,7 +12855,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12899,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12949,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12999,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13049,7 +13055,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13099,7 +13105,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13149,7 +13155,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13199,7 +13205,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13249,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13299,7 +13305,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13349,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13399,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13449,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13499,7 +13505,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13549,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13599,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13649,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13699,7 +13705,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13749,7 +13755,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13799,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13999,7 +14005,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14049,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14099,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14149,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14199,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14249,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14299,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14349,7 +14355,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14399,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14449,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14499,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14549,7 +14555,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14749,7 +14755,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14949,7 +14955,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14999,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15049,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15149,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15199,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15249,7 +15255,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15266,7 +15272,7 @@
         <v>107</v>
       </c>
       <c r="E285">
-        <v>19.61511226704287</v>
+        <v>20.2362220319729</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15275,10 +15281,10 @@
         <v>0.03001550426902936</v>
       </c>
       <c r="H285">
-        <v>0.02924488773295713</v>
+        <v>0.0300437779680271</v>
       </c>
       <c r="I285">
-        <v>0.8693834639277647</v>
+        <v>0.2482736989977425</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15290,16 +15296,16 @@
         <v>25.25</v>
       </c>
       <c r="M285">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="N285">
-        <v>24.43</v>
+        <v>25.14</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15316,7 +15322,7 @@
         <v>107</v>
       </c>
       <c r="E286">
-        <v>15.45760229052164</v>
+        <v>16.00195802511589</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15325,10 +15331,10 @@
         <v>0.03413037311758627</v>
       </c>
       <c r="H286">
-        <v>0.03340239770947836</v>
+        <v>0.03427804197488411</v>
       </c>
       <c r="I286">
-        <v>0.9120245918920862</v>
+        <v>0.3676688572978399</v>
       </c>
       <c r="J286">
         <v>0.4601229594604285</v>
@@ -15340,16 +15346,16 @@
         <v>25.25</v>
       </c>
       <c r="M286">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="N286">
-        <v>24.43</v>
+        <v>25.14</v>
       </c>
       <c r="O286">
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15366,7 +15372,7 @@
         <v>107</v>
       </c>
       <c r="E287">
-        <v>14.91514288128593</v>
+        <v>15.44948398063275</v>
       </c>
       <c r="F287">
         <v>-1</v>
@@ -15375,10 +15381,10 @@
         <v>0.03466726884057342</v>
       </c>
       <c r="H287">
-        <v>0.03394485711871407</v>
+        <v>0.03483051601936725</v>
       </c>
       <c r="I287">
-        <v>0.9175882781406575</v>
+        <v>0.3832471787938392</v>
       </c>
       <c r="J287">
         <v>0.4879413907032856</v>
@@ -15390,16 +15396,16 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="N287">
-        <v>24.43</v>
+        <v>25.14</v>
       </c>
       <c r="O287">
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15416,7 +15422,7 @@
         <v>107</v>
       </c>
       <c r="E288">
-        <v>14.41292085363852</v>
+        <v>14.93799016170569</v>
       </c>
       <c r="F288">
         <v>-1</v>
@@ -15425,10 +15431,10 @@
         <v>0.03516433987306546</v>
       </c>
       <c r="H288">
-        <v>0.03444707914636148</v>
+        <v>0.03534200983829431</v>
       </c>
       <c r="I288">
-        <v>0.9227392732960151</v>
+        <v>0.3976699652288413</v>
       </c>
       <c r="J288">
         <v>0.513696366480076</v>
@@ -15440,16 +15446,16 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="N288">
-        <v>24.43</v>
+        <v>25.14</v>
       </c>
       <c r="O288">
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15466,7 +15472,7 @@
         <v>107</v>
       </c>
       <c r="E289">
-        <v>13.96609832460708</v>
+        <v>14.48291860136906</v>
       </c>
       <c r="F289">
         <v>-1</v>
@@ -15475,10 +15481,10 @@
         <v>0.03560657960692735</v>
       </c>
       <c r="H289">
-        <v>0.03489390167539292</v>
+        <v>0.03579708139863094</v>
       </c>
       <c r="I289">
-        <v>0.9273220684655676</v>
+        <v>0.4105017917035898</v>
       </c>
       <c r="J289">
         <v>0.536610342327842</v>
@@ -15490,16 +15496,16 @@
         <v>25.25</v>
       </c>
       <c r="M289">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="N289">
-        <v>24.43</v>
+        <v>25.14</v>
       </c>
       <c r="O289">
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15513,7 +15519,7 @@
         <v>13.06652891544442</v>
       </c>
       <c r="D290" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E290">
         <v>12.12027532907597</v>
@@ -15563,10 +15569,10 @@
         <v>12.7241137365128</v>
       </c>
       <c r="D291" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E291">
-        <v>11.77431180632123</v>
+        <v>11.83093547368522</v>
       </c>
       <c r="F291">
         <v>-1</v>
@@ -15575,10 +15581,10 @@
         <v>0.03777588626348719</v>
       </c>
       <c r="H291">
-        <v>0.03708568819367878</v>
+        <v>0.03664906452631477</v>
       </c>
       <c r="I291">
-        <v>0.9498019301915761</v>
+        <v>0.8931782628275826</v>
       </c>
       <c r="J291">
         <v>0.6490096509578859</v>
@@ -15590,16 +15596,16 @@
         <v>25.25</v>
       </c>
       <c r="M291">
-        <v>19.5</v>
+        <v>19.12</v>
       </c>
       <c r="N291">
-        <v>24.43</v>
+        <v>24.24</v>
       </c>
       <c r="O291">
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="230">
   <si>
     <t>trade_time</t>
   </si>
@@ -184,6 +184,9 @@
     <t>2021-08-18</t>
   </si>
   <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -337,7 +340,7 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-24</t>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2021-08-23</t>
@@ -1058,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P291"/>
+  <dimension ref="A1:P292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1119,7 +1122,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1155,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1169,7 +1172,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1205,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1219,7 +1222,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1255,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1269,7 +1272,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1305,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1319,7 +1322,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1355,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1369,7 +1372,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1405,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1419,7 +1422,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1455,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1469,7 +1472,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1505,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1519,7 +1522,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1555,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1569,7 +1572,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1605,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1619,7 +1622,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1655,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1669,7 +1672,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1705,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1719,7 +1722,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1755,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1769,7 +1772,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1805,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1819,7 +1822,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1855,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1869,7 +1872,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1905,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1919,7 +1922,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1955,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1969,7 +1972,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2005,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2019,7 +2022,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2055,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2069,7 +2072,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2105,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2119,7 +2122,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2155,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2169,7 +2172,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2205,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2219,7 +2222,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2255,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2269,7 +2272,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2305,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2319,7 +2322,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2355,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2369,7 +2372,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2405,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2419,7 +2422,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2455,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2469,7 +2472,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2505,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2519,7 +2522,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2555,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2569,7 +2572,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2605,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2655,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2669,7 +2672,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2705,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2755,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2805,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2819,7 +2822,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2855,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2869,7 +2872,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2905,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2919,7 +2922,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2955,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2969,7 +2972,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3005,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3019,7 +3022,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3055,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3069,7 +3072,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3105,7 +3108,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3119,7 +3122,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3155,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3169,7 +3172,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3205,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3219,7 +3222,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3255,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3269,7 +3272,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3305,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3319,7 +3322,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3355,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3369,7 +3372,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3405,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3419,7 +3422,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3455,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3469,7 +3472,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3505,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3519,7 +3522,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3555,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3569,7 +3572,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3605,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3619,7 +3622,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3655,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3705,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3755,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3769,7 +3772,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3805,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3855,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3905,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3919,7 +3922,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3955,7 +3958,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4005,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4055,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4069,7 +4072,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4105,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4155,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4169,7 +4172,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4205,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4255,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4269,7 +4272,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4305,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4355,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4369,7 +4372,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4405,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4455,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4469,7 +4472,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4505,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4555,7 +4558,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4569,7 +4572,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4605,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4619,7 +4622,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4655,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4705,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4719,7 +4722,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4755,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4769,7 +4772,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4805,7 +4808,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4855,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4869,7 +4872,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4905,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4919,7 +4922,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4955,7 +4958,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5005,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5019,7 +5022,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5055,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5069,7 +5072,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5105,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5155,7 +5158,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5169,7 +5172,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5205,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5219,7 +5222,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5255,7 +5258,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5305,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5319,7 +5322,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5355,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5369,7 +5372,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5405,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5455,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5469,7 +5472,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5505,7 +5508,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5519,7 +5522,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5555,7 +5558,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5605,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5619,7 +5622,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5655,7 +5658,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5669,7 +5672,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5705,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5755,7 +5758,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5769,7 +5772,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5805,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5819,7 +5822,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5855,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5869,7 +5872,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5905,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5919,7 +5922,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5955,7 +5958,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5969,7 +5972,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6005,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6019,7 +6022,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6055,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6069,7 +6072,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6105,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6119,7 +6122,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6155,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6169,7 +6172,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6205,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6219,7 +6222,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6255,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6269,7 +6272,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6305,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6319,7 +6322,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6355,7 +6358,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6369,7 +6372,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6405,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6419,7 +6422,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6455,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6469,7 +6472,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6505,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6519,7 +6522,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6555,7 +6558,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6569,7 +6572,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6605,7 +6608,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6619,7 +6622,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6655,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6669,7 +6672,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6705,7 +6708,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6719,7 +6722,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6755,7 +6758,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6769,7 +6772,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6805,7 +6808,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6819,7 +6822,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6855,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6869,7 +6872,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6905,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6919,7 +6922,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6955,7 +6958,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6969,7 +6972,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7005,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7019,7 +7022,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7055,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7069,7 +7072,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7105,7 +7108,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7119,7 +7122,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7155,7 +7158,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7169,7 +7172,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7205,7 +7208,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7219,7 +7222,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7255,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7269,7 +7272,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7305,7 +7308,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7319,7 +7322,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7355,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7369,7 +7372,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7405,7 +7408,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7419,7 +7422,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7455,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7469,7 +7472,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7505,7 +7508,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7519,7 +7522,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7555,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7569,7 +7572,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7605,7 +7608,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7619,7 +7622,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7655,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7669,7 +7672,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7705,7 +7708,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7719,7 +7722,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7755,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7769,7 +7772,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7805,7 +7808,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7819,7 +7822,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7855,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7869,7 +7872,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7905,7 +7908,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7919,7 +7922,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7955,7 +7958,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7969,7 +7972,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8005,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8019,7 +8022,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8055,7 +8058,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8069,7 +8072,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8105,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8119,7 +8122,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8155,7 +8158,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8169,7 +8172,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8205,7 +8208,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8219,7 +8222,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8255,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8269,7 +8272,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8305,7 +8308,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8319,7 +8322,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8355,7 +8358,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8369,7 +8372,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8405,7 +8408,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8419,7 +8422,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8455,7 +8458,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8469,7 +8472,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8505,7 +8508,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8519,7 +8522,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8555,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8569,7 +8572,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8605,7 +8608,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8619,7 +8622,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8655,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8669,7 +8672,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8705,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8719,7 +8722,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8755,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8769,7 +8772,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8805,7 +8808,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8819,7 +8822,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8855,7 +8858,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8869,7 +8872,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8905,7 +8908,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8919,7 +8922,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8969,7 +8972,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -9005,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9019,7 +9022,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9055,7 +9058,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9069,7 +9072,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9105,7 +9108,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9119,7 +9122,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9155,7 +9158,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9169,7 +9172,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9205,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9219,7 +9222,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9255,7 +9258,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9269,7 +9272,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9305,7 +9308,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9319,7 +9322,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9355,7 +9358,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9369,7 +9372,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9405,7 +9408,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9419,7 +9422,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9455,7 +9458,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9469,7 +9472,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9505,7 +9508,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9519,7 +9522,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9555,7 +9558,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9569,7 +9572,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9605,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9619,7 +9622,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9655,7 +9658,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9669,7 +9672,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9705,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9719,7 +9722,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9755,7 +9758,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9769,7 +9772,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9805,7 +9808,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9819,7 +9822,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9855,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9869,7 +9872,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9905,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9919,7 +9922,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9955,7 +9958,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9969,7 +9972,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10005,7 +10008,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10019,7 +10022,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10055,7 +10058,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10069,7 +10072,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10105,7 +10108,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10119,7 +10122,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10155,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10169,7 +10172,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10205,7 +10208,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10219,7 +10222,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10255,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10269,7 +10272,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10305,7 +10308,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10319,7 +10322,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10355,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10369,7 +10372,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10405,7 +10408,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10419,7 +10422,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10455,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10469,7 +10472,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10505,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10519,7 +10522,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10555,7 +10558,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10569,7 +10572,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10605,7 +10608,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10619,7 +10622,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10655,7 +10658,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10669,7 +10672,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10705,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10719,7 +10722,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10755,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10769,7 +10772,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10805,7 +10808,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10855,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10905,7 +10908,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10919,7 +10922,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10955,7 +10958,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11005,7 +11008,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11055,7 +11058,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11069,7 +11072,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11105,7 +11108,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11155,7 +11158,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11205,7 +11208,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11219,7 +11222,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11255,7 +11258,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11305,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11319,7 +11322,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11355,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11369,7 +11372,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11405,7 +11408,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11455,7 +11458,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11469,7 +11472,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11505,7 +11508,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11519,7 +11522,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11555,7 +11558,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11605,7 +11608,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11619,7 +11622,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11655,7 +11658,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11669,7 +11672,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11705,7 +11708,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11755,7 +11758,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11769,7 +11772,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11805,7 +11808,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11819,7 +11822,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11855,7 +11858,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11905,7 +11908,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11919,7 +11922,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11955,7 +11958,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11969,7 +11972,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12005,7 +12008,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12055,7 +12058,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12069,7 +12072,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12105,7 +12108,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12119,7 +12122,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12155,7 +12158,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12205,7 +12208,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12219,7 +12222,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12255,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12269,7 +12272,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12305,7 +12308,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12355,7 +12358,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12369,7 +12372,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12405,7 +12408,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12455,7 +12458,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12469,7 +12472,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12505,7 +12508,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12555,7 +12558,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12569,7 +12572,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12605,7 +12608,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12655,7 +12658,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12669,7 +12672,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12705,7 +12708,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12755,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12769,7 +12772,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12805,7 +12808,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12855,7 +12858,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12905,7 +12908,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12919,7 +12922,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12955,7 +12958,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12969,7 +12972,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13005,7 +13008,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13019,7 +13022,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13055,7 +13058,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13069,7 +13072,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13105,7 +13108,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13119,7 +13122,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13155,7 +13158,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13169,7 +13172,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13205,7 +13208,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13219,7 +13222,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13255,7 +13258,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13269,7 +13272,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13305,7 +13308,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13319,7 +13322,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13355,7 +13358,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13369,7 +13372,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13405,7 +13408,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13419,7 +13422,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13455,7 +13458,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13469,7 +13472,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13505,7 +13508,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13519,7 +13522,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13555,7 +13558,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13569,7 +13572,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13605,7 +13608,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13619,7 +13622,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13655,7 +13658,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13669,7 +13672,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13705,7 +13708,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13719,7 +13722,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13755,7 +13758,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13769,7 +13772,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13805,7 +13808,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13819,7 +13822,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13869,7 +13872,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13919,7 +13922,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13969,7 +13972,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14005,7 +14008,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14019,7 +14022,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14055,7 +14058,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14069,7 +14072,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14105,7 +14108,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14119,7 +14122,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14155,7 +14158,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14169,7 +14172,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14205,7 +14208,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14219,7 +14222,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14255,7 +14258,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14269,7 +14272,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14305,7 +14308,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14319,7 +14322,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14355,7 +14358,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14369,7 +14372,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14405,7 +14408,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14419,7 +14422,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14455,7 +14458,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14469,7 +14472,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14505,7 +14508,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14519,7 +14522,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14555,7 +14558,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14605,7 +14608,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14655,7 +14658,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14705,7 +14708,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14755,7 +14758,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14805,7 +14808,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14819,7 +14822,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14855,7 +14858,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14869,7 +14872,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14905,7 +14908,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14919,7 +14922,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14955,7 +14958,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14969,7 +14972,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15005,7 +15008,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15019,7 +15022,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15055,7 +15058,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15069,7 +15072,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15105,7 +15108,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15119,7 +15122,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15155,7 +15158,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15169,7 +15172,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15205,7 +15208,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15219,7 +15222,7 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E284">
         <v>19.49746116193226</v>
@@ -15255,7 +15258,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15269,10 +15272,10 @@
         <v>20.48449573097064</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E285">
-        <v>20.2362220319729</v>
+        <v>20.00634533918734</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15281,10 +15284,10 @@
         <v>0.03001550426902936</v>
       </c>
       <c r="H285">
-        <v>0.0300437779680271</v>
+        <v>0.02983365466081266</v>
       </c>
       <c r="I285">
-        <v>0.2482736989977425</v>
+        <v>0.478150391783295</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15296,60 +15299,60 @@
         <v>25.25</v>
       </c>
       <c r="M285">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="N285">
-        <v>25.14</v>
+        <v>24.92</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B286" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C286">
-        <v>16.36962688241373</v>
+        <v>20.2362220319729</v>
       </c>
       <c r="D286" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E286">
-        <v>16.00195802511589</v>
+        <v>20.00634533918734</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.03413037311758627</v>
+        <v>0.0300437779680271</v>
       </c>
       <c r="H286">
-        <v>0.03427804197488411</v>
+        <v>0.02983365466081266</v>
       </c>
       <c r="I286">
-        <v>0.3676688572978399</v>
+        <v>0.2298766927855525</v>
       </c>
       <c r="J286">
-        <v>0.4601229594604285</v>
+        <v>0.246917319638827</v>
       </c>
       <c r="K286">
-        <v>19.3</v>
+        <v>19.86</v>
       </c>
       <c r="L286">
-        <v>25.25</v>
+        <v>25.14</v>
       </c>
       <c r="M286">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="N286">
-        <v>25.14</v>
+        <v>24.92</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15366,28 +15369,28 @@
         <v>55</v>
       </c>
       <c r="C287">
-        <v>15.83273115942659</v>
+        <v>16.36962688241373</v>
       </c>
       <c r="D287" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E287">
-        <v>15.44948398063275</v>
+        <v>15.76355310673747</v>
       </c>
       <c r="F287">
         <v>-1</v>
       </c>
       <c r="G287">
-        <v>0.03466726884057342</v>
+        <v>0.03413037311758627</v>
       </c>
       <c r="H287">
-        <v>0.03483051601936725</v>
+        <v>0.03407644689326253</v>
       </c>
       <c r="I287">
-        <v>0.3832471787938392</v>
+        <v>0.606073775676256</v>
       </c>
       <c r="J287">
-        <v>0.4879413907032856</v>
+        <v>0.4601229594604285</v>
       </c>
       <c r="K287">
         <v>19.3</v>
@@ -15396,10 +15399,10 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="N287">
-        <v>25.14</v>
+        <v>24.92</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15416,28 +15419,28 @@
         <v>55</v>
       </c>
       <c r="C288">
-        <v>15.33566012693453</v>
+        <v>15.83273115942659</v>
       </c>
       <c r="D288" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E288">
-        <v>14.93799016170569</v>
+        <v>15.20996632500462</v>
       </c>
       <c r="F288">
         <v>-1</v>
       </c>
       <c r="G288">
-        <v>0.03516433987306546</v>
+        <v>0.03466726884057342</v>
       </c>
       <c r="H288">
-        <v>0.03534200983829431</v>
+        <v>0.03463003367499538</v>
       </c>
       <c r="I288">
-        <v>0.3976699652288413</v>
+        <v>0.6227648344219681</v>
       </c>
       <c r="J288">
-        <v>0.513696366480076</v>
+        <v>0.4879413907032856</v>
       </c>
       <c r="K288">
         <v>19.3</v>
@@ -15446,10 +15449,10 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="N288">
-        <v>25.14</v>
+        <v>24.92</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15466,28 +15469,28 @@
         <v>55</v>
       </c>
       <c r="C289">
-        <v>14.89342039307265</v>
+        <v>15.33566012693453</v>
       </c>
       <c r="D289" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E289">
-        <v>14.48291860136906</v>
+        <v>14.69744230704649</v>
       </c>
       <c r="F289">
         <v>-1</v>
       </c>
       <c r="G289">
-        <v>0.03560657960692735</v>
+        <v>0.03516433987306546</v>
       </c>
       <c r="H289">
-        <v>0.03579708139863094</v>
+        <v>0.03514255769295352</v>
       </c>
       <c r="I289">
-        <v>0.4105017917035898</v>
+        <v>0.6382178198880428</v>
       </c>
       <c r="J289">
-        <v>0.536610342327842</v>
+        <v>0.513696366480076</v>
       </c>
       <c r="K289">
         <v>19.3</v>
@@ -15496,10 +15499,10 @@
         <v>25.25</v>
       </c>
       <c r="M289">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="N289">
-        <v>25.14</v>
+        <v>24.92</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15516,28 +15519,28 @@
         <v>55</v>
       </c>
       <c r="C290">
-        <v>13.06652891544442</v>
+        <v>14.89342039307265</v>
       </c>
       <c r="D290" t="s">
         <v>108</v>
       </c>
       <c r="E290">
-        <v>12.12027532907597</v>
+        <v>14.24145418767595</v>
       </c>
       <c r="F290">
         <v>-1</v>
       </c>
       <c r="G290">
-        <v>0.03743347108455558</v>
+        <v>0.03560657960692735</v>
       </c>
       <c r="H290">
-        <v>0.03673972467092403</v>
+        <v>0.03559854581232406</v>
       </c>
       <c r="I290">
-        <v>0.9462535863684511</v>
+        <v>0.6519662053967021</v>
       </c>
       <c r="J290">
-        <v>0.6312679318422579</v>
+        <v>0.536610342327842</v>
       </c>
       <c r="K290">
         <v>19.3</v>
@@ -15546,16 +15549,16 @@
         <v>25.25</v>
       </c>
       <c r="M290">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="N290">
-        <v>24.43</v>
+        <v>24.92</v>
       </c>
       <c r="O290">
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>54</v>
+        <v>228</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15566,28 +15569,28 @@
         <v>55</v>
       </c>
       <c r="C291">
-        <v>12.7241137365128</v>
+        <v>13.06652891544442</v>
       </c>
       <c r="D291" t="s">
         <v>109</v>
       </c>
       <c r="E291">
-        <v>11.83093547368522</v>
+        <v>12.12027532907597</v>
       </c>
       <c r="F291">
         <v>-1</v>
       </c>
       <c r="G291">
-        <v>0.03777588626348719</v>
+        <v>0.03743347108455558</v>
       </c>
       <c r="H291">
-        <v>0.03664906452631477</v>
+        <v>0.03673972467092403</v>
       </c>
       <c r="I291">
-        <v>0.8931782628275826</v>
+        <v>0.9462535863684511</v>
       </c>
       <c r="J291">
-        <v>0.6490096509578859</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K291">
         <v>19.3</v>
@@ -15596,16 +15599,66 @@
         <v>25.25</v>
       </c>
       <c r="M291">
+        <v>19.5</v>
+      </c>
+      <c r="N291">
+        <v>24.43</v>
+      </c>
+      <c r="O291">
+        <v>1</v>
+      </c>
+      <c r="P291" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16">
+      <c r="A292" s="1">
+        <v>0</v>
+      </c>
+      <c r="B292" t="s">
+        <v>55</v>
+      </c>
+      <c r="C292">
+        <v>12.7241137365128</v>
+      </c>
+      <c r="D292" t="s">
+        <v>110</v>
+      </c>
+      <c r="E292">
+        <v>11.83093547368522</v>
+      </c>
+      <c r="F292">
+        <v>-1</v>
+      </c>
+      <c r="G292">
+        <v>0.03777588626348719</v>
+      </c>
+      <c r="H292">
+        <v>0.03664906452631477</v>
+      </c>
+      <c r="I292">
+        <v>0.8931782628275826</v>
+      </c>
+      <c r="J292">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K292">
+        <v>19.3</v>
+      </c>
+      <c r="L292">
+        <v>25.25</v>
+      </c>
+      <c r="M292">
         <v>19.12</v>
       </c>
-      <c r="N291">
+      <c r="N292">
         <v>24.24</v>
       </c>
-      <c r="O291">
-        <v>1</v>
-      </c>
-      <c r="P291" t="s">
-        <v>228</v>
+      <c r="O292">
+        <v>1</v>
+      </c>
+      <c r="P292" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -340,7 +340,7 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-25</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-08-23</t>
@@ -15275,7 +15275,7 @@
         <v>108</v>
       </c>
       <c r="E285">
-        <v>20.00634533918734</v>
+        <v>19.695975417544</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15284,10 +15284,10 @@
         <v>0.03001550426902936</v>
       </c>
       <c r="H285">
-        <v>0.02983365466081266</v>
+        <v>0.029464024582456</v>
       </c>
       <c r="I285">
-        <v>0.478150391783295</v>
+        <v>0.7885203134266412</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15299,10 +15299,10 @@
         <v>25.25</v>
       </c>
       <c r="M285">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N285">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15325,7 +15325,7 @@
         <v>108</v>
       </c>
       <c r="E286">
-        <v>20.00634533918734</v>
+        <v>19.695975417544</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15334,10 +15334,10 @@
         <v>0.0300437779680271</v>
       </c>
       <c r="H286">
-        <v>0.02983365466081266</v>
+        <v>0.029464024582456</v>
       </c>
       <c r="I286">
-        <v>0.2298766927855525</v>
+        <v>0.5402466144288987</v>
       </c>
       <c r="J286">
         <v>0.246917319638827</v>
@@ -15349,10 +15349,10 @@
         <v>25.14</v>
       </c>
       <c r="M286">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N286">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15375,7 +15375,7 @@
         <v>108</v>
       </c>
       <c r="E287">
-        <v>15.76355310673747</v>
+        <v>15.47876786187272</v>
       </c>
       <c r="F287">
         <v>-1</v>
@@ -15384,10 +15384,10 @@
         <v>0.03413037311758627</v>
       </c>
       <c r="H287">
-        <v>0.03407644689326253</v>
+        <v>0.03368123213812727</v>
       </c>
       <c r="I287">
-        <v>0.606073775676256</v>
+        <v>0.8908590205410079</v>
       </c>
       <c r="J287">
         <v>0.4601229594604285</v>
@@ -15399,10 +15399,10 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N287">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15425,7 +15425,7 @@
         <v>108</v>
       </c>
       <c r="E288">
-        <v>15.20996632500462</v>
+        <v>14.92851929188901</v>
       </c>
       <c r="F288">
         <v>-1</v>
@@ -15434,10 +15434,10 @@
         <v>0.03466726884057342</v>
       </c>
       <c r="H288">
-        <v>0.03463003367499538</v>
+        <v>0.03423148070811099</v>
       </c>
       <c r="I288">
-        <v>0.6227648344219681</v>
+        <v>0.9042118675375796</v>
       </c>
       <c r="J288">
         <v>0.4879413907032856</v>
@@ -15449,10 +15449,10 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N288">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15475,7 +15475,7 @@
         <v>108</v>
       </c>
       <c r="E289">
-        <v>14.69744230704649</v>
+        <v>14.41908587102409</v>
       </c>
       <c r="F289">
         <v>-1</v>
@@ -15484,10 +15484,10 @@
         <v>0.03516433987306546</v>
       </c>
       <c r="H289">
-        <v>0.03514255769295352</v>
+        <v>0.0347409141289759</v>
       </c>
       <c r="I289">
-        <v>0.6382178198880428</v>
+        <v>0.9165742559104384</v>
       </c>
       <c r="J289">
         <v>0.513696366480076</v>
@@ -15499,10 +15499,10 @@
         <v>25.25</v>
       </c>
       <c r="M289">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N289">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15525,7 +15525,7 @@
         <v>108</v>
       </c>
       <c r="E290">
-        <v>14.24145418767595</v>
+        <v>13.96584742875528</v>
       </c>
       <c r="F290">
         <v>-1</v>
@@ -15534,10 +15534,10 @@
         <v>0.03560657960692735</v>
       </c>
       <c r="H290">
-        <v>0.03559854581232406</v>
+        <v>0.03519415257124472</v>
       </c>
       <c r="I290">
-        <v>0.6519662053967021</v>
+        <v>0.9275729643173651</v>
       </c>
       <c r="J290">
         <v>0.536610342327842</v>
@@ -15549,10 +15549,10 @@
         <v>25.25</v>
       </c>
       <c r="M290">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="N290">
-        <v>24.92</v>
+        <v>24.58</v>
       </c>
       <c r="O290">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
   <si>
     <t>trade_time</t>
   </si>
@@ -184,9 +184,6 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -340,7 +337,7 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-26</t>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2021-08-23</t>
@@ -1061,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P292"/>
+  <dimension ref="A1:P291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1122,7 +1119,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1158,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1172,7 +1169,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1208,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1222,7 +1219,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1258,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1272,7 +1269,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1308,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1322,7 +1319,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1358,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1372,7 +1369,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1408,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1422,7 +1419,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1458,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1472,7 +1469,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1508,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1522,7 +1519,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1558,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1572,7 +1569,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1608,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1622,7 +1619,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1658,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1672,7 +1669,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1708,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1722,7 +1719,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1758,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1772,7 +1769,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1808,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1822,7 +1819,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1858,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1872,7 +1869,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1908,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1922,7 +1919,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1958,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1972,7 +1969,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2008,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2022,7 +2019,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2058,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2072,7 +2069,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2108,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2122,7 +2119,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2158,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2172,7 +2169,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2208,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2222,7 +2219,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2258,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2272,7 +2269,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2308,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2322,7 +2319,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2358,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2372,7 +2369,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2408,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2422,7 +2419,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2458,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2472,7 +2469,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2508,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2522,7 +2519,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2558,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2572,7 +2569,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2608,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2658,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2672,7 +2669,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2708,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2758,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2808,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2822,7 +2819,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2858,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2872,7 +2869,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2908,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2922,7 +2919,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2958,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2972,7 +2969,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3008,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3022,7 +3019,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3058,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3072,7 +3069,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3108,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3122,7 +3119,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3158,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3172,7 +3169,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3208,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3222,7 +3219,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3258,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3272,7 +3269,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3308,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3322,7 +3319,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3358,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3372,7 +3369,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3408,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3422,7 +3419,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3458,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3472,7 +3469,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3508,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3522,7 +3519,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3558,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3572,7 +3569,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3608,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3622,7 +3619,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3658,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3708,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3758,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3772,7 +3769,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3808,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3858,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3908,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3922,7 +3919,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3958,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4008,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4058,7 +4055,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4072,7 +4069,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4108,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4158,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4172,7 +4169,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4208,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4258,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4272,7 +4269,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4308,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4358,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4372,7 +4369,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4408,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4458,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4472,7 +4469,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4508,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4558,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4572,7 +4569,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4608,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4622,7 +4619,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4658,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4708,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4722,7 +4719,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4758,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4772,7 +4769,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4808,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4858,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4872,7 +4869,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4908,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4922,7 +4919,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4958,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5008,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5022,7 +5019,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5058,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5072,7 +5069,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5108,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5158,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5172,7 +5169,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5208,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5222,7 +5219,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5258,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5308,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5322,7 +5319,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5358,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5372,7 +5369,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5408,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5458,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5472,7 +5469,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5508,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5522,7 +5519,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5558,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5608,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5622,7 +5619,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5658,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5672,7 +5669,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5708,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5758,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5772,7 +5769,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5808,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5822,7 +5819,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5858,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5872,7 +5869,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5908,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5922,7 +5919,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5958,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5972,7 +5969,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6008,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6022,7 +6019,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6058,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6072,7 +6069,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6108,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6122,7 +6119,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6158,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6172,7 +6169,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6208,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6222,7 +6219,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6258,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6272,7 +6269,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6308,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6322,7 +6319,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6358,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6372,7 +6369,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6408,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6422,7 +6419,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6458,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6472,7 +6469,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6508,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6522,7 +6519,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6558,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6572,7 +6569,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6608,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6622,7 +6619,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6658,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6672,7 +6669,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6708,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6722,7 +6719,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6758,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6772,7 +6769,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6808,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6822,7 +6819,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6858,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6872,7 +6869,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6908,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6922,7 +6919,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6958,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6972,7 +6969,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7008,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7022,7 +7019,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7058,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7072,7 +7069,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7108,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7122,7 +7119,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7158,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7172,7 +7169,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7208,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7222,7 +7219,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7258,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7272,7 +7269,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7308,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7322,7 +7319,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7358,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7372,7 +7369,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7408,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7422,7 +7419,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7458,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7472,7 +7469,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7508,7 +7505,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7522,7 +7519,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7558,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7572,7 +7569,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7608,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7622,7 +7619,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7658,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7672,7 +7669,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7708,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7722,7 +7719,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7758,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7772,7 +7769,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7808,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7822,7 +7819,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7858,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7872,7 +7869,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7908,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7922,7 +7919,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7958,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7972,7 +7969,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8008,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8022,7 +8019,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8058,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8072,7 +8069,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8108,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8122,7 +8119,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8158,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8172,7 +8169,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8208,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8222,7 +8219,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8258,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8272,7 +8269,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8308,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8322,7 +8319,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8358,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8372,7 +8369,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8408,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8422,7 +8419,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8458,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8472,7 +8469,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8508,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8522,7 +8519,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8558,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8572,7 +8569,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8608,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8622,7 +8619,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8658,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8672,7 +8669,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8708,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8722,7 +8719,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8758,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8772,7 +8769,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8808,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8822,7 +8819,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8858,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8872,7 +8869,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8908,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8922,7 +8919,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8972,7 +8969,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -9008,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9022,7 +9019,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9058,7 +9055,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9072,7 +9069,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9108,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9122,7 +9119,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9158,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9172,7 +9169,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9208,7 +9205,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9222,7 +9219,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9258,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9272,7 +9269,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9308,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9322,7 +9319,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9358,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9372,7 +9369,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9408,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9422,7 +9419,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9458,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9472,7 +9469,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9508,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9522,7 +9519,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9558,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9572,7 +9569,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9608,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9622,7 +9619,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9658,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9672,7 +9669,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9708,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9722,7 +9719,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9758,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9772,7 +9769,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9808,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9822,7 +9819,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9858,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9872,7 +9869,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9908,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9922,7 +9919,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9958,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9972,7 +9969,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10008,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10022,7 +10019,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10058,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10072,7 +10069,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10108,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10122,7 +10119,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10158,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10172,7 +10169,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10208,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10222,7 +10219,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10258,7 +10255,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10272,7 +10269,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10308,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10322,7 +10319,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10358,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10372,7 +10369,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10408,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10422,7 +10419,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10458,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10472,7 +10469,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10508,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10522,7 +10519,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10558,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10572,7 +10569,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10608,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10622,7 +10619,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10658,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10672,7 +10669,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10708,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10722,7 +10719,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10758,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10772,7 +10769,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10808,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10858,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10908,7 +10905,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10922,7 +10919,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10958,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11008,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11058,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11072,7 +11069,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11108,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11158,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11208,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11222,7 +11219,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11258,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11308,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11322,7 +11319,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11358,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11372,7 +11369,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11408,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11458,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11472,7 +11469,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11508,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11522,7 +11519,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11558,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11608,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11622,7 +11619,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11658,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11672,7 +11669,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11708,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11758,7 +11755,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11772,7 +11769,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11808,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11822,7 +11819,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11858,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11908,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11922,7 +11919,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11958,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11972,7 +11969,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12008,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12058,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12072,7 +12069,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12108,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12122,7 +12119,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12158,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12208,7 +12205,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12222,7 +12219,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12258,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12272,7 +12269,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12308,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12358,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12372,7 +12369,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12408,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12458,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12472,7 +12469,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12508,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12558,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12572,7 +12569,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12608,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12658,7 +12655,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12672,7 +12669,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12708,7 +12705,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12758,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12772,7 +12769,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12808,7 +12805,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12858,7 +12855,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12908,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12922,7 +12919,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12958,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12972,7 +12969,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13008,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13022,7 +13019,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13058,7 +13055,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13072,7 +13069,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13108,7 +13105,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13122,7 +13119,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13158,7 +13155,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13172,7 +13169,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13208,7 +13205,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13222,7 +13219,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13258,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13272,7 +13269,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13308,7 +13305,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13322,7 +13319,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13358,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13372,7 +13369,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13408,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13422,7 +13419,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13458,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13472,7 +13469,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13508,7 +13505,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13522,7 +13519,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13558,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13572,7 +13569,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13608,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13622,7 +13619,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13658,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13672,7 +13669,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13708,7 +13705,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13722,7 +13719,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13758,7 +13755,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13772,7 +13769,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13808,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13822,7 +13819,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13872,7 +13869,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13922,7 +13919,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13972,7 +13969,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14008,7 +14005,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14022,7 +14019,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14058,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14072,7 +14069,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14108,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14122,7 +14119,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14158,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14172,7 +14169,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14208,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14222,7 +14219,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14258,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14272,7 +14269,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14308,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14322,7 +14319,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14358,7 +14355,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14372,7 +14369,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14408,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14422,7 +14419,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14458,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14472,7 +14469,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14508,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14522,7 +14519,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14558,7 +14555,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14608,7 +14605,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14658,7 +14655,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14708,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14758,7 +14755,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14808,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14822,7 +14819,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14858,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14872,7 +14869,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14908,7 +14905,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14922,7 +14919,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14958,7 +14955,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14972,7 +14969,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15008,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15022,7 +15019,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15058,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15072,7 +15069,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15108,7 +15105,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15122,7 +15119,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15158,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15172,7 +15169,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15208,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15222,7 +15219,7 @@
         <v>18.31833037024829</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E284">
         <v>19.49746116193226</v>
@@ -15258,7 +15255,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15272,10 +15269,10 @@
         <v>20.48449573097064</v>
       </c>
       <c r="D285" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E285">
-        <v>19.695975417544</v>
+        <v>19.52017392065009</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15284,10 +15281,10 @@
         <v>0.03001550426902936</v>
       </c>
       <c r="H285">
-        <v>0.029464024582456</v>
+        <v>0.0291598260793499</v>
       </c>
       <c r="I285">
-        <v>0.7885203134266412</v>
+        <v>0.9643218103205449</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15299,60 +15296,60 @@
         <v>25.25</v>
       </c>
       <c r="M285">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="N285">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C286">
-        <v>20.2362220319729</v>
+        <v>16.36962688241373</v>
       </c>
       <c r="D286" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E286">
-        <v>19.695975417544</v>
+        <v>15.35839983133243</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.0300437779680271</v>
+        <v>0.03413037311758627</v>
       </c>
       <c r="H286">
-        <v>0.029464024582456</v>
+        <v>0.03332160016866757</v>
       </c>
       <c r="I286">
-        <v>0.5402466144288987</v>
+        <v>1.011227051081296</v>
       </c>
       <c r="J286">
-        <v>0.246917319638827</v>
+        <v>0.4601229594604285</v>
       </c>
       <c r="K286">
-        <v>19.86</v>
+        <v>19.3</v>
       </c>
       <c r="L286">
-        <v>25.14</v>
+        <v>25.25</v>
       </c>
       <c r="M286">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="N286">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15369,28 +15366,28 @@
         <v>55</v>
       </c>
       <c r="C287">
-        <v>16.36962688241373</v>
+        <v>15.83273115942659</v>
       </c>
       <c r="D287" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E287">
-        <v>15.47876786187272</v>
+        <v>14.81538405347187</v>
       </c>
       <c r="F287">
         <v>-1</v>
       </c>
       <c r="G287">
-        <v>0.03413037311758627</v>
+        <v>0.03466726884057342</v>
       </c>
       <c r="H287">
-        <v>0.03368123213812727</v>
+        <v>0.03386461594652813</v>
       </c>
       <c r="I287">
-        <v>0.8908590205410079</v>
+        <v>1.017347105954723</v>
       </c>
       <c r="J287">
-        <v>0.4601229594604285</v>
+        <v>0.4879413907032856</v>
       </c>
       <c r="K287">
         <v>19.3</v>
@@ -15399,10 +15396,10 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="N287">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15419,28 +15416,28 @@
         <v>55</v>
       </c>
       <c r="C288">
-        <v>15.83273115942659</v>
+        <v>15.33566012693453</v>
       </c>
       <c r="D288" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E288">
-        <v>14.92851929188901</v>
+        <v>14.31264692630892</v>
       </c>
       <c r="F288">
         <v>-1</v>
       </c>
       <c r="G288">
-        <v>0.03466726884057342</v>
+        <v>0.03516433987306546</v>
       </c>
       <c r="H288">
-        <v>0.03423148070811099</v>
+        <v>0.03436735307369108</v>
       </c>
       <c r="I288">
-        <v>0.9042118675375796</v>
+        <v>1.023013200625616</v>
       </c>
       <c r="J288">
-        <v>0.4879413907032856</v>
+        <v>0.513696366480076</v>
       </c>
       <c r="K288">
         <v>19.3</v>
@@ -15449,10 +15446,10 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="N288">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15469,28 +15466,28 @@
         <v>55</v>
       </c>
       <c r="C289">
-        <v>15.33566012693453</v>
+        <v>14.89342039307265</v>
       </c>
       <c r="D289" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E289">
-        <v>14.41908587102409</v>
+        <v>13.86536611776052</v>
       </c>
       <c r="F289">
         <v>-1</v>
       </c>
       <c r="G289">
-        <v>0.03516433987306546</v>
+        <v>0.03560657960692735</v>
       </c>
       <c r="H289">
-        <v>0.0347409141289759</v>
+        <v>0.03481463388223948</v>
       </c>
       <c r="I289">
-        <v>0.9165742559104384</v>
+        <v>1.028054275312124</v>
       </c>
       <c r="J289">
-        <v>0.513696366480076</v>
+        <v>0.536610342327842</v>
       </c>
       <c r="K289">
         <v>19.3</v>
@@ -15499,10 +15496,10 @@
         <v>25.25</v>
       </c>
       <c r="M289">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="N289">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15519,28 +15516,28 @@
         <v>55</v>
       </c>
       <c r="C290">
-        <v>14.89342039307265</v>
+        <v>13.06652891544442</v>
       </c>
       <c r="D290" t="s">
         <v>108</v>
       </c>
       <c r="E290">
-        <v>13.96584742875528</v>
+        <v>12.12027532907597</v>
       </c>
       <c r="F290">
         <v>-1</v>
       </c>
       <c r="G290">
-        <v>0.03560657960692735</v>
+        <v>0.03743347108455558</v>
       </c>
       <c r="H290">
-        <v>0.03519415257124472</v>
+        <v>0.03673972467092403</v>
       </c>
       <c r="I290">
-        <v>0.9275729643173651</v>
+        <v>0.9462535863684511</v>
       </c>
       <c r="J290">
-        <v>0.536610342327842</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K290">
         <v>19.3</v>
@@ -15549,16 +15546,16 @@
         <v>25.25</v>
       </c>
       <c r="M290">
-        <v>19.78</v>
+        <v>19.5</v>
       </c>
       <c r="N290">
-        <v>24.58</v>
+        <v>24.43</v>
       </c>
       <c r="O290">
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>228</v>
+        <v>54</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15569,28 +15566,28 @@
         <v>55</v>
       </c>
       <c r="C291">
-        <v>13.06652891544442</v>
+        <v>12.7241137365128</v>
       </c>
       <c r="D291" t="s">
         <v>109</v>
       </c>
       <c r="E291">
-        <v>12.12027532907597</v>
+        <v>11.83093547368522</v>
       </c>
       <c r="F291">
         <v>-1</v>
       </c>
       <c r="G291">
-        <v>0.03743347108455558</v>
+        <v>0.03777588626348719</v>
       </c>
       <c r="H291">
-        <v>0.03673972467092403</v>
+        <v>0.03664906452631477</v>
       </c>
       <c r="I291">
-        <v>0.9462535863684511</v>
+        <v>0.8931782628275826</v>
       </c>
       <c r="J291">
-        <v>0.6312679318422579</v>
+        <v>0.6490096509578859</v>
       </c>
       <c r="K291">
         <v>19.3</v>
@@ -15599,66 +15596,16 @@
         <v>25.25</v>
       </c>
       <c r="M291">
-        <v>19.5</v>
+        <v>19.12</v>
       </c>
       <c r="N291">
-        <v>24.43</v>
+        <v>24.24</v>
       </c>
       <c r="O291">
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16">
-      <c r="A292" s="1">
-        <v>0</v>
-      </c>
-      <c r="B292" t="s">
-        <v>55</v>
-      </c>
-      <c r="C292">
-        <v>12.7241137365128</v>
-      </c>
-      <c r="D292" t="s">
-        <v>110</v>
-      </c>
-      <c r="E292">
-        <v>11.83093547368522</v>
-      </c>
-      <c r="F292">
-        <v>-1</v>
-      </c>
-      <c r="G292">
-        <v>0.03777588626348719</v>
-      </c>
-      <c r="H292">
-        <v>0.03664906452631477</v>
-      </c>
-      <c r="I292">
-        <v>0.8931782628275826</v>
-      </c>
-      <c r="J292">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K292">
-        <v>19.3</v>
-      </c>
-      <c r="L292">
-        <v>25.25</v>
-      </c>
-      <c r="M292">
-        <v>19.12</v>
-      </c>
-      <c r="N292">
-        <v>24.24</v>
-      </c>
-      <c r="O292">
-        <v>1</v>
-      </c>
-      <c r="P292" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,526 +178,517 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
+    <t>2018-01-02</t>
+  </si>
+  <si>
+    <t>2018-01-03</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-01-22</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-07-23</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-10-10</t>
+  </si>
+  <si>
+    <t>2019-12-30</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>2021-02-09</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>2021-02-23</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-03-08</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>2021-03-11</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2017-06-07</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-07-18</t>
+  </si>
+  <si>
+    <t>2017-07-19</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>2017-07-21</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>2017-07-27</t>
+  </si>
+  <si>
+    <t>2017-07-28</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-01</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>2017-08-04</t>
+  </si>
+  <si>
+    <t>2017-08-07</t>
+  </si>
+  <si>
+    <t>2017-08-08</t>
+  </si>
+  <si>
+    <t>2017-08-09</t>
+  </si>
+  <si>
+    <t>2017-08-10</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>2017-08-14</t>
+  </si>
+  <si>
+    <t>2017-08-15</t>
+  </si>
+  <si>
+    <t>2017-08-16</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>2017-08-18</t>
+  </si>
+  <si>
+    <t>2017-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-22</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>2017-08-28</t>
+  </si>
+  <si>
+    <t>2017-08-29</t>
+  </si>
+  <si>
+    <t>2017-08-30</t>
+  </si>
+  <si>
+    <t>2017-08-31</t>
+  </si>
+  <si>
+    <t>2017-09-01</t>
+  </si>
+  <si>
+    <t>2017-09-04</t>
+  </si>
+  <si>
+    <t>2017-09-05</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
+    <t>2017-09-29</t>
+  </si>
+  <si>
+    <t>2017-10-09</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2017-10-18</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
+  </si>
+  <si>
+    <t>2017-10-20</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-26</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-05-09</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>2018-05-11</t>
+  </si>
+  <si>
+    <t>2018-05-14</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-18</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-23</t>
+  </si>
+  <si>
+    <t>2018-05-24</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>2018-05-28</t>
+  </si>
+  <si>
+    <t>2018-09-04</t>
+  </si>
+  <si>
+    <t>2018-09-17</t>
+  </si>
+  <si>
+    <t>2019-06-21</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-10-17</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-20</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>2020-08-07</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-13</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-09-03</t>
+  </si>
+  <si>
+    <t>2020-09-09</t>
+  </si>
+  <si>
+    <t>2020-09-10</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>2020-09-16</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
-    <t>2018-01-02</t>
-  </si>
-  <si>
-    <t>2018-01-03</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-01-22</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-07-23</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-10-10</t>
-  </si>
-  <si>
-    <t>2019-12-30</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-02-09</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-02-23</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-08-13</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-08-23</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2017-06-07</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-07-18</t>
-  </si>
-  <si>
-    <t>2017-07-19</t>
-  </si>
-  <si>
-    <t>2017-07-20</t>
-  </si>
-  <si>
-    <t>2017-07-21</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-07-26</t>
-  </si>
-  <si>
-    <t>2017-07-27</t>
-  </si>
-  <si>
-    <t>2017-07-28</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-01</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-08-03</t>
-  </si>
-  <si>
-    <t>2017-08-04</t>
-  </si>
-  <si>
-    <t>2017-08-07</t>
-  </si>
-  <si>
-    <t>2017-08-08</t>
-  </si>
-  <si>
-    <t>2017-08-09</t>
-  </si>
-  <si>
-    <t>2017-08-10</t>
-  </si>
-  <si>
-    <t>2017-08-11</t>
-  </si>
-  <si>
-    <t>2017-08-14</t>
-  </si>
-  <si>
-    <t>2017-08-15</t>
-  </si>
-  <si>
-    <t>2017-08-16</t>
-  </si>
-  <si>
-    <t>2017-08-17</t>
-  </si>
-  <si>
-    <t>2017-08-18</t>
-  </si>
-  <si>
-    <t>2017-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-22</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>2017-08-25</t>
-  </si>
-  <si>
-    <t>2017-08-28</t>
-  </si>
-  <si>
-    <t>2017-08-29</t>
-  </si>
-  <si>
-    <t>2017-08-30</t>
-  </si>
-  <si>
-    <t>2017-08-31</t>
-  </si>
-  <si>
-    <t>2017-09-01</t>
-  </si>
-  <si>
-    <t>2017-09-04</t>
-  </si>
-  <si>
-    <t>2017-09-05</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
-    <t>2017-09-29</t>
-  </si>
-  <si>
-    <t>2017-10-09</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2017-10-18</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
-  </si>
-  <si>
-    <t>2017-10-20</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-26</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-05-09</t>
-  </si>
-  <si>
-    <t>2018-05-10</t>
-  </si>
-  <si>
-    <t>2018-05-11</t>
-  </si>
-  <si>
-    <t>2018-05-14</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-18</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-23</t>
-  </si>
-  <si>
-    <t>2018-05-24</t>
-  </si>
-  <si>
-    <t>2018-05-25</t>
-  </si>
-  <si>
-    <t>2018-05-28</t>
-  </si>
-  <si>
-    <t>2018-09-04</t>
-  </si>
-  <si>
-    <t>2018-09-17</t>
-  </si>
-  <si>
-    <t>2019-06-21</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-10-17</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-20</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-29</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>2020-08-07</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-13</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-09-03</t>
-  </si>
-  <si>
-    <t>2020-09-09</t>
-  </si>
-  <si>
-    <t>2020-09-10</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>2020-09-16</t>
-  </si>
-  <si>
-    <t>2020-09-17</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1058,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P291"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1119,7 +1110,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1155,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1169,7 +1160,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1205,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1219,7 +1210,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1255,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1269,7 +1260,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1305,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1319,7 +1310,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1355,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1369,7 +1360,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1405,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1419,7 +1410,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1455,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1469,7 +1460,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1505,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1519,7 +1510,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1555,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1569,7 +1560,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1605,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1619,7 +1610,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1655,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1669,7 +1660,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1705,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1719,7 +1710,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1755,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1769,7 +1760,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1805,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1819,7 +1810,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1855,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1869,7 +1860,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1905,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1919,7 +1910,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1955,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1969,7 +1960,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2005,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2019,7 +2010,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2055,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2069,7 +2060,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2105,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2119,7 +2110,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2155,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2169,7 +2160,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2205,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2219,7 +2210,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2255,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2269,7 +2260,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2305,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2319,7 +2310,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2355,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2369,7 +2360,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2405,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2419,7 +2410,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2455,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2469,7 +2460,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2505,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2519,7 +2510,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2555,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2569,7 +2560,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2605,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2655,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2669,7 +2660,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2705,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2755,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2805,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2819,7 +2810,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2855,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2869,7 +2860,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2905,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2919,7 +2910,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2955,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2969,7 +2960,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3005,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3019,7 +3010,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3055,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3069,7 +3060,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3105,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3119,7 +3110,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3155,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3169,7 +3160,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3205,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3219,7 +3210,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3255,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3269,7 +3260,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3305,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3319,7 +3310,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3355,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3369,7 +3360,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3405,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3419,7 +3410,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3455,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3469,7 +3460,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3505,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3519,7 +3510,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3555,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3569,7 +3560,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3605,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3619,7 +3610,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3655,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3705,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3755,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3769,7 +3760,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3805,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3855,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3905,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3919,7 +3910,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3955,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4005,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4055,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4069,7 +4060,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4105,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4155,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4169,7 +4160,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4205,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4255,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4269,7 +4260,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4305,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4355,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4369,7 +4360,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4405,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4455,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4469,7 +4460,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4505,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4555,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4569,7 +4560,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4605,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4619,7 +4610,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4655,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4705,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4719,7 +4710,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4755,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4769,7 +4760,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4805,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4855,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4869,7 +4860,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4905,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4919,7 +4910,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4955,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5005,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5019,7 +5010,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5055,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5069,7 +5060,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5105,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5155,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5169,7 +5160,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5205,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5219,7 +5210,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5255,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5305,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5319,7 +5310,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5355,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5369,7 +5360,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5405,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5455,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5469,7 +5460,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5505,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5519,7 +5510,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5555,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5605,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5619,7 +5610,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5655,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5669,7 +5660,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5705,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5755,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5769,7 +5760,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5805,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5819,7 +5810,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5855,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5869,7 +5860,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5905,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5919,7 +5910,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5955,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5969,7 +5960,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6005,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6019,7 +6010,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6055,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6069,7 +6060,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6105,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6119,7 +6110,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6155,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6169,7 +6160,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6205,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6219,7 +6210,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6255,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6269,7 +6260,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6305,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6319,7 +6310,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6355,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6369,7 +6360,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6405,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6419,7 +6410,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6455,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6469,7 +6460,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6505,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6519,7 +6510,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6555,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6569,7 +6560,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6605,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6619,7 +6610,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6655,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6669,7 +6660,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6705,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6719,7 +6710,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6755,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6769,7 +6760,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6805,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6819,7 +6810,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6855,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6869,7 +6860,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6905,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6919,7 +6910,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6955,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6969,7 +6960,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7005,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7019,7 +7010,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7055,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7069,7 +7060,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7105,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7119,7 +7110,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7155,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7169,7 +7160,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7205,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7219,7 +7210,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7255,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7269,7 +7260,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7305,7 +7296,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7319,7 +7310,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7355,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7369,7 +7360,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7405,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7419,7 +7410,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7455,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7469,7 +7460,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7505,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7519,7 +7510,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7555,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7569,7 +7560,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7605,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7619,7 +7610,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7655,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7669,7 +7660,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7705,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7719,7 +7710,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7755,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7769,7 +7760,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7805,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7819,7 +7810,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7855,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7869,7 +7860,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7905,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7919,7 +7910,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7955,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7969,7 +7960,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8005,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8019,7 +8010,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8055,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8069,7 +8060,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8105,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8119,7 +8110,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8155,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8169,7 +8160,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8205,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8219,7 +8210,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8255,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8269,7 +8260,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8305,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8319,7 +8310,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8355,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8369,7 +8360,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8405,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8419,7 +8410,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8455,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8469,7 +8460,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8505,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8519,7 +8510,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8555,7 +8546,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8569,7 +8560,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8605,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8619,7 +8610,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8655,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8669,7 +8660,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8705,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8719,7 +8710,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8755,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8769,7 +8760,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8805,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8819,7 +8810,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8855,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8869,7 +8860,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8905,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8919,7 +8910,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8969,7 +8960,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -9005,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9019,7 +9010,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9055,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9069,7 +9060,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9105,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9119,7 +9110,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9155,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9169,7 +9160,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9205,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9219,7 +9210,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9255,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9269,7 +9260,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9305,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9319,7 +9310,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9355,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9369,7 +9360,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9405,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9419,7 +9410,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9455,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9469,7 +9460,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9505,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9519,7 +9510,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9555,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9569,7 +9560,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9605,7 +9596,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9619,7 +9610,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9655,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9669,7 +9660,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9705,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9719,7 +9710,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9755,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9769,7 +9760,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9805,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9819,7 +9810,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9855,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9869,7 +9860,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9905,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9919,7 +9910,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9955,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9969,7 +9960,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10005,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10019,7 +10010,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10055,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10069,7 +10060,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10105,7 +10096,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10119,7 +10110,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10155,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10169,7 +10160,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10205,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10219,7 +10210,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10255,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10269,7 +10260,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10305,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10319,7 +10310,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10355,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10369,7 +10360,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10405,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10419,7 +10410,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10455,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10469,7 +10460,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10505,7 +10496,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10519,7 +10510,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10555,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10569,7 +10560,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10605,7 +10596,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10619,7 +10610,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10655,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10669,7 +10660,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10705,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10719,7 +10710,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10755,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10769,7 +10760,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10805,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10855,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10905,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10919,7 +10910,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10955,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11005,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11055,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11069,7 +11060,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11105,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11155,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11205,7 +11196,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11219,7 +11210,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11255,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11305,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11319,7 +11310,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11355,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11369,7 +11360,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11405,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11455,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11469,7 +11460,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11505,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11519,7 +11510,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11555,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11605,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11619,7 +11610,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11655,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11669,7 +11660,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11705,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11755,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11769,7 +11760,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11805,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11819,7 +11810,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11855,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11905,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11919,7 +11910,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11955,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11969,7 +11960,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12005,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12055,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12069,7 +12060,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12105,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12119,7 +12110,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12155,7 +12146,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12205,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12219,7 +12210,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12255,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12269,7 +12260,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12305,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12355,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12369,7 +12360,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12405,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12455,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12469,7 +12460,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12505,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12555,7 +12546,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12569,7 +12560,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12605,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12655,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12669,7 +12660,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12705,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12755,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12769,7 +12760,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12805,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12855,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12905,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12919,7 +12910,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12955,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12969,7 +12960,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13005,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13019,7 +13010,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13055,7 +13046,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13069,7 +13060,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13105,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13119,7 +13110,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13155,7 +13146,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13169,7 +13160,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13205,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13219,7 +13210,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13255,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13269,7 +13260,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13305,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13319,7 +13310,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13355,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13369,7 +13360,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13405,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13419,7 +13410,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13455,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13469,7 +13460,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13505,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13519,7 +13510,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13555,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13569,7 +13560,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13605,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13619,7 +13610,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13655,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13669,7 +13660,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13705,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13719,7 +13710,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13755,7 +13746,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13769,7 +13760,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13805,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13819,7 +13810,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13869,7 +13860,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13919,7 +13910,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13969,7 +13960,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14005,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14019,7 +14010,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14055,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14069,7 +14060,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14105,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14119,7 +14110,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14155,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14169,7 +14160,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14205,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14219,7 +14210,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14255,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14269,7 +14260,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14305,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14319,7 +14310,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14355,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14369,7 +14360,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14405,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14419,7 +14410,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14455,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14469,7 +14460,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14505,7 +14496,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14519,7 +14510,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14555,7 +14546,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14605,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14655,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14705,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14755,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14805,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14819,7 +14810,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14855,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14869,7 +14860,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14905,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14919,7 +14910,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14955,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14969,7 +14960,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15005,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15019,7 +15010,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15055,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15069,7 +15060,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15105,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15119,7 +15110,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15155,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15169,7 +15160,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15205,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15216,78 +15207,78 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>18.31833037024829</v>
+        <v>20.48449573097064</v>
       </c>
       <c r="D284" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E284">
-        <v>19.49746116193226</v>
+        <v>20.81572880311511</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.02686166962975171</v>
+        <v>0.03001550426902936</v>
       </c>
       <c r="H284">
-        <v>0.02870253883806774</v>
+        <v>0.03054427119688489</v>
       </c>
       <c r="I284">
-        <v>1.179130791683974</v>
+        <v>-0.3312330721444674</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
       </c>
       <c r="K284">
-        <v>17.3</v>
+        <v>19.3</v>
       </c>
       <c r="L284">
-        <v>22.59</v>
+        <v>25.25</v>
       </c>
       <c r="M284">
-        <v>18.64</v>
+        <v>19.7</v>
       </c>
       <c r="N284">
-        <v>24.1</v>
+        <v>25.68</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C285">
-        <v>20.48449573097064</v>
+        <v>15.33566012693453</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E285">
-        <v>19.52017392065009</v>
+        <v>14.31264692630892</v>
       </c>
       <c r="F285">
         <v>-1</v>
       </c>
       <c r="G285">
-        <v>0.03001550426902936</v>
+        <v>0.03516433987306546</v>
       </c>
       <c r="H285">
-        <v>0.0291598260793499</v>
+        <v>0.03436735307369108</v>
       </c>
       <c r="I285">
-        <v>0.9643218103205449</v>
+        <v>1.023013200625616</v>
       </c>
       <c r="J285">
-        <v>0.246917319638827</v>
+        <v>0.513696366480076</v>
       </c>
       <c r="K285">
         <v>19.3</v>
@@ -15305,7 +15296,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15313,31 +15304,31 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C286">
-        <v>16.36962688241373</v>
+        <v>14.89342039307265</v>
       </c>
       <c r="D286" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E286">
-        <v>15.35839983133243</v>
+        <v>13.86536611776052</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.03413037311758627</v>
+        <v>0.03560657960692735</v>
       </c>
       <c r="H286">
-        <v>0.03332160016866757</v>
+        <v>0.03481463388223948</v>
       </c>
       <c r="I286">
-        <v>1.011227051081296</v>
+        <v>1.028054275312124</v>
       </c>
       <c r="J286">
-        <v>0.4601229594604285</v>
+        <v>0.536610342327842</v>
       </c>
       <c r="K286">
         <v>19.3</v>
@@ -15355,7 +15346,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15363,31 +15354,31 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C287">
-        <v>15.83273115942659</v>
+        <v>13.06652891544442</v>
       </c>
       <c r="D287" t="s">
         <v>107</v>
       </c>
       <c r="E287">
-        <v>14.81538405347187</v>
+        <v>12.17015714317603</v>
       </c>
       <c r="F287">
         <v>-1</v>
       </c>
       <c r="G287">
-        <v>0.03466726884057342</v>
+        <v>0.03743347108455558</v>
       </c>
       <c r="H287">
-        <v>0.03386461594652813</v>
+        <v>0.03630984285682397</v>
       </c>
       <c r="I287">
-        <v>1.017347105954723</v>
+        <v>0.8963717722683953</v>
       </c>
       <c r="J287">
-        <v>0.4879413907032856</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K287">
         <v>19.3</v>
@@ -15396,16 +15387,16 @@
         <v>25.25</v>
       </c>
       <c r="M287">
-        <v>19.52</v>
+        <v>19.12</v>
       </c>
       <c r="N287">
-        <v>24.34</v>
+        <v>24.24</v>
       </c>
       <c r="O287">
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15413,31 +15404,31 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C288">
-        <v>15.33566012693453</v>
+        <v>12.7241137365128</v>
       </c>
       <c r="D288" t="s">
         <v>107</v>
       </c>
       <c r="E288">
-        <v>14.31264692630892</v>
+        <v>11.83093547368522</v>
       </c>
       <c r="F288">
         <v>-1</v>
       </c>
       <c r="G288">
-        <v>0.03516433987306546</v>
+        <v>0.03777588626348719</v>
       </c>
       <c r="H288">
-        <v>0.03436735307369108</v>
+        <v>0.03664906452631477</v>
       </c>
       <c r="I288">
-        <v>1.023013200625616</v>
+        <v>0.8931782628275826</v>
       </c>
       <c r="J288">
-        <v>0.513696366480076</v>
+        <v>0.6490096509578859</v>
       </c>
       <c r="K288">
         <v>19.3</v>
@@ -15446,166 +15437,16 @@
         <v>25.25</v>
       </c>
       <c r="M288">
-        <v>19.52</v>
+        <v>19.12</v>
       </c>
       <c r="N288">
-        <v>24.34</v>
+        <v>24.24</v>
       </c>
       <c r="O288">
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16">
-      <c r="A289" s="1">
-        <v>0</v>
-      </c>
-      <c r="B289" t="s">
-        <v>55</v>
-      </c>
-      <c r="C289">
-        <v>14.89342039307265</v>
-      </c>
-      <c r="D289" t="s">
-        <v>107</v>
-      </c>
-      <c r="E289">
-        <v>13.86536611776052</v>
-      </c>
-      <c r="F289">
-        <v>-1</v>
-      </c>
-      <c r="G289">
-        <v>0.03560657960692735</v>
-      </c>
-      <c r="H289">
-        <v>0.03481463388223948</v>
-      </c>
-      <c r="I289">
-        <v>1.028054275312124</v>
-      </c>
-      <c r="J289">
-        <v>0.536610342327842</v>
-      </c>
-      <c r="K289">
-        <v>19.3</v>
-      </c>
-      <c r="L289">
-        <v>25.25</v>
-      </c>
-      <c r="M289">
-        <v>19.52</v>
-      </c>
-      <c r="N289">
-        <v>24.34</v>
-      </c>
-      <c r="O289">
-        <v>1</v>
-      </c>
-      <c r="P289" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16">
-      <c r="A290" s="1">
-        <v>0</v>
-      </c>
-      <c r="B290" t="s">
-        <v>55</v>
-      </c>
-      <c r="C290">
-        <v>13.06652891544442</v>
-      </c>
-      <c r="D290" t="s">
-        <v>108</v>
-      </c>
-      <c r="E290">
-        <v>12.12027532907597</v>
-      </c>
-      <c r="F290">
-        <v>-1</v>
-      </c>
-      <c r="G290">
-        <v>0.03743347108455558</v>
-      </c>
-      <c r="H290">
-        <v>0.03673972467092403</v>
-      </c>
-      <c r="I290">
-        <v>0.9462535863684511</v>
-      </c>
-      <c r="J290">
-        <v>0.6312679318422579</v>
-      </c>
-      <c r="K290">
-        <v>19.3</v>
-      </c>
-      <c r="L290">
-        <v>25.25</v>
-      </c>
-      <c r="M290">
-        <v>19.5</v>
-      </c>
-      <c r="N290">
-        <v>24.43</v>
-      </c>
-      <c r="O290">
-        <v>1</v>
-      </c>
-      <c r="P290" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16">
-      <c r="A291" s="1">
-        <v>0</v>
-      </c>
-      <c r="B291" t="s">
-        <v>55</v>
-      </c>
-      <c r="C291">
-        <v>12.7241137365128</v>
-      </c>
-      <c r="D291" t="s">
-        <v>109</v>
-      </c>
-      <c r="E291">
-        <v>11.83093547368522</v>
-      </c>
-      <c r="F291">
-        <v>-1</v>
-      </c>
-      <c r="G291">
-        <v>0.03777588626348719</v>
-      </c>
-      <c r="H291">
-        <v>0.03664906452631477</v>
-      </c>
-      <c r="I291">
-        <v>0.8931782628275826</v>
-      </c>
-      <c r="J291">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K291">
-        <v>19.3</v>
-      </c>
-      <c r="L291">
-        <v>25.25</v>
-      </c>
-      <c r="M291">
-        <v>19.12</v>
-      </c>
-      <c r="N291">
-        <v>24.24</v>
-      </c>
-      <c r="O291">
-        <v>1</v>
-      </c>
-      <c r="P291" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,7 +178,7 @@
     <t>2021-04-01</t>
   </si>
   <si>
-    <t>2021-08-18</t>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2017-12-29</t>
@@ -331,13 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-08-31</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
+    <t>2021-09-01</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -680,18 +674,6 @@
   </si>
   <si>
     <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1146,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1196,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1246,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1296,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1346,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1396,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1446,7 +1428,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1496,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1546,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1596,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1646,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1696,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1746,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1796,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1846,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1896,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1946,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1996,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2046,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2096,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2146,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2196,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2246,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2296,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2346,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2396,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2446,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2496,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2546,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2596,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2696,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2846,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2896,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2946,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2996,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3046,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3096,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3146,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3196,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3246,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3296,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3346,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3396,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3446,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3496,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3546,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3596,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3646,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3796,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3946,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4096,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4196,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4296,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4396,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4496,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4596,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4646,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4746,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4796,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4896,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4946,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5046,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5096,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5196,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5246,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5346,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5396,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5496,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5546,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5646,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5696,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5796,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5846,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5896,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5946,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5996,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6046,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6096,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6146,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6196,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6246,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6296,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6346,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6396,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6446,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6496,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6546,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6596,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6646,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6696,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6746,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6796,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6846,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6896,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6946,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6996,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7046,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7096,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7146,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7196,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7246,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7296,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7346,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7396,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7446,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7496,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7546,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7596,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7646,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7696,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7746,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7796,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7846,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7896,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7946,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7996,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8046,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8096,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8146,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8196,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8246,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8296,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8346,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8396,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8446,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8496,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8546,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8596,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8646,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8696,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8746,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8796,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8846,7 +8828,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8896,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9146,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9196,7 +9178,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9246,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9296,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9346,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9396,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9446,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9496,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9546,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9596,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9646,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9696,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9746,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9796,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9846,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9896,7 +9878,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9946,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9996,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10046,7 +10028,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10096,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10146,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10196,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10246,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10296,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10346,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10396,7 +10378,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10446,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10496,7 +10478,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10546,7 +10528,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10596,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10646,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10696,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10746,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10796,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10946,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +10978,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11028,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11096,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11246,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11278,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11346,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11396,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11496,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11546,7 +11528,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11646,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11696,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11796,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11846,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11878,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11946,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11996,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12096,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12146,7 +12128,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12246,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12296,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12396,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12496,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12596,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12696,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12796,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12946,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12996,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13046,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13096,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13146,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13196,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13246,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13296,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13346,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13396,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13446,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13496,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13546,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13596,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13646,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13696,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13746,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13796,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13996,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14046,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14096,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14146,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14196,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14246,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14296,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14346,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14396,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14446,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14496,7 +14478,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14546,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14746,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14946,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14996,7 +14978,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15046,7 +15028,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15146,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15196,7 +15178,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15207,246 +15189,46 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>20.48449573097064</v>
+        <v>20.81572880311511</v>
       </c>
       <c r="D284" t="s">
         <v>105</v>
       </c>
       <c r="E284">
-        <v>20.81572880311511</v>
+        <v>21.95165360722346</v>
       </c>
       <c r="F284">
         <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.03001550426902936</v>
+        <v>0.03054427119688489</v>
       </c>
       <c r="H284">
-        <v>0.03054427119688489</v>
+        <v>0.03182834639277654</v>
       </c>
       <c r="I284">
-        <v>-0.3312330721444674</v>
+        <v>-1.135924804108353</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
       </c>
       <c r="K284">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="L284">
-        <v>25.25</v>
+        <v>25.68</v>
       </c>
       <c r="M284">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="N284">
-        <v>25.68</v>
+        <v>26.89</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16">
-      <c r="A285" s="1">
-        <v>0</v>
-      </c>
-      <c r="B285" t="s">
-        <v>54</v>
-      </c>
-      <c r="C285">
-        <v>15.33566012693453</v>
-      </c>
-      <c r="D285" t="s">
-        <v>106</v>
-      </c>
-      <c r="E285">
-        <v>14.31264692630892</v>
-      </c>
-      <c r="F285">
-        <v>-1</v>
-      </c>
-      <c r="G285">
-        <v>0.03516433987306546</v>
-      </c>
-      <c r="H285">
-        <v>0.03436735307369108</v>
-      </c>
-      <c r="I285">
-        <v>1.023013200625616</v>
-      </c>
-      <c r="J285">
-        <v>0.513696366480076</v>
-      </c>
-      <c r="K285">
-        <v>19.3</v>
-      </c>
-      <c r="L285">
-        <v>25.25</v>
-      </c>
-      <c r="M285">
-        <v>19.52</v>
-      </c>
-      <c r="N285">
-        <v>24.34</v>
-      </c>
-      <c r="O285">
-        <v>1</v>
-      </c>
-      <c r="P285" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16">
-      <c r="A286" s="1">
-        <v>0</v>
-      </c>
-      <c r="B286" t="s">
-        <v>54</v>
-      </c>
-      <c r="C286">
-        <v>14.89342039307265</v>
-      </c>
-      <c r="D286" t="s">
-        <v>106</v>
-      </c>
-      <c r="E286">
-        <v>13.86536611776052</v>
-      </c>
-      <c r="F286">
-        <v>-1</v>
-      </c>
-      <c r="G286">
-        <v>0.03560657960692735</v>
-      </c>
-      <c r="H286">
-        <v>0.03481463388223948</v>
-      </c>
-      <c r="I286">
-        <v>1.028054275312124</v>
-      </c>
-      <c r="J286">
-        <v>0.536610342327842</v>
-      </c>
-      <c r="K286">
-        <v>19.3</v>
-      </c>
-      <c r="L286">
-        <v>25.25</v>
-      </c>
-      <c r="M286">
-        <v>19.52</v>
-      </c>
-      <c r="N286">
-        <v>24.34</v>
-      </c>
-      <c r="O286">
-        <v>1</v>
-      </c>
-      <c r="P286" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16">
-      <c r="A287" s="1">
-        <v>0</v>
-      </c>
-      <c r="B287" t="s">
-        <v>54</v>
-      </c>
-      <c r="C287">
-        <v>13.06652891544442</v>
-      </c>
-      <c r="D287" t="s">
-        <v>107</v>
-      </c>
-      <c r="E287">
-        <v>12.17015714317603</v>
-      </c>
-      <c r="F287">
-        <v>-1</v>
-      </c>
-      <c r="G287">
-        <v>0.03743347108455558</v>
-      </c>
-      <c r="H287">
-        <v>0.03630984285682397</v>
-      </c>
-      <c r="I287">
-        <v>0.8963717722683953</v>
-      </c>
-      <c r="J287">
-        <v>0.6312679318422579</v>
-      </c>
-      <c r="K287">
-        <v>19.3</v>
-      </c>
-      <c r="L287">
-        <v>25.25</v>
-      </c>
-      <c r="M287">
-        <v>19.12</v>
-      </c>
-      <c r="N287">
-        <v>24.24</v>
-      </c>
-      <c r="O287">
-        <v>1</v>
-      </c>
-      <c r="P287" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16">
-      <c r="A288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B288" t="s">
-        <v>54</v>
-      </c>
-      <c r="C288">
-        <v>12.7241137365128</v>
-      </c>
-      <c r="D288" t="s">
-        <v>107</v>
-      </c>
-      <c r="E288">
-        <v>11.83093547368522</v>
-      </c>
-      <c r="F288">
-        <v>-1</v>
-      </c>
-      <c r="G288">
-        <v>0.03777588626348719</v>
-      </c>
-      <c r="H288">
-        <v>0.03664906452631477</v>
-      </c>
-      <c r="I288">
-        <v>0.8931782628275826</v>
-      </c>
-      <c r="J288">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K288">
-        <v>19.3</v>
-      </c>
-      <c r="L288">
-        <v>25.25</v>
-      </c>
-      <c r="M288">
-        <v>19.12</v>
-      </c>
-      <c r="N288">
-        <v>24.24</v>
-      </c>
-      <c r="O288">
-        <v>1</v>
-      </c>
-      <c r="P288" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,7 +178,7 @@
     <t>2021-04-01</t>
   </si>
   <si>
-    <t>2021-08-31</t>
+    <t>2021-09-01</t>
   </si>
   <si>
     <t>2017-12-29</t>
@@ -331,7 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-01</t>
+    <t>2021-09-02</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -673,7 +673,25 @@
     <t>2020-09-17</t>
   </si>
   <si>
-    <t>2021-06-30</t>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-08-13</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P284"/>
+  <dimension ref="A1:P290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15189,46 +15207,346 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>20.81572880311511</v>
+        <v>17.68754081079143</v>
       </c>
       <c r="D284" t="s">
         <v>105</v>
       </c>
       <c r="E284">
-        <v>21.95165360722346</v>
+        <v>17.72649777498028</v>
       </c>
       <c r="F284">
         <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.03054427119688489</v>
+        <v>0.03609245918920857</v>
       </c>
       <c r="H284">
-        <v>0.03182834639277654</v>
+        <v>0.03645350222501972</v>
       </c>
       <c r="I284">
-        <v>-1.135924804108353</v>
+        <v>-0.03895696418884853</v>
       </c>
       <c r="J284">
-        <v>0.246917319638827</v>
+        <v>0.4601229594604285</v>
       </c>
       <c r="K284">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="L284">
-        <v>25.68</v>
+        <v>26.89</v>
       </c>
       <c r="M284">
-        <v>20</v>
+        <v>20.35</v>
       </c>
       <c r="N284">
-        <v>26.89</v>
+        <v>27.09</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
         <v>219</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16">
+      <c r="A285" s="1">
+        <v>0</v>
+      </c>
+      <c r="B285" t="s">
+        <v>54</v>
+      </c>
+      <c r="C285">
+        <v>17.13117218593429</v>
+      </c>
+      <c r="D285" t="s">
+        <v>105</v>
+      </c>
+      <c r="E285">
+        <v>17.16039269918814</v>
+      </c>
+      <c r="F285">
+        <v>-1</v>
+      </c>
+      <c r="G285">
+        <v>0.03664882781406571</v>
+      </c>
+      <c r="H285">
+        <v>0.03701960730081186</v>
+      </c>
+      <c r="I285">
+        <v>-0.029220513253847</v>
+      </c>
+      <c r="J285">
+        <v>0.4879413907032856</v>
+      </c>
+      <c r="K285">
+        <v>20</v>
+      </c>
+      <c r="L285">
+        <v>26.89</v>
+      </c>
+      <c r="M285">
+        <v>20.35</v>
+      </c>
+      <c r="N285">
+        <v>27.09</v>
+      </c>
+      <c r="O285">
+        <v>1</v>
+      </c>
+      <c r="P285" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16">
+      <c r="A286" s="1">
+        <v>0</v>
+      </c>
+      <c r="B286" t="s">
+        <v>54</v>
+      </c>
+      <c r="C286">
+        <v>16.61607267039848</v>
+      </c>
+      <c r="D286" t="s">
+        <v>105</v>
+      </c>
+      <c r="E286">
+        <v>16.63627894213045</v>
+      </c>
+      <c r="F286">
+        <v>-1</v>
+      </c>
+      <c r="G286">
+        <v>0.03716392732960152</v>
+      </c>
+      <c r="H286">
+        <v>0.03754372105786954</v>
+      </c>
+      <c r="I286">
+        <v>-0.02020627173197198</v>
+      </c>
+      <c r="J286">
+        <v>0.513696366480076</v>
+      </c>
+      <c r="K286">
+        <v>20</v>
+      </c>
+      <c r="L286">
+        <v>26.89</v>
+      </c>
+      <c r="M286">
+        <v>20.35</v>
+      </c>
+      <c r="N286">
+        <v>27.09</v>
+      </c>
+      <c r="O286">
+        <v>1</v>
+      </c>
+      <c r="P286" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16">
+      <c r="A287" s="1">
+        <v>0</v>
+      </c>
+      <c r="B287" t="s">
+        <v>54</v>
+      </c>
+      <c r="C287">
+        <v>16.15779315344316</v>
+      </c>
+      <c r="D287" t="s">
+        <v>105</v>
+      </c>
+      <c r="E287">
+        <v>16.16997953362841</v>
+      </c>
+      <c r="F287">
+        <v>-1</v>
+      </c>
+      <c r="G287">
+        <v>0.03762220684655684</v>
+      </c>
+      <c r="H287">
+        <v>0.03801002046637159</v>
+      </c>
+      <c r="I287">
+        <v>-0.01218638018525553</v>
+      </c>
+      <c r="J287">
+        <v>0.536610342327842</v>
+      </c>
+      <c r="K287">
+        <v>20</v>
+      </c>
+      <c r="L287">
+        <v>26.89</v>
+      </c>
+      <c r="M287">
+        <v>20.35</v>
+      </c>
+      <c r="N287">
+        <v>27.09</v>
+      </c>
+      <c r="O287">
+        <v>1</v>
+      </c>
+      <c r="P287" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>54</v>
+      </c>
+      <c r="C288">
+        <v>14.26464136315484</v>
+      </c>
+      <c r="D288" t="s">
+        <v>105</v>
+      </c>
+      <c r="E288">
+        <v>14.24369758701005</v>
+      </c>
+      <c r="F288">
+        <v>-1</v>
+      </c>
+      <c r="G288">
+        <v>0.03951535863684516</v>
+      </c>
+      <c r="H288">
+        <v>0.03993630241298995</v>
+      </c>
+      <c r="I288">
+        <v>0.02094377614479193</v>
+      </c>
+      <c r="J288">
+        <v>0.6312679318422579</v>
+      </c>
+      <c r="K288">
+        <v>20</v>
+      </c>
+      <c r="L288">
+        <v>26.89</v>
+      </c>
+      <c r="M288">
+        <v>20.35</v>
+      </c>
+      <c r="N288">
+        <v>27.09</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16">
+      <c r="A289" s="1">
+        <v>0</v>
+      </c>
+      <c r="B289" t="s">
+        <v>54</v>
+      </c>
+      <c r="C289">
+        <v>13.90980698084228</v>
+      </c>
+      <c r="D289" t="s">
+        <v>105</v>
+      </c>
+      <c r="E289">
+        <v>13.88265360300702</v>
+      </c>
+      <c r="F289">
+        <v>-1</v>
+      </c>
+      <c r="G289">
+        <v>0.03987019301915772</v>
+      </c>
+      <c r="H289">
+        <v>0.04029734639699298</v>
+      </c>
+      <c r="I289">
+        <v>0.02715337783526195</v>
+      </c>
+      <c r="J289">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K289">
+        <v>20</v>
+      </c>
+      <c r="L289">
+        <v>26.89</v>
+      </c>
+      <c r="M289">
+        <v>20.35</v>
+      </c>
+      <c r="N289">
+        <v>27.09</v>
+      </c>
+      <c r="O289">
+        <v>1</v>
+      </c>
+      <c r="P289" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16">
+      <c r="A290" s="1">
+        <v>0</v>
+      </c>
+      <c r="B290" t="s">
+        <v>54</v>
+      </c>
+      <c r="C290">
+        <v>13.33176793386675</v>
+      </c>
+      <c r="D290" t="s">
+        <v>105</v>
+      </c>
+      <c r="E290">
+        <v>13.29449887270942</v>
+      </c>
+      <c r="F290">
+        <v>-1</v>
+      </c>
+      <c r="G290">
+        <v>0.04044823206613325</v>
+      </c>
+      <c r="H290">
+        <v>0.04088550112729059</v>
+      </c>
+      <c r="I290">
+        <v>0.03726906115733364</v>
+      </c>
+      <c r="J290">
+        <v>0.6779116033066624</v>
+      </c>
+      <c r="K290">
+        <v>20</v>
+      </c>
+      <c r="L290">
+        <v>26.89</v>
+      </c>
+      <c r="M290">
+        <v>20.35</v>
+      </c>
+      <c r="N290">
+        <v>27.09</v>
+      </c>
+      <c r="O290">
+        <v>1</v>
+      </c>
+      <c r="P290" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="227">
   <si>
     <t>trade_time</t>
   </si>
@@ -331,7 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-02</t>
+    <t>2021-09-06</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
   </si>
   <si>
     <t>2021-07-22</t>
@@ -1049,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P290"/>
+  <dimension ref="A1:P291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15207,28 +15210,28 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>17.68754081079143</v>
+        <v>21.95165360722346</v>
       </c>
       <c r="D284" t="s">
         <v>105</v>
       </c>
       <c r="E284">
-        <v>17.72649777498028</v>
+        <v>21.6841197515124</v>
       </c>
       <c r="F284">
         <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.03609245918920857</v>
+        <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.03645350222501972</v>
+        <v>0.0319558802484876</v>
       </c>
       <c r="I284">
-        <v>-0.03895696418884853</v>
+        <v>0.2675338557110614</v>
       </c>
       <c r="J284">
-        <v>0.4601229594604285</v>
+        <v>0.246917319638827</v>
       </c>
       <c r="K284">
         <v>20</v>
@@ -15237,10 +15240,10 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N284">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15257,28 +15260,28 @@
         <v>54</v>
       </c>
       <c r="C285">
-        <v>17.13117218593429</v>
+        <v>17.68754081079143</v>
       </c>
       <c r="D285" t="s">
         <v>105</v>
       </c>
       <c r="E285">
-        <v>17.16039269918814</v>
+        <v>17.24944244322309</v>
       </c>
       <c r="F285">
         <v>-1</v>
       </c>
       <c r="G285">
-        <v>0.03664882781406571</v>
+        <v>0.03609245918920857</v>
       </c>
       <c r="H285">
-        <v>0.03701960730081186</v>
+        <v>0.03639055755677691</v>
       </c>
       <c r="I285">
-        <v>-0.029220513253847</v>
+        <v>0.4380983675683439</v>
       </c>
       <c r="J285">
-        <v>0.4879413907032856</v>
+        <v>0.4601229594604285</v>
       </c>
       <c r="K285">
         <v>20</v>
@@ -15287,10 +15290,10 @@
         <v>26.89</v>
       </c>
       <c r="M285">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N285">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15307,28 +15310,28 @@
         <v>54</v>
       </c>
       <c r="C286">
-        <v>16.61607267039848</v>
+        <v>17.13117218593429</v>
       </c>
       <c r="D286" t="s">
         <v>105</v>
       </c>
       <c r="E286">
-        <v>16.63627894213045</v>
+        <v>16.67081907337166</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.03716392732960152</v>
+        <v>0.03664882781406571</v>
       </c>
       <c r="H286">
-        <v>0.03754372105786954</v>
+        <v>0.03696918092662834</v>
       </c>
       <c r="I286">
-        <v>-0.02020627173197198</v>
+        <v>0.460353112562629</v>
       </c>
       <c r="J286">
-        <v>0.513696366480076</v>
+        <v>0.4879413907032856</v>
       </c>
       <c r="K286">
         <v>20</v>
@@ -15337,10 +15340,10 @@
         <v>26.89</v>
       </c>
       <c r="M286">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N286">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15357,28 +15360,28 @@
         <v>54</v>
       </c>
       <c r="C287">
-        <v>16.15779315344316</v>
+        <v>16.61607267039848</v>
       </c>
       <c r="D287" t="s">
         <v>105</v>
       </c>
       <c r="E287">
-        <v>16.16997953362841</v>
+        <v>16.13511557721442</v>
       </c>
       <c r="F287">
         <v>-1</v>
       </c>
       <c r="G287">
-        <v>0.03762220684655684</v>
+        <v>0.03716392732960152</v>
       </c>
       <c r="H287">
-        <v>0.03801002046637159</v>
+        <v>0.03750488442278558</v>
       </c>
       <c r="I287">
-        <v>-0.01218638018525553</v>
+        <v>0.4809570931840597</v>
       </c>
       <c r="J287">
-        <v>0.536610342327842</v>
+        <v>0.513696366480076</v>
       </c>
       <c r="K287">
         <v>20</v>
@@ -15387,10 +15390,10 @@
         <v>26.89</v>
       </c>
       <c r="M287">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N287">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15407,28 +15410,28 @@
         <v>54</v>
       </c>
       <c r="C288">
-        <v>14.26464136315484</v>
+        <v>16.15779315344316</v>
       </c>
       <c r="D288" t="s">
         <v>105</v>
       </c>
       <c r="E288">
-        <v>14.24369758701005</v>
+        <v>15.65850487958089</v>
       </c>
       <c r="F288">
         <v>-1</v>
       </c>
       <c r="G288">
-        <v>0.03951535863684516</v>
+        <v>0.03762220684655684</v>
       </c>
       <c r="H288">
-        <v>0.03993630241298995</v>
+        <v>0.03798149512041911</v>
       </c>
       <c r="I288">
-        <v>0.02094377614479193</v>
+        <v>0.4992882738622715</v>
       </c>
       <c r="J288">
-        <v>0.6312679318422579</v>
+        <v>0.536610342327842</v>
       </c>
       <c r="K288">
         <v>20</v>
@@ -15437,10 +15440,10 @@
         <v>26.89</v>
       </c>
       <c r="M288">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N288">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15457,28 +15460,28 @@
         <v>54</v>
       </c>
       <c r="C289">
-        <v>13.90980698084228</v>
+        <v>14.26464136315484</v>
       </c>
       <c r="D289" t="s">
         <v>105</v>
       </c>
       <c r="E289">
-        <v>13.88265360300702</v>
+        <v>13.68962701768104</v>
       </c>
       <c r="F289">
         <v>-1</v>
       </c>
       <c r="G289">
-        <v>0.03987019301915772</v>
+        <v>0.03951535863684516</v>
       </c>
       <c r="H289">
-        <v>0.04029734639699298</v>
+        <v>0.03995037298231897</v>
       </c>
       <c r="I289">
-        <v>0.02715337783526195</v>
+        <v>0.5750143454738073</v>
       </c>
       <c r="J289">
-        <v>0.6490096509578859</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K289">
         <v>20</v>
@@ -15487,10 +15490,10 @@
         <v>26.89</v>
       </c>
       <c r="M289">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N289">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15507,28 +15510,28 @@
         <v>54</v>
       </c>
       <c r="C290">
-        <v>13.33176793386675</v>
+        <v>13.90980698084228</v>
       </c>
       <c r="D290" t="s">
         <v>105</v>
       </c>
       <c r="E290">
-        <v>13.29449887270942</v>
+        <v>13.32059926007597</v>
       </c>
       <c r="F290">
         <v>-1</v>
       </c>
       <c r="G290">
-        <v>0.04044823206613325</v>
+        <v>0.03987019301915772</v>
       </c>
       <c r="H290">
-        <v>0.04088550112729059</v>
+        <v>0.04031940073992403</v>
       </c>
       <c r="I290">
-        <v>0.03726906115733364</v>
+        <v>0.5892077207663107</v>
       </c>
       <c r="J290">
-        <v>0.6779116033066624</v>
+        <v>0.6490096509578859</v>
       </c>
       <c r="K290">
         <v>20</v>
@@ -15537,16 +15540,66 @@
         <v>26.89</v>
       </c>
       <c r="M290">
-        <v>20.35</v>
+        <v>20.8</v>
       </c>
       <c r="N290">
-        <v>27.09</v>
+        <v>26.82</v>
       </c>
       <c r="O290">
         <v>1</v>
       </c>
       <c r="P290" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16">
+      <c r="A291" s="1">
+        <v>0</v>
+      </c>
+      <c r="B291" t="s">
+        <v>54</v>
+      </c>
+      <c r="C291">
+        <v>13.33176793386675</v>
+      </c>
+      <c r="D291" t="s">
+        <v>105</v>
+      </c>
+      <c r="E291">
+        <v>12.71943865122142</v>
+      </c>
+      <c r="F291">
+        <v>-1</v>
+      </c>
+      <c r="G291">
+        <v>0.04044823206613325</v>
+      </c>
+      <c r="H291">
+        <v>0.04092056134877858</v>
+      </c>
+      <c r="I291">
+        <v>0.6123292826453319</v>
+      </c>
+      <c r="J291">
+        <v>0.6779116033066624</v>
+      </c>
+      <c r="K291">
+        <v>20</v>
+      </c>
+      <c r="L291">
+        <v>26.89</v>
+      </c>
+      <c r="M291">
+        <v>20.8</v>
+      </c>
+      <c r="N291">
+        <v>26.82</v>
+      </c>
+      <c r="O291">
+        <v>1</v>
+      </c>
+      <c r="P291" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -331,7 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-06</t>
+    <t>2021-09-07</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -692,9 +692,6 @@
   </si>
   <si>
     <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>2021-08-13</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P291"/>
+  <dimension ref="A1:P290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15216,7 +15213,7 @@
         <v>105</v>
       </c>
       <c r="E284">
-        <v>21.6841197515124</v>
+        <v>21.94004455562075</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15225,10 +15222,10 @@
         <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.0319558802484876</v>
+        <v>0.03235995544437925</v>
       </c>
       <c r="I284">
-        <v>0.2675338557110614</v>
+        <v>0.01160905160271142</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15240,10 +15237,10 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N284">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15266,7 +15263,7 @@
         <v>105</v>
       </c>
       <c r="E285">
-        <v>17.24944244322309</v>
+        <v>17.44140555538495</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15275,10 +15272,10 @@
         <v>0.03609245918920857</v>
       </c>
       <c r="H285">
-        <v>0.03639055755677691</v>
+        <v>0.03685859444461505</v>
       </c>
       <c r="I285">
-        <v>0.4380983675683439</v>
+        <v>0.2461352554064788</v>
       </c>
       <c r="J285">
         <v>0.4601229594604285</v>
@@ -15290,10 +15287,10 @@
         <v>26.89</v>
       </c>
       <c r="M285">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N285">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15316,7 +15313,7 @@
         <v>105</v>
       </c>
       <c r="E286">
-        <v>16.67081907337166</v>
+        <v>16.85443665616067</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15325,10 +15322,10 @@
         <v>0.03664882781406571</v>
       </c>
       <c r="H286">
-        <v>0.03696918092662834</v>
+        <v>0.03744556334383933</v>
       </c>
       <c r="I286">
-        <v>0.460353112562629</v>
+        <v>0.2767355297736174</v>
       </c>
       <c r="J286">
         <v>0.4879413907032856</v>
@@ -15340,10 +15337,10 @@
         <v>26.89</v>
       </c>
       <c r="M286">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N286">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15366,7 +15363,7 @@
         <v>105</v>
       </c>
       <c r="E287">
-        <v>16.13511557721442</v>
+        <v>16.31100666727039</v>
       </c>
       <c r="F287">
         <v>-1</v>
@@ -15375,10 +15372,10 @@
         <v>0.03716392732960152</v>
       </c>
       <c r="H287">
-        <v>0.03750488442278558</v>
+        <v>0.03798899333272961</v>
       </c>
       <c r="I287">
-        <v>0.4809570931840597</v>
+        <v>0.3050660031280863</v>
       </c>
       <c r="J287">
         <v>0.513696366480076</v>
@@ -15390,10 +15387,10 @@
         <v>26.89</v>
       </c>
       <c r="M287">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N287">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15416,7 +15413,7 @@
         <v>105</v>
       </c>
       <c r="E288">
-        <v>15.65850487958089</v>
+        <v>15.82752177688253</v>
       </c>
       <c r="F288">
         <v>-1</v>
@@ -15425,10 +15422,10 @@
         <v>0.03762220684655684</v>
       </c>
       <c r="H288">
-        <v>0.03798149512041911</v>
+        <v>0.03847247822311747</v>
       </c>
       <c r="I288">
-        <v>0.4992882738622715</v>
+        <v>0.330271376560626</v>
       </c>
       <c r="J288">
         <v>0.536610342327842</v>
@@ -15440,10 +15437,10 @@
         <v>26.89</v>
       </c>
       <c r="M288">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N288">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15466,7 +15463,7 @@
         <v>105</v>
       </c>
       <c r="E289">
-        <v>13.68962701768104</v>
+        <v>13.83024663812835</v>
       </c>
       <c r="F289">
         <v>-1</v>
@@ -15475,10 +15472,10 @@
         <v>0.03951535863684516</v>
       </c>
       <c r="H289">
-        <v>0.03995037298231897</v>
+        <v>0.04046975336187164</v>
       </c>
       <c r="I289">
-        <v>0.5750143454738073</v>
+        <v>0.4343947250264879</v>
       </c>
       <c r="J289">
         <v>0.6312679318422579</v>
@@ -15490,10 +15487,10 @@
         <v>26.89</v>
       </c>
       <c r="M289">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N289">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15516,7 +15513,7 @@
         <v>105</v>
       </c>
       <c r="E290">
-        <v>13.32059926007597</v>
+        <v>13.45589636478861</v>
       </c>
       <c r="F290">
         <v>-1</v>
@@ -15525,10 +15522,10 @@
         <v>0.03987019301915772</v>
       </c>
       <c r="H290">
-        <v>0.04031940073992403</v>
+        <v>0.04084410363521139</v>
       </c>
       <c r="I290">
-        <v>0.5892077207663107</v>
+        <v>0.4539106160536779</v>
       </c>
       <c r="J290">
         <v>0.6490096509578859</v>
@@ -15540,66 +15537,16 @@
         <v>26.89</v>
       </c>
       <c r="M290">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N290">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="O290">
         <v>1</v>
       </c>
       <c r="P290" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16">
-      <c r="A291" s="1">
-        <v>0</v>
-      </c>
-      <c r="B291" t="s">
-        <v>54</v>
-      </c>
-      <c r="C291">
-        <v>13.33176793386675</v>
-      </c>
-      <c r="D291" t="s">
-        <v>105</v>
-      </c>
-      <c r="E291">
-        <v>12.71943865122142</v>
-      </c>
-      <c r="F291">
-        <v>-1</v>
-      </c>
-      <c r="G291">
-        <v>0.04044823206613325</v>
-      </c>
-      <c r="H291">
-        <v>0.04092056134877858</v>
-      </c>
-      <c r="I291">
-        <v>0.6123292826453319</v>
-      </c>
-      <c r="J291">
-        <v>0.6779116033066624</v>
-      </c>
-      <c r="K291">
-        <v>20</v>
-      </c>
-      <c r="L291">
-        <v>26.89</v>
-      </c>
-      <c r="M291">
-        <v>20.8</v>
-      </c>
-      <c r="N291">
-        <v>26.82</v>
-      </c>
-      <c r="O291">
-        <v>1</v>
-      </c>
-      <c r="P291" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -331,7 +331,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15213,7 +15213,7 @@
         <v>105</v>
       </c>
       <c r="E284">
-        <v>21.94004455562075</v>
+        <v>21.73942801954851</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15222,10 +15222,10 @@
         <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.03235995544437925</v>
+        <v>0.03206057198045149</v>
       </c>
       <c r="I284">
-        <v>0.01160905160271142</v>
+        <v>0.212225587674947</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15237,10 +15237,10 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N284">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15263,7 +15263,7 @@
         <v>105</v>
       </c>
       <c r="E285">
-        <v>17.44140555538495</v>
+        <v>17.28343014727704</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15272,10 +15272,10 @@
         <v>0.03609245918920857</v>
       </c>
       <c r="H285">
-        <v>0.03685859444461505</v>
+        <v>0.03651656985272295</v>
       </c>
       <c r="I285">
-        <v>0.2461352554064788</v>
+        <v>0.4041106635143876</v>
       </c>
       <c r="J285">
         <v>0.4601229594604285</v>
@@ -15287,10 +15287,10 @@
         <v>26.89</v>
       </c>
       <c r="M285">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N285">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15313,7 +15313,7 @@
         <v>105</v>
       </c>
       <c r="E286">
-        <v>16.85443665616067</v>
+        <v>16.70202493430133</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15322,10 +15322,10 @@
         <v>0.03664882781406571</v>
       </c>
       <c r="H286">
-        <v>0.03744556334383933</v>
+        <v>0.03709797506569866</v>
       </c>
       <c r="I286">
-        <v>0.2767355297736174</v>
+        <v>0.4291472516329584</v>
       </c>
       <c r="J286">
         <v>0.4879413907032856</v>
@@ -15337,10 +15337,10 @@
         <v>26.89</v>
       </c>
       <c r="M286">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N286">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15363,7 +15363,7 @@
         <v>105</v>
       </c>
       <c r="E287">
-        <v>16.31100666727039</v>
+        <v>16.16374594056641</v>
       </c>
       <c r="F287">
         <v>-1</v>
@@ -15372,10 +15372,10 @@
         <v>0.03716392732960152</v>
       </c>
       <c r="H287">
-        <v>0.03798899333272961</v>
+        <v>0.03763625405943358</v>
       </c>
       <c r="I287">
-        <v>0.3050660031280863</v>
+        <v>0.4523267298320697</v>
       </c>
       <c r="J287">
         <v>0.513696366480076</v>
@@ -15387,10 +15387,10 @@
         <v>26.89</v>
       </c>
       <c r="M287">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N287">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15413,7 +15413,7 @@
         <v>105</v>
       </c>
       <c r="E288">
-        <v>15.82752177688253</v>
+        <v>15.6848438453481</v>
       </c>
       <c r="F288">
         <v>-1</v>
@@ -15422,10 +15422,10 @@
         <v>0.03762220684655684</v>
       </c>
       <c r="H288">
-        <v>0.03847247822311747</v>
+        <v>0.0381151561546519</v>
       </c>
       <c r="I288">
-        <v>0.330271376560626</v>
+        <v>0.4729493080950569</v>
       </c>
       <c r="J288">
         <v>0.536610342327842</v>
@@ -15437,10 +15437,10 @@
         <v>26.89</v>
       </c>
       <c r="M288">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N288">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O288">
         <v>1</v>
@@ -15463,7 +15463,7 @@
         <v>105</v>
       </c>
       <c r="E289">
-        <v>13.83024663812835</v>
+        <v>13.70650022449681</v>
       </c>
       <c r="F289">
         <v>-1</v>
@@ -15472,10 +15472,10 @@
         <v>0.03951535863684516</v>
       </c>
       <c r="H289">
-        <v>0.04046975336187164</v>
+        <v>0.04009349977550319</v>
       </c>
       <c r="I289">
-        <v>0.4343947250264879</v>
+        <v>0.5581411386580335</v>
       </c>
       <c r="J289">
         <v>0.6312679318422579</v>
@@ -15487,10 +15487,10 @@
         <v>26.89</v>
       </c>
       <c r="M289">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N289">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O289">
         <v>1</v>
@@ -15513,7 +15513,7 @@
         <v>105</v>
       </c>
       <c r="E290">
-        <v>13.45589636478861</v>
+        <v>13.33569829498018</v>
       </c>
       <c r="F290">
         <v>-1</v>
@@ -15522,10 +15522,10 @@
         <v>0.03987019301915772</v>
       </c>
       <c r="H290">
-        <v>0.04084410363521139</v>
+        <v>0.04046430170501981</v>
       </c>
       <c r="I290">
-        <v>0.4539106160536779</v>
+        <v>0.5741086858620985</v>
       </c>
       <c r="J290">
         <v>0.6490096509578859</v>
@@ -15537,10 +15537,10 @@
         <v>26.89</v>
       </c>
       <c r="M290">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N290">
-        <v>27.15</v>
+        <v>26.9</v>
       </c>
       <c r="O290">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="229">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,12 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -331,7 +337,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -692,6 +698,9 @@
   </si>
   <si>
     <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P290"/>
+  <dimension ref="A1:P292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1110,7 +1119,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1146,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1160,7 +1169,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1196,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1210,7 +1219,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1246,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1260,7 +1269,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1296,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1310,7 +1319,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1346,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1360,7 +1369,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1396,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1410,7 +1419,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1446,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1460,7 +1469,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1496,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1510,7 +1519,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1546,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1560,7 +1569,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1596,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1610,7 +1619,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1646,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1660,7 +1669,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1696,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1710,7 +1719,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1746,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1760,7 +1769,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1796,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1810,7 +1819,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1846,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1860,7 +1869,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1896,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1910,7 +1919,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1946,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1960,7 +1969,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1996,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2010,7 +2019,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2046,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2060,7 +2069,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2096,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2110,7 +2119,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2146,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2160,7 +2169,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2196,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2210,7 +2219,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2246,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2260,7 +2269,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2296,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2310,7 +2319,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2346,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2360,7 +2369,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2396,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2410,7 +2419,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2446,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2460,7 +2469,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2496,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2510,7 +2519,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2546,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2560,7 +2569,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2596,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2660,7 +2669,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2696,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,7 +2819,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2846,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2860,7 +2869,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2896,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2910,7 +2919,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2946,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2960,7 +2969,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2996,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3010,7 +3019,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3046,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3060,7 +3069,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3096,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3110,7 +3119,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3146,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3160,7 +3169,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3196,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3210,7 +3219,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3246,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3260,7 +3269,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3296,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3310,7 +3319,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3346,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3360,7 +3369,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3396,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3410,7 +3419,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3446,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3460,7 +3469,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3496,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3510,7 +3519,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3546,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3560,7 +3569,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3596,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3610,7 +3619,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3646,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3760,7 +3769,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3796,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3910,7 +3919,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3946,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4055,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4060,7 +4069,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4096,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4160,7 +4169,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4196,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4260,7 +4269,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4296,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4360,7 +4369,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4396,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4460,7 +4469,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4496,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4560,7 +4569,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4596,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4610,7 +4619,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4646,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4710,7 +4719,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4746,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4760,7 +4769,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4796,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4860,7 +4869,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4896,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4910,7 +4919,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4946,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5010,7 +5019,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5046,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5060,7 +5069,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5096,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5160,7 +5169,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5196,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5210,7 +5219,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5246,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5310,7 +5319,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5346,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5360,7 +5369,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5396,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5460,7 +5469,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5496,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5510,7 +5519,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5546,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5610,7 +5619,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5646,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5660,7 +5669,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5696,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5760,7 +5769,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5796,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5810,7 +5819,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5846,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5860,7 +5869,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5896,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5910,7 +5919,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5946,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5960,7 +5969,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5996,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6010,7 +6019,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6046,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6060,7 +6069,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6096,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6110,7 +6119,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6146,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6160,7 +6169,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6196,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6210,7 +6219,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6246,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6260,7 +6269,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6296,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6310,7 +6319,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6346,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6360,7 +6369,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6396,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6410,7 +6419,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6446,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6460,7 +6469,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6496,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6510,7 +6519,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6546,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6560,7 +6569,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6596,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6610,7 +6619,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6646,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6660,7 +6669,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6696,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6710,7 +6719,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6746,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6760,7 +6769,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6796,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6810,7 +6819,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6846,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6860,7 +6869,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6896,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6910,7 +6919,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6946,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,7 +6969,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6996,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7010,7 +7019,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7046,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7060,7 +7069,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7096,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7110,7 +7119,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7146,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,7 +7169,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7196,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7210,7 +7219,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7246,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7260,7 +7269,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7296,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7310,7 +7319,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7346,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7360,7 +7369,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7396,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7410,7 +7419,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7446,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7460,7 +7469,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7496,7 +7505,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7510,7 +7519,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7546,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7560,7 +7569,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7596,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7610,7 +7619,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7646,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7660,7 +7669,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7696,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7710,7 +7719,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7746,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7760,7 +7769,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7796,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7810,7 +7819,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7846,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7860,7 +7869,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7896,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7910,7 +7919,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7946,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7960,7 +7969,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7996,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8010,7 +8019,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8046,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8060,7 +8069,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8096,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8110,7 +8119,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8146,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8160,7 +8169,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8196,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8210,7 +8219,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8246,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8260,7 +8269,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8296,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8310,7 +8319,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8346,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8360,7 +8369,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8396,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8410,7 +8419,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8446,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8460,7 +8469,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8496,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8510,7 +8519,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8546,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8560,7 +8569,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8596,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8610,7 +8619,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8646,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8660,7 +8669,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8696,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8710,7 +8719,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8746,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8760,7 +8769,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8796,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8810,7 +8819,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8846,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8860,7 +8869,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8896,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8910,7 +8919,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8960,7 +8969,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8996,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9010,7 +9019,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9046,7 +9055,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9060,7 +9069,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9096,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9110,7 +9119,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9146,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9160,7 +9169,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9196,7 +9205,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9210,7 +9219,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9246,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9260,7 +9269,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9296,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9310,7 +9319,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9346,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9360,7 +9369,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9396,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9410,7 +9419,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9446,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9460,7 +9469,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9496,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9510,7 +9519,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9546,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9560,7 +9569,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9596,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9610,7 +9619,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9646,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9660,7 +9669,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9696,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9710,7 +9719,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9746,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9760,7 +9769,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9796,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9810,7 +9819,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9846,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9860,7 +9869,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9896,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9910,7 +9919,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9946,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9960,7 +9969,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9996,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10010,7 +10019,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10046,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10060,7 +10069,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10096,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10110,7 +10119,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10146,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10160,7 +10169,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10196,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10210,7 +10219,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10246,7 +10255,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10260,7 +10269,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10296,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10310,7 +10319,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10346,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10360,7 +10369,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10396,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10410,7 +10419,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10446,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10460,7 +10469,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10496,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10510,7 +10519,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10546,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10560,7 +10569,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10596,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10610,7 +10619,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10646,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10660,7 +10669,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10696,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10710,7 +10719,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10746,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10760,7 +10769,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10796,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10905,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10910,7 +10919,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10946,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11060,7 +11069,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11096,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11210,7 +11219,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11246,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11310,7 +11319,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11346,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11360,7 +11369,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11396,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11460,7 +11469,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11496,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11510,7 +11519,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11546,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11610,7 +11619,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11646,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11660,7 +11669,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11696,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11755,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11760,7 +11769,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11796,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11810,7 +11819,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11846,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11910,7 +11919,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11946,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11960,7 +11969,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11996,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12060,7 +12069,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12096,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12110,7 +12119,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12146,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12205,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12210,7 +12219,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12246,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12260,7 +12269,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12296,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12360,7 +12369,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12396,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12460,7 +12469,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12496,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12560,7 +12569,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12596,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12655,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12660,7 +12669,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12696,7 +12705,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12760,7 +12769,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12796,7 +12805,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12855,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12910,7 +12919,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12946,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12960,7 +12969,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12996,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13010,7 +13019,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13046,7 +13055,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13060,7 +13069,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13096,7 +13105,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13110,7 +13119,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13146,7 +13155,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13160,7 +13169,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13196,7 +13205,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13210,7 +13219,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13246,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13260,7 +13269,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13296,7 +13305,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13310,7 +13319,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13346,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13360,7 +13369,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13396,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13410,7 +13419,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13446,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13460,7 +13469,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13496,7 +13505,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13510,7 +13519,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13546,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13560,7 +13569,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13596,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13610,7 +13619,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13646,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13660,7 +13669,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13696,7 +13705,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13710,7 +13719,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13746,7 +13755,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13760,7 +13769,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13796,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13810,7 +13819,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13860,7 +13869,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13910,7 +13919,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13960,7 +13969,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13996,7 +14005,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14010,7 +14019,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14046,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14060,7 +14069,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14096,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14110,7 +14119,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14146,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14160,7 +14169,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14196,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14210,7 +14219,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14246,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14260,7 +14269,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14296,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14310,7 +14319,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14346,7 +14355,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14360,7 +14369,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14396,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14410,7 +14419,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14446,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14460,7 +14469,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14496,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14510,7 +14519,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14546,7 +14555,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14596,7 +14605,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14646,7 +14655,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14696,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14746,7 +14755,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14796,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14810,7 +14819,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14846,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14860,7 +14869,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14896,7 +14905,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14910,7 +14919,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14946,7 +14955,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14960,7 +14969,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14996,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15010,7 +15019,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15046,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15060,7 +15069,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15096,7 +15105,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15110,7 +15119,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15146,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15160,7 +15169,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15196,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15210,10 +15219,10 @@
         <v>21.95165360722346</v>
       </c>
       <c r="D284" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E284">
-        <v>21.73942801954851</v>
+        <v>21.61881148347628</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15222,10 +15231,10 @@
         <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.03206057198045149</v>
+        <v>0.03184118851652372</v>
       </c>
       <c r="I284">
-        <v>0.212225587674947</v>
+        <v>0.3328421237471773</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15237,66 +15246,66 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N284">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B285" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C285">
-        <v>17.68754081079143</v>
+        <v>21.6841197515124</v>
       </c>
       <c r="D285" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E285">
-        <v>17.28343014727704</v>
+        <v>21.61881148347628</v>
       </c>
       <c r="F285">
         <v>-1</v>
       </c>
       <c r="G285">
-        <v>0.03609245918920857</v>
+        <v>0.0319558802484876</v>
       </c>
       <c r="H285">
-        <v>0.03651656985272295</v>
+        <v>0.03184118851652372</v>
       </c>
       <c r="I285">
-        <v>0.4041106635143876</v>
+        <v>0.06530826803611589</v>
       </c>
       <c r="J285">
-        <v>0.4601229594604285</v>
+        <v>0.246917319638827</v>
       </c>
       <c r="K285">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="L285">
-        <v>26.89</v>
+        <v>26.82</v>
       </c>
       <c r="M285">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N285">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15307,28 +15316,28 @@
         <v>54</v>
       </c>
       <c r="C286">
-        <v>17.13117218593429</v>
+        <v>17.68754081079143</v>
       </c>
       <c r="D286" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E286">
-        <v>16.70202493430133</v>
+        <v>17.20545473916913</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.03664882781406571</v>
+        <v>0.03609245918920857</v>
       </c>
       <c r="H286">
-        <v>0.03709797506569866</v>
+        <v>0.03625454526083087</v>
       </c>
       <c r="I286">
-        <v>0.4291472516329584</v>
+        <v>0.4820860716223017</v>
       </c>
       <c r="J286">
-        <v>0.4879413907032856</v>
+        <v>0.4601229594604285</v>
       </c>
       <c r="K286">
         <v>20</v>
@@ -15337,16 +15346,16 @@
         <v>26.89</v>
       </c>
       <c r="M286">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N286">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O286">
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15357,28 +15366,28 @@
         <v>54</v>
       </c>
       <c r="C287">
-        <v>16.61607267039848</v>
+        <v>17.13117218593429</v>
       </c>
       <c r="D287" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E287">
-        <v>16.16374594056641</v>
+        <v>16.62961321244199</v>
       </c>
       <c r="F287">
         <v>-1</v>
       </c>
       <c r="G287">
-        <v>0.03716392732960152</v>
+        <v>0.03664882781406571</v>
       </c>
       <c r="H287">
-        <v>0.03763625405943358</v>
+        <v>0.03683038678755801</v>
       </c>
       <c r="I287">
-        <v>0.4523267298320697</v>
+        <v>0.5015589734923012</v>
       </c>
       <c r="J287">
-        <v>0.513696366480076</v>
+        <v>0.4879413907032856</v>
       </c>
       <c r="K287">
         <v>20</v>
@@ -15387,16 +15396,16 @@
         <v>26.89</v>
       </c>
       <c r="M287">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N287">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O287">
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15407,28 +15416,28 @@
         <v>54</v>
       </c>
       <c r="C288">
-        <v>16.15779315344316</v>
+        <v>16.61607267039848</v>
       </c>
       <c r="D288" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E288">
-        <v>15.6848438453481</v>
+        <v>16.09648521386243</v>
       </c>
       <c r="F288">
         <v>-1</v>
       </c>
       <c r="G288">
-        <v>0.03762220684655684</v>
+        <v>0.03716392732960152</v>
       </c>
       <c r="H288">
-        <v>0.0381151561546519</v>
+        <v>0.03736351478613757</v>
       </c>
       <c r="I288">
-        <v>0.4729493080950569</v>
+        <v>0.5195874565360512</v>
       </c>
       <c r="J288">
-        <v>0.536610342327842</v>
+        <v>0.513696366480076</v>
       </c>
       <c r="K288">
         <v>20</v>
@@ -15437,16 +15446,16 @@
         <v>26.89</v>
       </c>
       <c r="M288">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N288">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O288">
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15457,28 +15466,28 @@
         <v>54</v>
       </c>
       <c r="C289">
-        <v>14.26464136315484</v>
+        <v>16.15779315344316</v>
       </c>
       <c r="D289" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E289">
-        <v>13.70650022449681</v>
+        <v>15.62216591381367</v>
       </c>
       <c r="F289">
         <v>-1</v>
       </c>
       <c r="G289">
-        <v>0.03951535863684516</v>
+        <v>0.03762220684655684</v>
       </c>
       <c r="H289">
-        <v>0.04009349977550319</v>
+        <v>0.03783783408618634</v>
       </c>
       <c r="I289">
-        <v>0.5581411386580335</v>
+        <v>0.5356272396294877</v>
       </c>
       <c r="J289">
-        <v>0.6312679318422579</v>
+        <v>0.536610342327842</v>
       </c>
       <c r="K289">
         <v>20</v>
@@ -15487,16 +15496,16 @@
         <v>26.89</v>
       </c>
       <c r="M289">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N289">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O289">
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15507,28 +15516,28 @@
         <v>54</v>
       </c>
       <c r="C290">
-        <v>13.90980698084228</v>
+        <v>14.26464136315484</v>
       </c>
       <c r="D290" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E290">
-        <v>13.33569829498018</v>
+        <v>13.66275381086526</v>
       </c>
       <c r="F290">
         <v>-1</v>
       </c>
       <c r="G290">
-        <v>0.03987019301915772</v>
+        <v>0.03951535863684516</v>
       </c>
       <c r="H290">
-        <v>0.04046430170501981</v>
+        <v>0.03979724618913474</v>
       </c>
       <c r="I290">
-        <v>0.5741086858620985</v>
+        <v>0.6018875522895808</v>
       </c>
       <c r="J290">
-        <v>0.6490096509578859</v>
+        <v>0.6312679318422579</v>
       </c>
       <c r="K290">
         <v>20</v>
@@ -15537,16 +15546,116 @@
         <v>26.89</v>
       </c>
       <c r="M290">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N290">
-        <v>26.9</v>
+        <v>26.73</v>
       </c>
       <c r="O290">
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>225</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16">
+      <c r="A291" s="1">
+        <v>0</v>
+      </c>
+      <c r="B291" t="s">
+        <v>54</v>
+      </c>
+      <c r="C291">
+        <v>13.90980698084228</v>
+      </c>
+      <c r="D291" t="s">
+        <v>107</v>
+      </c>
+      <c r="E291">
+        <v>13.29550022517176</v>
+      </c>
+      <c r="F291">
+        <v>-1</v>
+      </c>
+      <c r="G291">
+        <v>0.03987019301915772</v>
+      </c>
+      <c r="H291">
+        <v>0.04016449977482824</v>
+      </c>
+      <c r="I291">
+        <v>0.6143067556705208</v>
+      </c>
+      <c r="J291">
+        <v>0.6490096509578859</v>
+      </c>
+      <c r="K291">
+        <v>20</v>
+      </c>
+      <c r="L291">
+        <v>26.89</v>
+      </c>
+      <c r="M291">
+        <v>20.7</v>
+      </c>
+      <c r="N291">
+        <v>26.73</v>
+      </c>
+      <c r="O291">
+        <v>1</v>
+      </c>
+      <c r="P291" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16">
+      <c r="A292" s="1">
+        <v>0</v>
+      </c>
+      <c r="B292" t="s">
+        <v>56</v>
+      </c>
+      <c r="C292">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D292" t="s">
+        <v>54</v>
+      </c>
+      <c r="E292">
+        <v>13.76730272629556</v>
+      </c>
+      <c r="F292">
+        <v>1</v>
+      </c>
+      <c r="G292">
+        <v>0.03714775253913554</v>
+      </c>
+      <c r="H292">
+        <v>0.04001269727370445</v>
+      </c>
+      <c r="I292">
+        <v>2.235055265431093</v>
+      </c>
+      <c r="J292">
+        <v>0.6561348636852222</v>
+      </c>
+      <c r="K292">
+        <v>19.52</v>
+      </c>
+      <c r="L292">
+        <v>24.34</v>
+      </c>
+      <c r="M292">
+        <v>20</v>
+      </c>
+      <c r="N292">
+        <v>26.89</v>
+      </c>
+      <c r="O292">
+        <v>1</v>
+      </c>
+      <c r="P292" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="224">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,7 +181,10 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-06</t>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-08-30</t>
@@ -337,7 +340,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-09-13</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -680,24 +683,6 @@
   </si>
   <si>
     <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
   </si>
   <si>
     <t>2021-08-27</t>
@@ -1058,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P292"/>
+  <dimension ref="A1:P287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1119,7 +1104,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1155,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1169,7 +1154,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1205,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1219,7 +1204,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1255,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1269,7 +1254,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1305,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1319,7 +1304,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1355,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1369,7 +1354,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1405,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1419,7 +1404,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1455,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1469,7 +1454,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1505,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1519,7 +1504,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1555,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1569,7 +1554,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1605,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1619,7 +1604,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1655,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1669,7 +1654,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1705,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1719,7 +1704,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1755,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1769,7 +1754,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1805,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1819,7 +1804,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1855,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1869,7 +1854,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1905,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1919,7 +1904,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1955,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1969,7 +1954,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2005,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2019,7 +2004,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2055,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2069,7 +2054,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2105,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2119,7 +2104,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2155,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2169,7 +2154,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2205,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2219,7 +2204,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2255,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2269,7 +2254,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2305,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2319,7 +2304,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2355,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2369,7 +2354,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2405,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2419,7 +2404,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2455,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2469,7 +2454,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2505,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2519,7 +2504,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2555,7 +2540,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2569,7 +2554,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2605,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2655,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2669,7 +2654,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2705,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2755,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2805,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2819,7 +2804,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2855,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2869,7 +2854,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2905,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2919,7 +2904,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2955,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2969,7 +2954,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3005,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3019,7 +3004,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3055,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3069,7 +3054,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3105,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3119,7 +3104,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3155,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3169,7 +3154,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3205,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3219,7 +3204,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3255,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3269,7 +3254,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3305,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3319,7 +3304,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3355,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3369,7 +3354,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3405,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3419,7 +3404,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3455,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3469,7 +3454,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3505,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3519,7 +3504,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3555,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3569,7 +3554,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3605,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3619,7 +3604,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3655,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3705,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3755,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3769,7 +3754,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3805,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3855,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3905,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3919,7 +3904,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3955,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4005,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4055,7 +4040,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4069,7 +4054,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4105,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4155,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4169,7 +4154,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4205,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4255,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4269,7 +4254,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4305,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4355,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4369,7 +4354,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4405,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4455,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4469,7 +4454,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4505,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4555,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4569,7 +4554,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4605,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4619,7 +4604,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4655,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4705,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4719,7 +4704,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4755,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4769,7 +4754,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4805,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4855,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4869,7 +4854,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4905,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4919,7 +4904,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4955,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5005,7 +4990,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5019,7 +5004,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5055,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5069,7 +5054,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5105,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5155,7 +5140,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5169,7 +5154,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5205,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5219,7 +5204,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5255,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5305,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5319,7 +5304,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5355,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5369,7 +5354,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5405,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5455,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5469,7 +5454,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5505,7 +5490,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5519,7 +5504,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5555,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5605,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5619,7 +5604,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5655,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5669,7 +5654,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5705,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5755,7 +5740,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5769,7 +5754,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5805,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5819,7 +5804,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5855,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5869,7 +5854,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5905,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5919,7 +5904,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5955,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5969,7 +5954,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6005,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6019,7 +6004,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6055,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6069,7 +6054,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6105,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6119,7 +6104,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6155,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6169,7 +6154,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6205,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6219,7 +6204,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6255,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6269,7 +6254,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6305,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6319,7 +6304,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6355,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6369,7 +6354,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6405,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6419,7 +6404,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6455,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6469,7 +6454,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6505,7 +6490,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6519,7 +6504,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6555,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6569,7 +6554,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6605,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6619,7 +6604,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6655,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6669,7 +6654,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6705,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6719,7 +6704,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6755,7 +6740,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6769,7 +6754,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6805,7 +6790,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6819,7 +6804,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6855,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6869,7 +6854,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6905,7 +6890,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6919,7 +6904,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6955,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6969,7 +6954,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7005,7 +6990,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7019,7 +7004,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7055,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7069,7 +7054,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7105,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7119,7 +7104,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7155,7 +7140,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7169,7 +7154,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7205,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7219,7 +7204,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7255,7 +7240,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7269,7 +7254,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7305,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7319,7 +7304,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7355,7 +7340,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7369,7 +7354,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7405,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7419,7 +7404,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7455,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7469,7 +7454,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7505,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7519,7 +7504,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7555,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7569,7 +7554,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7605,7 +7590,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7619,7 +7604,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7655,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7669,7 +7654,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7705,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7719,7 +7704,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7755,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7769,7 +7754,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7805,7 +7790,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7819,7 +7804,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7855,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7869,7 +7854,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7905,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7919,7 +7904,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7955,7 +7940,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7969,7 +7954,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8005,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8019,7 +8004,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8055,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8069,7 +8054,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8105,7 +8090,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8119,7 +8104,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8155,7 +8140,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8169,7 +8154,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8205,7 +8190,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8219,7 +8204,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8255,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8269,7 +8254,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8305,7 +8290,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8319,7 +8304,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8355,7 +8340,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8369,7 +8354,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8405,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8419,7 +8404,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8455,7 +8440,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8469,7 +8454,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8505,7 +8490,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8519,7 +8504,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8555,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8569,7 +8554,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8605,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8619,7 +8604,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8655,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8669,7 +8654,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8705,7 +8690,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8719,7 +8704,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8755,7 +8740,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8769,7 +8754,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8805,7 +8790,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8819,7 +8804,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8855,7 +8840,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8869,7 +8854,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8905,7 +8890,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8919,7 +8904,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8969,7 +8954,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -9005,7 +8990,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9019,7 +9004,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9055,7 +9040,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9069,7 +9054,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9105,7 +9090,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9119,7 +9104,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9155,7 +9140,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9169,7 +9154,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9205,7 +9190,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9219,7 +9204,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9255,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9269,7 +9254,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9305,7 +9290,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9319,7 +9304,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9355,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9369,7 +9354,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9405,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9419,7 +9404,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9455,7 +9440,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9469,7 +9454,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9505,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9519,7 +9504,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9555,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9569,7 +9554,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9605,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9619,7 +9604,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9655,7 +9640,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9669,7 +9654,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9705,7 +9690,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9719,7 +9704,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9755,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9769,7 +9754,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9805,7 +9790,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9819,7 +9804,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9855,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9869,7 +9854,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9905,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9919,7 +9904,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9955,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9969,7 +9954,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10005,7 +9990,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10019,7 +10004,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10055,7 +10040,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10069,7 +10054,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10105,7 +10090,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10119,7 +10104,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10155,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10169,7 +10154,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10205,7 +10190,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10219,7 +10204,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10255,7 +10240,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10269,7 +10254,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10305,7 +10290,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10319,7 +10304,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10355,7 +10340,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10369,7 +10354,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10405,7 +10390,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10419,7 +10404,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10455,7 +10440,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10469,7 +10454,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10505,7 +10490,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10519,7 +10504,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10555,7 +10540,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10569,7 +10554,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10605,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10619,7 +10604,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10655,7 +10640,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10669,7 +10654,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10705,7 +10690,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10719,7 +10704,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10755,7 +10740,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10769,7 +10754,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10805,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10855,7 +10840,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10905,7 +10890,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10919,7 +10904,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10955,7 +10940,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11005,7 +10990,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11055,7 +11040,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11069,7 +11054,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11105,7 +11090,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11155,7 +11140,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11205,7 +11190,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11219,7 +11204,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11255,7 +11240,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11305,7 +11290,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11319,7 +11304,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11355,7 +11340,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11369,7 +11354,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11405,7 +11390,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11455,7 +11440,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11469,7 +11454,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11505,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11519,7 +11504,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11555,7 +11540,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11605,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11619,7 +11604,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11655,7 +11640,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11669,7 +11654,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11705,7 +11690,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11755,7 +11740,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11769,7 +11754,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11805,7 +11790,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11819,7 +11804,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11855,7 +11840,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11905,7 +11890,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11919,7 +11904,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11955,7 +11940,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11969,7 +11954,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12005,7 +11990,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12055,7 +12040,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12069,7 +12054,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12105,7 +12090,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12119,7 +12104,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12155,7 +12140,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12205,7 +12190,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12219,7 +12204,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12255,7 +12240,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12269,7 +12254,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12305,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12355,7 +12340,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12369,7 +12354,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12405,7 +12390,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12455,7 +12440,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12469,7 +12454,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12505,7 +12490,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12555,7 +12540,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12569,7 +12554,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12605,7 +12590,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12655,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12669,7 +12654,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12705,7 +12690,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12755,7 +12740,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12769,7 +12754,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12805,7 +12790,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12855,7 +12840,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12905,7 +12890,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12919,7 +12904,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12955,7 +12940,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12969,7 +12954,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13005,7 +12990,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13019,7 +13004,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13055,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13069,7 +13054,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13105,7 +13090,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13119,7 +13104,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13155,7 +13140,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13169,7 +13154,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13205,7 +13190,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13219,7 +13204,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13255,7 +13240,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13269,7 +13254,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13305,7 +13290,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13319,7 +13304,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13355,7 +13340,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13369,7 +13354,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13405,7 +13390,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13419,7 +13404,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13455,7 +13440,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13469,7 +13454,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13505,7 +13490,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13519,7 +13504,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13555,7 +13540,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13569,7 +13554,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13605,7 +13590,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13619,7 +13604,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13655,7 +13640,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13669,7 +13654,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13705,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13719,7 +13704,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13755,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13769,7 +13754,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13805,7 +13790,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13819,7 +13804,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13869,7 +13854,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13919,7 +13904,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13969,7 +13954,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14005,7 +13990,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14019,7 +14004,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14055,7 +14040,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14069,7 +14054,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14105,7 +14090,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14119,7 +14104,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14155,7 +14140,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14169,7 +14154,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14205,7 +14190,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14219,7 +14204,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14255,7 +14240,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14269,7 +14254,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14305,7 +14290,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14319,7 +14304,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14355,7 +14340,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14369,7 +14354,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14405,7 +14390,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14419,7 +14404,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14455,7 +14440,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14469,7 +14454,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14505,7 +14490,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14519,7 +14504,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14555,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14605,7 +14590,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14655,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14705,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14755,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14805,7 +14790,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14819,7 +14804,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14855,7 +14840,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14869,7 +14854,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14905,7 +14890,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14919,7 +14904,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14955,7 +14940,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14969,7 +14954,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15005,7 +14990,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15019,7 +15004,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15055,7 +15040,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15069,7 +15054,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15105,7 +15090,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15119,7 +15104,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15155,7 +15140,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15169,7 +15154,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15205,7 +15190,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15219,10 +15204,10 @@
         <v>21.95165360722346</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E284">
-        <v>21.61881148347628</v>
+        <v>21.95535282365687</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15231,10 +15216,10 @@
         <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.03184118851652372</v>
+        <v>0.03242464717634314</v>
       </c>
       <c r="I284">
-        <v>0.3328421237471773</v>
+        <v>-0.003699216433407315</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15246,16 +15231,16 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="N284">
-        <v>26.73</v>
+        <v>27.19</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15266,90 +15251,90 @@
         <v>55</v>
       </c>
       <c r="C285">
-        <v>21.6841197515124</v>
+        <v>21.94004455562075</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E285">
-        <v>21.61881148347628</v>
+        <v>21.95535282365687</v>
       </c>
       <c r="F285">
         <v>-1</v>
       </c>
       <c r="G285">
-        <v>0.0319558802484876</v>
+        <v>0.03235995544437925</v>
       </c>
       <c r="H285">
-        <v>0.03184118851652372</v>
+        <v>0.03242464717634314</v>
       </c>
       <c r="I285">
-        <v>0.06530826803611589</v>
+        <v>-0.01530826803611873</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
       </c>
       <c r="K285">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="L285">
-        <v>26.82</v>
+        <v>27.15</v>
       </c>
       <c r="M285">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="N285">
-        <v>26.73</v>
+        <v>27.19</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B286" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C286">
-        <v>17.68754081079143</v>
+        <v>22.01066109169298</v>
       </c>
       <c r="D286" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E286">
-        <v>17.20545473916913</v>
+        <v>21.95535282365687</v>
       </c>
       <c r="F286">
         <v>-1</v>
       </c>
       <c r="G286">
-        <v>0.03609245918920857</v>
+        <v>0.03252933890830702</v>
       </c>
       <c r="H286">
-        <v>0.03625454526083087</v>
+        <v>0.03242464717634314</v>
       </c>
       <c r="I286">
-        <v>0.4820860716223017</v>
+        <v>0.05530826803611788</v>
       </c>
       <c r="J286">
-        <v>0.4601229594604285</v>
+        <v>0.246917319638827</v>
       </c>
       <c r="K286">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="L286">
-        <v>26.89</v>
+        <v>27.27</v>
       </c>
       <c r="M286">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="N286">
-        <v>26.73</v>
+        <v>27.19</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -15363,299 +15348,49 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
+        <v>57</v>
+      </c>
+      <c r="C287">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D287" t="s">
         <v>54</v>
       </c>
-      <c r="C287">
-        <v>17.13117218593429</v>
-      </c>
-      <c r="D287" t="s">
-        <v>107</v>
-      </c>
       <c r="E287">
-        <v>16.62961321244199</v>
+        <v>13.76730272629556</v>
       </c>
       <c r="F287">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03664882781406571</v>
+        <v>0.03714775253913554</v>
       </c>
       <c r="H287">
-        <v>0.03683038678755801</v>
+        <v>0.04001269727370445</v>
       </c>
       <c r="I287">
-        <v>0.5015589734923012</v>
+        <v>2.235055265431093</v>
       </c>
       <c r="J287">
-        <v>0.4879413907032856</v>
+        <v>0.6561348636852222</v>
       </c>
       <c r="K287">
+        <v>19.52</v>
+      </c>
+      <c r="L287">
+        <v>24.34</v>
+      </c>
+      <c r="M287">
         <v>20</v>
       </c>
-      <c r="L287">
+      <c r="N287">
         <v>26.89</v>
-      </c>
-      <c r="M287">
-        <v>20.7</v>
-      </c>
-      <c r="N287">
-        <v>26.73</v>
       </c>
       <c r="O287">
         <v>1</v>
       </c>
       <c r="P287" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16">
-      <c r="A288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B288" t="s">
-        <v>54</v>
-      </c>
-      <c r="C288">
-        <v>16.61607267039848</v>
-      </c>
-      <c r="D288" t="s">
-        <v>107</v>
-      </c>
-      <c r="E288">
-        <v>16.09648521386243</v>
-      </c>
-      <c r="F288">
-        <v>-1</v>
-      </c>
-      <c r="G288">
-        <v>0.03716392732960152</v>
-      </c>
-      <c r="H288">
-        <v>0.03736351478613757</v>
-      </c>
-      <c r="I288">
-        <v>0.5195874565360512</v>
-      </c>
-      <c r="J288">
-        <v>0.513696366480076</v>
-      </c>
-      <c r="K288">
-        <v>20</v>
-      </c>
-      <c r="L288">
-        <v>26.89</v>
-      </c>
-      <c r="M288">
-        <v>20.7</v>
-      </c>
-      <c r="N288">
-        <v>26.73</v>
-      </c>
-      <c r="O288">
-        <v>1</v>
-      </c>
-      <c r="P288" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16">
-      <c r="A289" s="1">
-        <v>0</v>
-      </c>
-      <c r="B289" t="s">
-        <v>54</v>
-      </c>
-      <c r="C289">
-        <v>16.15779315344316</v>
-      </c>
-      <c r="D289" t="s">
-        <v>107</v>
-      </c>
-      <c r="E289">
-        <v>15.62216591381367</v>
-      </c>
-      <c r="F289">
-        <v>-1</v>
-      </c>
-      <c r="G289">
-        <v>0.03762220684655684</v>
-      </c>
-      <c r="H289">
-        <v>0.03783783408618634</v>
-      </c>
-      <c r="I289">
-        <v>0.5356272396294877</v>
-      </c>
-      <c r="J289">
-        <v>0.536610342327842</v>
-      </c>
-      <c r="K289">
-        <v>20</v>
-      </c>
-      <c r="L289">
-        <v>26.89</v>
-      </c>
-      <c r="M289">
-        <v>20.7</v>
-      </c>
-      <c r="N289">
-        <v>26.73</v>
-      </c>
-      <c r="O289">
-        <v>1</v>
-      </c>
-      <c r="P289" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16">
-      <c r="A290" s="1">
-        <v>0</v>
-      </c>
-      <c r="B290" t="s">
-        <v>54</v>
-      </c>
-      <c r="C290">
-        <v>14.26464136315484</v>
-      </c>
-      <c r="D290" t="s">
-        <v>107</v>
-      </c>
-      <c r="E290">
-        <v>13.66275381086526</v>
-      </c>
-      <c r="F290">
-        <v>-1</v>
-      </c>
-      <c r="G290">
-        <v>0.03951535863684516</v>
-      </c>
-      <c r="H290">
-        <v>0.03979724618913474</v>
-      </c>
-      <c r="I290">
-        <v>0.6018875522895808</v>
-      </c>
-      <c r="J290">
-        <v>0.6312679318422579</v>
-      </c>
-      <c r="K290">
-        <v>20</v>
-      </c>
-      <c r="L290">
-        <v>26.89</v>
-      </c>
-      <c r="M290">
-        <v>20.7</v>
-      </c>
-      <c r="N290">
-        <v>26.73</v>
-      </c>
-      <c r="O290">
-        <v>1</v>
-      </c>
-      <c r="P290" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16">
-      <c r="A291" s="1">
-        <v>0</v>
-      </c>
-      <c r="B291" t="s">
-        <v>54</v>
-      </c>
-      <c r="C291">
-        <v>13.90980698084228</v>
-      </c>
-      <c r="D291" t="s">
-        <v>107</v>
-      </c>
-      <c r="E291">
-        <v>13.29550022517176</v>
-      </c>
-      <c r="F291">
-        <v>-1</v>
-      </c>
-      <c r="G291">
-        <v>0.03987019301915772</v>
-      </c>
-      <c r="H291">
-        <v>0.04016449977482824</v>
-      </c>
-      <c r="I291">
-        <v>0.6143067556705208</v>
-      </c>
-      <c r="J291">
-        <v>0.6490096509578859</v>
-      </c>
-      <c r="K291">
-        <v>20</v>
-      </c>
-      <c r="L291">
-        <v>26.89</v>
-      </c>
-      <c r="M291">
-        <v>20.7</v>
-      </c>
-      <c r="N291">
-        <v>26.73</v>
-      </c>
-      <c r="O291">
-        <v>1</v>
-      </c>
-      <c r="P291" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16">
-      <c r="A292" s="1">
-        <v>0</v>
-      </c>
-      <c r="B292" t="s">
-        <v>56</v>
-      </c>
-      <c r="C292">
-        <v>11.53224746086446</v>
-      </c>
-      <c r="D292" t="s">
-        <v>54</v>
-      </c>
-      <c r="E292">
-        <v>13.76730272629556</v>
-      </c>
-      <c r="F292">
-        <v>1</v>
-      </c>
-      <c r="G292">
-        <v>0.03714775253913554</v>
-      </c>
-      <c r="H292">
-        <v>0.04001269727370445</v>
-      </c>
-      <c r="I292">
-        <v>2.235055265431093</v>
-      </c>
-      <c r="J292">
-        <v>0.6561348636852222</v>
-      </c>
-      <c r="K292">
-        <v>19.52</v>
-      </c>
-      <c r="L292">
-        <v>24.34</v>
-      </c>
-      <c r="M292">
-        <v>20</v>
-      </c>
-      <c r="N292">
-        <v>26.89</v>
-      </c>
-      <c r="O292">
-        <v>1</v>
-      </c>
-      <c r="P292" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -340,7 +340,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-13</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15207,7 +15207,7 @@
         <v>108</v>
       </c>
       <c r="E284">
-        <v>21.95535282365687</v>
+        <v>21.39350321544016</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15216,10 +15216,10 @@
         <v>0.03182834639277654</v>
       </c>
       <c r="H284">
-        <v>0.03242464717634314</v>
+        <v>0.03156649678455984</v>
       </c>
       <c r="I284">
-        <v>-0.003699216433407315</v>
+        <v>0.5581503917832968</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15231,10 +15231,10 @@
         <v>26.89</v>
       </c>
       <c r="M284">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="N284">
-        <v>27.19</v>
+        <v>26.48</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15257,7 +15257,7 @@
         <v>108</v>
       </c>
       <c r="E285">
-        <v>21.95535282365687</v>
+        <v>21.39350321544016</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15266,10 +15266,10 @@
         <v>0.03235995544437925</v>
       </c>
       <c r="H285">
-        <v>0.03242464717634314</v>
+        <v>0.03156649678455984</v>
       </c>
       <c r="I285">
-        <v>-0.01530826803611873</v>
+        <v>0.5465413401805854</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15281,10 +15281,10 @@
         <v>27.15</v>
       </c>
       <c r="M285">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="N285">
-        <v>27.19</v>
+        <v>26.48</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15307,7 +15307,7 @@
         <v>108</v>
       </c>
       <c r="E286">
-        <v>21.95535282365687</v>
+        <v>21.39350321544016</v>
       </c>
       <c r="F286">
         <v>-1</v>
@@ -15316,10 +15316,10 @@
         <v>0.03252933890830702</v>
       </c>
       <c r="H286">
-        <v>0.03242464717634314</v>
+        <v>0.03156649678455984</v>
       </c>
       <c r="I286">
-        <v>0.05530826803611788</v>
+        <v>0.617157876252822</v>
       </c>
       <c r="J286">
         <v>0.246917319638827</v>
@@ -15331,10 +15331,10 @@
         <v>27.27</v>
       </c>
       <c r="M286">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="N286">
-        <v>27.19</v>
+        <v>26.48</v>
       </c>
       <c r="O286">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="225">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,171 +178,171 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
+    <t>2018-01-02</t>
+  </si>
+  <si>
+    <t>2018-01-03</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-01-22</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-07-23</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-10-10</t>
+  </si>
+  <si>
+    <t>2019-12-30</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>2021-02-09</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>2021-02-23</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-03-08</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>2021-03-11</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-10</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
-    <t>2018-01-02</t>
-  </si>
-  <si>
-    <t>2018-01-03</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-01-22</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-07-23</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-10-10</t>
-  </si>
-  <si>
-    <t>2019-12-30</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-02-09</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-02-23</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-09-14</t>
-  </si>
-  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -683,6 +683,9 @@
   </si>
   <si>
     <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-08-27</t>
@@ -1104,7 +1107,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1154,7 +1157,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1204,7 +1207,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1254,7 +1257,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1304,7 +1307,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1354,7 +1357,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1404,7 +1407,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1454,7 +1457,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1504,7 +1507,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1554,7 +1557,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1604,7 +1607,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1654,7 +1657,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1704,7 +1707,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1754,7 +1757,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1804,7 +1807,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1854,7 +1857,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1904,7 +1907,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1954,7 +1957,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2004,7 +2007,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2054,7 +2057,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2104,7 +2107,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2154,7 +2157,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2204,7 +2207,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2254,7 +2257,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2304,7 +2307,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2354,7 +2357,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2404,7 +2407,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2454,7 +2457,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2504,7 +2507,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2554,7 +2557,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2654,7 +2657,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2804,7 +2807,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2854,7 +2857,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2904,7 +2907,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2954,7 +2957,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3004,7 +3007,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3054,7 +3057,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3104,7 +3107,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3154,7 +3157,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3204,7 +3207,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3254,7 +3257,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3304,7 +3307,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3354,7 +3357,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3404,7 +3407,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3454,7 +3457,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3504,7 +3507,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3554,7 +3557,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3604,7 +3607,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3754,7 +3757,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3904,7 +3907,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -4054,7 +4057,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4154,7 +4157,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4254,7 +4257,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4354,7 +4357,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4454,7 +4457,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4554,7 +4557,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4604,7 +4607,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4704,7 +4707,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4754,7 +4757,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4854,7 +4857,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4904,7 +4907,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -5004,7 +5007,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5054,7 +5057,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5154,7 +5157,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5204,7 +5207,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5304,7 +5307,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5354,7 +5357,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5454,7 +5457,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5504,7 +5507,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5604,7 +5607,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5654,7 +5657,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5754,7 +5757,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5804,7 +5807,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5854,7 +5857,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5904,7 +5907,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5954,7 +5957,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6004,7 +6007,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6054,7 +6057,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6104,7 +6107,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6154,7 +6157,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6204,7 +6207,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6254,7 +6257,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6304,7 +6307,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6354,7 +6357,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6404,7 +6407,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6454,7 +6457,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6504,7 +6507,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6554,7 +6557,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6604,7 +6607,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6654,7 +6657,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6704,7 +6707,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6754,7 +6757,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6804,7 +6807,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6854,7 +6857,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6904,7 +6907,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6954,7 +6957,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7004,7 +7007,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7054,7 +7057,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7104,7 +7107,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7154,7 +7157,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7204,7 +7207,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7254,7 +7257,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7304,7 +7307,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7354,7 +7357,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7404,7 +7407,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7454,7 +7457,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7504,7 +7507,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7554,7 +7557,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7604,7 +7607,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7654,7 +7657,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7704,7 +7707,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7754,7 +7757,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7804,7 +7807,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7854,7 +7857,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7904,7 +7907,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7954,7 +7957,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8004,7 +8007,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8054,7 +8057,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8104,7 +8107,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8154,7 +8157,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8204,7 +8207,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8254,7 +8257,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8304,7 +8307,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8354,7 +8357,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8404,7 +8407,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8454,7 +8457,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8504,7 +8507,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8554,7 +8557,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8604,7 +8607,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8654,7 +8657,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8704,7 +8707,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8754,7 +8757,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8804,7 +8807,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8854,7 +8857,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8904,7 +8907,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8954,7 +8957,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8990,7 +8993,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9004,7 +9007,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9040,7 +9043,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9054,7 +9057,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9090,7 +9093,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9104,7 +9107,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9154,7 +9157,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9204,7 +9207,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9254,7 +9257,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9304,7 +9307,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9354,7 +9357,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9404,7 +9407,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9454,7 +9457,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9504,7 +9507,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9554,7 +9557,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9604,7 +9607,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9654,7 +9657,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9704,7 +9707,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9754,7 +9757,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9804,7 +9807,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9854,7 +9857,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9904,7 +9907,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9954,7 +9957,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10004,7 +10007,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10054,7 +10057,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10104,7 +10107,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10154,7 +10157,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10204,7 +10207,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10254,7 +10257,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10304,7 +10307,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10354,7 +10357,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10404,7 +10407,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10454,7 +10457,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10504,7 +10507,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10554,7 +10557,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10604,7 +10607,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10654,7 +10657,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10704,7 +10707,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10754,7 +10757,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10904,7 +10907,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -11054,7 +11057,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11204,7 +11207,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11304,7 +11307,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11354,7 +11357,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11454,7 +11457,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11504,7 +11507,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11604,7 +11607,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11654,7 +11657,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11754,7 +11757,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11804,7 +11807,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11904,7 +11907,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11954,7 +11957,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12054,7 +12057,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12104,7 +12107,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12204,7 +12207,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12254,7 +12257,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12354,7 +12357,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12454,7 +12457,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12554,7 +12557,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12654,7 +12657,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12754,7 +12757,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12904,7 +12907,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12954,7 +12957,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13004,7 +13007,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13054,7 +13057,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13104,7 +13107,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13154,7 +13157,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13204,7 +13207,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13254,7 +13257,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13304,7 +13307,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13354,7 +13357,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13404,7 +13407,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13454,7 +13457,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13504,7 +13507,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13554,7 +13557,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13604,7 +13607,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13654,7 +13657,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13704,7 +13707,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13754,7 +13757,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13804,7 +13807,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13854,7 +13857,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13904,7 +13907,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13954,7 +13957,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14004,7 +14007,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14054,7 +14057,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14104,7 +14107,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14154,7 +14157,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14204,7 +14207,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14254,7 +14257,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14304,7 +14307,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14354,7 +14357,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14404,7 +14407,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14454,7 +14457,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14504,7 +14507,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14590,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14640,7 +14643,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14690,7 +14693,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14790,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14804,7 +14807,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14840,7 +14843,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14854,7 +14857,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14890,7 +14893,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14904,7 +14907,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14954,7 +14957,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15004,7 +15007,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15054,7 +15057,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15090,7 +15093,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15104,7 +15107,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15154,7 +15157,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15201,40 +15204,40 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>21.95165360722346</v>
+        <v>22.06523254534987</v>
       </c>
       <c r="D284" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E284">
-        <v>21.39350321544016</v>
+        <v>21.32140699279456</v>
       </c>
       <c r="F284">
         <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.03182834639277654</v>
+        <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.03156649678455984</v>
+        <v>0.03115859300720543</v>
       </c>
       <c r="I284">
-        <v>0.5581503917832968</v>
+        <v>0.7438255525553075</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
       </c>
       <c r="K284">
-        <v>20</v>
+        <v>20.35</v>
       </c>
       <c r="L284">
-        <v>26.89</v>
+        <v>27.09</v>
       </c>
       <c r="M284">
-        <v>20.6</v>
+        <v>19.92</v>
       </c>
       <c r="N284">
-        <v>26.48</v>
+        <v>26.24</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15251,40 +15254,40 @@
         <v>55</v>
       </c>
       <c r="C285">
-        <v>21.94004455562075</v>
+        <v>22.01066109169298</v>
       </c>
       <c r="D285" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E285">
-        <v>21.39350321544016</v>
+        <v>21.32140699279456</v>
       </c>
       <c r="F285">
         <v>-1</v>
       </c>
       <c r="G285">
-        <v>0.03235995544437925</v>
+        <v>0.03252933890830702</v>
       </c>
       <c r="H285">
-        <v>0.03156649678455984</v>
+        <v>0.03115859300720543</v>
       </c>
       <c r="I285">
-        <v>0.5465413401805854</v>
+        <v>0.6892540988984202</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
       </c>
       <c r="K285">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="L285">
-        <v>27.15</v>
+        <v>27.27</v>
       </c>
       <c r="M285">
-        <v>20.6</v>
+        <v>19.92</v>
       </c>
       <c r="N285">
-        <v>26.48</v>
+        <v>26.24</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15295,52 +15298,52 @@
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B286" t="s">
         <v>56</v>
       </c>
       <c r="C286">
-        <v>22.01066109169298</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D286" t="s">
         <v>108</v>
       </c>
       <c r="E286">
-        <v>21.39350321544016</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F286">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G286">
-        <v>0.03252933890830702</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H286">
-        <v>0.03156649678455984</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I286">
-        <v>0.617157876252822</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J286">
-        <v>0.246917319638827</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K286">
-        <v>21.3</v>
+        <v>19.52</v>
       </c>
       <c r="L286">
-        <v>27.27</v>
+        <v>24.34</v>
       </c>
       <c r="M286">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="N286">
-        <v>26.48</v>
+        <v>26.89</v>
       </c>
       <c r="O286">
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15348,13 +15351,13 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C287">
         <v>11.53224746086446</v>
       </c>
       <c r="D287" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="E287">
         <v>13.76730272629556</v>
@@ -15390,7 +15393,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -337,7 +337,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-15</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-01</t>
@@ -15210,7 +15210,7 @@
         <v>107</v>
       </c>
       <c r="E284">
-        <v>21.32140699279456</v>
+        <v>20.56140699279457</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15219,10 +15219,10 @@
         <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.03115859300720543</v>
+        <v>0.03039859300720544</v>
       </c>
       <c r="I284">
-        <v>0.7438255525553075</v>
+        <v>1.503825552555305</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15237,7 +15237,7 @@
         <v>19.92</v>
       </c>
       <c r="N284">
-        <v>26.24</v>
+        <v>25.48</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15260,7 +15260,7 @@
         <v>107</v>
       </c>
       <c r="E285">
-        <v>21.32140699279456</v>
+        <v>20.56140699279457</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15269,10 +15269,10 @@
         <v>0.03252933890830702</v>
       </c>
       <c r="H285">
-        <v>0.03115859300720543</v>
+        <v>0.03039859300720544</v>
       </c>
       <c r="I285">
-        <v>0.6892540988984202</v>
+        <v>1.449254098898418</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15287,7 +15287,7 @@
         <v>19.92</v>
       </c>
       <c r="N285">
-        <v>26.24</v>
+        <v>25.48</v>
       </c>
       <c r="O285">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -187,6 +187,9 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -337,7 +340,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2021-09-01</t>
@@ -1046,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P287"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1107,7 +1110,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1143,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1157,7 +1160,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1193,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1207,7 +1210,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1243,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1257,7 +1260,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1293,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1307,7 +1310,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1343,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1357,7 +1360,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1393,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1407,7 +1410,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1443,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1457,7 +1460,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1493,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1507,7 +1510,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1543,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1557,7 +1560,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1593,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1607,7 +1610,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1643,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1657,7 +1660,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1693,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1707,7 +1710,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1743,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1757,7 +1760,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1793,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1807,7 +1810,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1843,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1857,7 +1860,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1893,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1907,7 +1910,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1943,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1957,7 +1960,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1993,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2007,7 +2010,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2043,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2057,7 +2060,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2093,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2107,7 +2110,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2143,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2157,7 +2160,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2193,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2207,7 +2210,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2243,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2257,7 +2260,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2293,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2307,7 +2310,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2343,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2357,7 +2360,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2393,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2407,7 +2410,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2443,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2457,7 +2460,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2493,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2507,7 +2510,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2543,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2557,7 +2560,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2593,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2643,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2657,7 +2660,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2693,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2743,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2793,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2807,7 +2810,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2843,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2857,7 +2860,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2893,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2907,7 +2910,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2943,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2957,7 +2960,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2993,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3007,7 +3010,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3043,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3057,7 +3060,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3093,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3107,7 +3110,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3143,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3157,7 +3160,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3193,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3207,7 +3210,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3243,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3257,7 +3260,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3293,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3307,7 +3310,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3343,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3357,7 +3360,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3393,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3407,7 +3410,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3443,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3457,7 +3460,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3493,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3507,7 +3510,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3543,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3557,7 +3560,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3593,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3607,7 +3610,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3643,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3693,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3743,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3757,7 +3760,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3793,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3843,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3893,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3907,7 +3910,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3943,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3993,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4043,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4057,7 +4060,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4093,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4143,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4157,7 +4160,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4193,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4243,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4257,7 +4260,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4293,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4343,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4357,7 +4360,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4393,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4443,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4457,7 +4460,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4493,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4543,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4557,7 +4560,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4593,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4607,7 +4610,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4643,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4693,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4707,7 +4710,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4743,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4757,7 +4760,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4793,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4843,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4857,7 +4860,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4893,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4907,7 +4910,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4943,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4993,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5007,7 +5010,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5043,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5057,7 +5060,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5093,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5143,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5157,7 +5160,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5193,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5207,7 +5210,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5243,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5293,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5307,7 +5310,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5343,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5357,7 +5360,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5393,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5443,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5457,7 +5460,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5493,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5507,7 +5510,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5543,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5593,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5607,7 +5610,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5643,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5657,7 +5660,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5693,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5743,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5757,7 +5760,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5793,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5807,7 +5810,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5843,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5857,7 +5860,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5893,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5907,7 +5910,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5943,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5957,7 +5960,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5993,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6007,7 +6010,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6043,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6057,7 +6060,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6093,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6107,7 +6110,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6143,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6157,7 +6160,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6193,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6207,7 +6210,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6243,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6257,7 +6260,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6293,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6307,7 +6310,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6343,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6357,7 +6360,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6393,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6407,7 +6410,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6443,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6457,7 +6460,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6493,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6507,7 +6510,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6543,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6557,7 +6560,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6593,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6607,7 +6610,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6643,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6657,7 +6660,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6693,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6707,7 +6710,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6743,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6757,7 +6760,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6793,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6807,7 +6810,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6843,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6857,7 +6860,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6893,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6907,7 +6910,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6943,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6957,7 +6960,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6993,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7007,7 +7010,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7043,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7057,7 +7060,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7093,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7107,7 +7110,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7143,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7157,7 +7160,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7193,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7207,7 +7210,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7243,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7257,7 +7260,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7293,7 +7296,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7307,7 +7310,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7343,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7357,7 +7360,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7393,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7407,7 +7410,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7443,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7457,7 +7460,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7493,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7507,7 +7510,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7543,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7557,7 +7560,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7593,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7607,7 +7610,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7643,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7657,7 +7660,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7693,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7707,7 +7710,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7743,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7757,7 +7760,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7793,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7807,7 +7810,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7843,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7857,7 +7860,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7893,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7907,7 +7910,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7943,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7957,7 +7960,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7993,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8007,7 +8010,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8043,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8057,7 +8060,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8093,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8107,7 +8110,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8143,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8157,7 +8160,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8193,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8207,7 +8210,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8243,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8257,7 +8260,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8293,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8307,7 +8310,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8343,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8357,7 +8360,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8393,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8407,7 +8410,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8443,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8457,7 +8460,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8493,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8507,7 +8510,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8543,7 +8546,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8557,7 +8560,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8593,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8607,7 +8610,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8643,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8657,7 +8660,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8693,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8707,7 +8710,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8743,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8757,7 +8760,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8793,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8807,7 +8810,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8843,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8857,7 +8860,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8893,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8907,7 +8910,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8957,7 +8960,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8993,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9007,7 +9010,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9043,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9057,7 +9060,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9093,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9107,7 +9110,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9143,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9157,7 +9160,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9193,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9207,7 +9210,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9243,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9257,7 +9260,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9293,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9307,7 +9310,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9343,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9357,7 +9360,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9393,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9407,7 +9410,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9443,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9457,7 +9460,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9493,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9507,7 +9510,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9543,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9557,7 +9560,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9593,7 +9596,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9607,7 +9610,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9643,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9657,7 +9660,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9693,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9707,7 +9710,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9743,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9757,7 +9760,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9793,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9807,7 +9810,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9843,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9857,7 +9860,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9893,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9907,7 +9910,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9943,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9957,7 +9960,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9993,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10007,7 +10010,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10043,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10057,7 +10060,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10093,7 +10096,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10107,7 +10110,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10143,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10157,7 +10160,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10193,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10207,7 +10210,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10243,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10257,7 +10260,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10293,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10307,7 +10310,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10343,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10357,7 +10360,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10393,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10407,7 +10410,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10443,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10457,7 +10460,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10493,7 +10496,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10507,7 +10510,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10543,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10557,7 +10560,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10593,7 +10596,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10607,7 +10610,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10643,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10657,7 +10660,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10693,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10707,7 +10710,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10743,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10757,7 +10760,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10793,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10843,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10893,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10907,7 +10910,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10943,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10993,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11043,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11057,7 +11060,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11093,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11143,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11193,7 +11196,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11207,7 +11210,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11243,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11293,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11307,7 +11310,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11343,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11357,7 +11360,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11393,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11443,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11457,7 +11460,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11493,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11507,7 +11510,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11543,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11593,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11607,7 +11610,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11643,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11657,7 +11660,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11693,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11743,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11757,7 +11760,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11793,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11807,7 +11810,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11843,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11893,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11907,7 +11910,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11943,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11957,7 +11960,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11993,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12043,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12057,7 +12060,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12093,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12107,7 +12110,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12143,7 +12146,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12193,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12207,7 +12210,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12243,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12257,7 +12260,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12293,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12343,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12357,7 +12360,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12393,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12443,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12457,7 +12460,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12493,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12543,7 +12546,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12557,7 +12560,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12593,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12643,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12657,7 +12660,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12693,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12743,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12757,7 +12760,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12793,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12843,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12893,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12907,7 +12910,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12943,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12957,7 +12960,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12993,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13007,7 +13010,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13043,7 +13046,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13057,7 +13060,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13093,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13107,7 +13110,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13143,7 +13146,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13157,7 +13160,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13193,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13207,7 +13210,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13243,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13257,7 +13260,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13293,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13307,7 +13310,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13343,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13357,7 +13360,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13393,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13407,7 +13410,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13443,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13457,7 +13460,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13493,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13507,7 +13510,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13543,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13557,7 +13560,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13593,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13607,7 +13610,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13643,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13657,7 +13660,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13693,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13707,7 +13710,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13743,7 +13746,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13757,7 +13760,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13793,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13807,7 +13810,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13857,7 +13860,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13907,7 +13910,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13957,7 +13960,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13993,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14007,7 +14010,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14043,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14057,7 +14060,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14093,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14107,7 +14110,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14143,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14157,7 +14160,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14193,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14207,7 +14210,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14243,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14257,7 +14260,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14293,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14307,7 +14310,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14343,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14357,7 +14360,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14393,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14407,7 +14410,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14443,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14457,7 +14460,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14493,7 +14496,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14507,7 +14510,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14543,7 +14546,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14593,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14643,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14693,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14743,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14793,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14807,7 +14810,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14843,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14857,7 +14860,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14893,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14907,7 +14910,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14943,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14957,7 +14960,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14993,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15007,7 +15010,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15043,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15057,7 +15060,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15093,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15107,7 +15110,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15143,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15157,7 +15160,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15193,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15207,10 +15210,10 @@
         <v>22.06523254534987</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E284">
-        <v>20.56140699279457</v>
+        <v>20.97461600927764</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15219,10 +15222,10 @@
         <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.03039859300720544</v>
+        <v>0.03092538399072236</v>
       </c>
       <c r="I284">
-        <v>1.503825552555305</v>
+        <v>1.090616536072236</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15234,16 +15237,16 @@
         <v>27.09</v>
       </c>
       <c r="M284">
-        <v>19.92</v>
+        <v>20.15</v>
       </c>
       <c r="N284">
-        <v>25.48</v>
+        <v>25.95</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15257,10 +15260,10 @@
         <v>22.01066109169298</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E285">
-        <v>20.56140699279457</v>
+        <v>20.97461600927764</v>
       </c>
       <c r="F285">
         <v>-1</v>
@@ -15269,10 +15272,10 @@
         <v>0.03252933890830702</v>
       </c>
       <c r="H285">
-        <v>0.03039859300720544</v>
+        <v>0.03092538399072236</v>
       </c>
       <c r="I285">
-        <v>1.449254098898418</v>
+        <v>1.036045082415349</v>
       </c>
       <c r="J285">
         <v>0.246917319638827</v>
@@ -15284,16 +15287,16 @@
         <v>27.27</v>
       </c>
       <c r="M285">
-        <v>19.92</v>
+        <v>20.15</v>
       </c>
       <c r="N285">
-        <v>25.48</v>
+        <v>25.95</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15307,7 +15310,7 @@
         <v>11.3975321062961</v>
       </c>
       <c r="D286" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E286">
         <v>13.62927469907388</v>
@@ -15343,7 +15346,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15357,7 +15360,7 @@
         <v>11.53224746086446</v>
       </c>
       <c r="D287" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E287">
         <v>13.76730272629556</v>
@@ -15393,7 +15396,57 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>224</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>57</v>
+      </c>
+      <c r="C288">
+        <v>12.35558584102549</v>
+      </c>
+      <c r="D288" t="s">
+        <v>108</v>
+      </c>
+      <c r="E288">
+        <v>12.67404893055541</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>0.03860441415897451</v>
+      </c>
+      <c r="H288">
+        <v>0.03922595106944459</v>
+      </c>
+      <c r="I288">
+        <v>0.3184630895299136</v>
+      </c>
+      <c r="J288">
+        <v>0.6588561324786399</v>
+      </c>
+      <c r="K288">
+        <v>19.92</v>
+      </c>
+      <c r="L288">
+        <v>25.48</v>
+      </c>
+      <c r="M288">
+        <v>20.15</v>
+      </c>
+      <c r="N288">
+        <v>25.95</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -181,9 +181,6 @@
     <t>2021-09-02</t>
   </si>
   <si>
-    <t>2021-09-10</t>
-  </si>
-  <si>
     <t>2021-08-30</t>
   </si>
   <si>
@@ -340,7 +337,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-17</t>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-09-01</t>
@@ -686,6 +683,9 @@
   </si>
   <si>
     <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2021-08-26</t>
@@ -1110,7 +1110,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1160,7 +1160,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1196,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1210,7 +1210,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1260,7 +1260,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1310,7 +1310,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1346,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1360,7 +1360,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1410,7 +1410,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1460,7 +1460,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1510,7 +1510,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1560,7 +1560,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1610,7 +1610,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1646,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1660,7 +1660,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1710,7 +1710,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1760,7 +1760,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1810,7 +1810,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1860,7 +1860,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1896,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1910,7 +1910,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1946,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1960,7 +1960,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1996,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2010,7 +2010,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2046,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2060,7 +2060,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2096,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2110,7 +2110,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2146,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2160,7 +2160,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2210,7 +2210,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2260,7 +2260,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2310,7 +2310,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2360,7 +2360,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2396,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2410,7 +2410,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2446,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2460,7 +2460,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2510,7 +2510,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2546,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2560,7 +2560,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2660,7 +2660,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,7 +2810,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2846,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2860,7 +2860,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2910,7 +2910,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2946,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2960,7 +2960,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2996,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3010,7 +3010,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3046,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3060,7 +3060,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3096,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3110,7 +3110,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3160,7 +3160,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3196,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3210,7 +3210,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3246,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3260,7 +3260,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3296,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3310,7 +3310,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3346,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3360,7 +3360,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3396,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3410,7 +3410,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3460,7 +3460,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3496,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3510,7 +3510,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3546,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3560,7 +3560,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3610,7 +3610,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3646,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3760,7 +3760,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3796,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3910,7 +3910,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3946,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4060,7 +4060,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4096,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4160,7 +4160,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4196,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4260,7 +4260,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4296,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4360,7 +4360,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4460,7 +4460,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4496,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4560,7 +4560,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4596,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4610,7 +4610,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4646,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4710,7 +4710,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4746,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4760,7 +4760,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4860,7 +4860,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4896,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4910,7 +4910,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4946,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5010,7 +5010,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5060,7 +5060,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5096,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5160,7 +5160,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5196,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5210,7 +5210,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5246,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5310,7 +5310,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5346,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5360,7 +5360,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5396,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5460,7 +5460,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5496,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5510,7 +5510,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5546,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5610,7 +5610,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5646,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5660,7 +5660,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5696,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5760,7 +5760,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5810,7 +5810,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5860,7 +5860,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5896,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5910,7 +5910,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5946,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5960,7 +5960,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5996,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6010,7 +6010,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6046,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6060,7 +6060,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6096,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6110,7 +6110,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6160,7 +6160,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6196,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6210,7 +6210,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6246,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6260,7 +6260,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6296,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6310,7 +6310,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6346,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6360,7 +6360,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6410,7 +6410,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6446,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6460,7 +6460,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6510,7 +6510,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6546,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6560,7 +6560,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6596,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6610,7 +6610,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6646,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6660,7 +6660,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6710,7 +6710,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6746,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6760,7 +6760,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6796,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6810,7 +6810,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6846,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6860,7 +6860,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6896,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6910,7 +6910,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6946,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,7 +6960,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6996,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7010,7 +7010,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7046,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7060,7 +7060,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7096,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7110,7 +7110,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7146,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,7 +7160,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7196,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7210,7 +7210,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7246,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7260,7 +7260,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7296,7 +7296,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7310,7 +7310,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7346,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7360,7 +7360,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7396,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7410,7 +7410,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7446,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7460,7 +7460,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7496,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7510,7 +7510,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7546,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7560,7 +7560,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7596,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7610,7 +7610,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7646,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7660,7 +7660,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7696,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7710,7 +7710,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7746,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7760,7 +7760,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7810,7 +7810,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7846,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7860,7 +7860,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7896,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7910,7 +7910,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7946,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7960,7 +7960,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7996,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8010,7 +8010,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8046,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8060,7 +8060,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8110,7 +8110,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8146,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8160,7 +8160,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8196,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8210,7 +8210,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8246,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8260,7 +8260,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8296,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8310,7 +8310,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8346,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8360,7 +8360,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8396,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8410,7 +8410,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8446,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8460,7 +8460,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8496,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8510,7 +8510,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8546,7 +8546,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8560,7 +8560,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8596,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8610,7 +8610,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8646,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8660,7 +8660,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8696,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8710,7 +8710,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8746,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8760,7 +8760,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8796,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8810,7 +8810,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8846,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8860,7 +8860,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8896,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8910,7 +8910,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8960,7 +8960,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8996,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9010,7 +9010,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9046,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9060,7 +9060,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9096,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9110,7 +9110,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9146,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9160,7 +9160,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9210,7 +9210,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9246,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9260,7 +9260,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9296,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9310,7 +9310,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9360,7 +9360,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9396,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9410,7 +9410,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9446,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9460,7 +9460,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9496,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9510,7 +9510,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9546,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9560,7 +9560,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9596,7 +9596,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9610,7 +9610,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9646,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9660,7 +9660,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9696,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9710,7 +9710,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9746,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9760,7 +9760,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9810,7 +9810,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9846,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9860,7 +9860,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9896,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9910,7 +9910,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9946,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9960,7 +9960,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9996,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10010,7 +10010,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10046,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10060,7 +10060,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10096,7 +10096,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10110,7 +10110,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10146,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10160,7 +10160,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10196,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10210,7 +10210,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10246,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10260,7 +10260,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10296,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10310,7 +10310,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10346,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10360,7 +10360,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10396,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10410,7 +10410,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10460,7 +10460,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10496,7 +10496,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10510,7 +10510,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10546,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10560,7 +10560,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10596,7 +10596,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10610,7 +10610,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10646,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10660,7 +10660,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10696,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10710,7 +10710,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10746,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10760,7 +10760,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10796,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10910,7 +10910,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10946,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11060,7 +11060,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11096,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11196,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11210,7 +11210,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11246,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11310,7 +11310,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11346,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11360,7 +11360,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11460,7 +11460,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11496,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11510,7 +11510,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11546,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11610,7 +11610,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11646,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11660,7 +11660,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11696,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11760,7 +11760,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11796,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11810,7 +11810,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11846,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11910,7 +11910,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11946,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11960,7 +11960,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11996,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12060,7 +12060,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12096,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12110,7 +12110,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12146,7 +12146,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12210,7 +12210,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12246,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12260,7 +12260,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12296,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12360,7 +12360,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12396,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12460,7 +12460,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12496,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12546,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12560,7 +12560,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12596,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12660,7 +12660,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12696,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12760,7 +12760,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12796,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12910,7 +12910,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12946,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12960,7 +12960,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12996,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13010,7 +13010,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13046,7 +13046,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13060,7 +13060,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13096,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13110,7 +13110,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13146,7 +13146,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13160,7 +13160,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13196,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13210,7 +13210,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13246,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13260,7 +13260,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13296,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13310,7 +13310,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13346,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13360,7 +13360,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13396,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13410,7 +13410,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13446,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13460,7 +13460,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13496,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13510,7 +13510,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13546,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13560,7 +13560,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13596,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13610,7 +13610,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13646,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13660,7 +13660,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13696,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13710,7 +13710,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13746,7 +13746,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13760,7 +13760,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13796,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13810,7 +13810,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13860,7 +13860,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13910,7 +13910,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13960,7 +13960,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13996,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14010,7 +14010,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14046,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14060,7 +14060,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14096,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14110,7 +14110,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14146,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14160,7 +14160,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14196,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14210,7 +14210,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14246,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14260,7 +14260,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14296,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14310,7 +14310,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14346,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14360,7 +14360,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14396,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14410,7 +14410,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14446,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14460,7 +14460,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14496,7 +14496,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14510,7 +14510,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14546,7 +14546,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14596,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14646,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14696,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14746,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14796,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14810,7 +14810,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14846,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14860,7 +14860,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14896,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14910,7 +14910,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14946,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14960,7 +14960,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14996,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15010,7 +15010,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15046,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15060,7 +15060,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15096,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15110,7 +15110,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15146,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15160,7 +15160,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15196,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15210,10 +15210,10 @@
         <v>22.06523254534987</v>
       </c>
       <c r="D284" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E284">
-        <v>20.97461600927764</v>
+        <v>21.28634533918734</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15222,10 +15222,10 @@
         <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.03092538399072236</v>
+        <v>0.03111365466081266</v>
       </c>
       <c r="I284">
-        <v>1.090616536072236</v>
+        <v>0.7788872061625298</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15237,60 +15237,60 @@
         <v>27.09</v>
       </c>
       <c r="M284">
-        <v>20.15</v>
+        <v>19.9</v>
       </c>
       <c r="N284">
-        <v>25.95</v>
+        <v>26.2</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285">
-        <v>22.01066109169298</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D285" t="s">
         <v>108</v>
       </c>
       <c r="E285">
-        <v>20.97461600927764</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F285">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03252933890830702</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H285">
-        <v>0.03092538399072236</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I285">
-        <v>1.036045082415349</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J285">
-        <v>0.246917319638827</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K285">
-        <v>21.3</v>
+        <v>19.52</v>
       </c>
       <c r="L285">
-        <v>27.27</v>
+        <v>24.34</v>
       </c>
       <c r="M285">
-        <v>20.15</v>
+        <v>20</v>
       </c>
       <c r="N285">
-        <v>25.95</v>
+        <v>26.89</v>
       </c>
       <c r="O285">
         <v>1</v>
@@ -15304,13 +15304,13 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C286">
         <v>11.3975321062961</v>
       </c>
       <c r="D286" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E286">
         <v>13.62927469907388</v>
@@ -15354,13 +15354,13 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C287">
         <v>11.53224746086446</v>
       </c>
       <c r="D287" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E287">
         <v>13.76730272629556</v>
@@ -15404,16 +15404,16 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C288">
         <v>12.35558584102549</v>
       </c>
       <c r="D288" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E288">
-        <v>12.67404893055541</v>
+        <v>13.08876296367507</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -15422,10 +15422,10 @@
         <v>0.03860441415897451</v>
       </c>
       <c r="H288">
-        <v>0.03922595106944459</v>
+        <v>0.03931123703632493</v>
       </c>
       <c r="I288">
-        <v>0.3184630895299136</v>
+        <v>0.7331771226495736</v>
       </c>
       <c r="J288">
         <v>0.6588561324786399</v>
@@ -15437,16 +15437,16 @@
         <v>25.48</v>
       </c>
       <c r="M288">
-        <v>20.15</v>
+        <v>19.9</v>
       </c>
       <c r="N288">
-        <v>25.95</v>
+        <v>26.2</v>
       </c>
       <c r="O288">
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="223">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,15 +178,9 @@
     <t>2021-04-01</t>
   </si>
   <si>
-    <t>2021-09-02</t>
-  </si>
-  <si>
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-09-16</t>
-  </si>
-  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -337,9 +331,6 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
     <t>2021-09-01</t>
   </si>
   <si>
@@ -682,7 +673,7 @@
     <t>2020-09-17</t>
   </si>
   <si>
-    <t>2021-06-30</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -1049,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1110,7 +1101,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1146,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1160,7 +1151,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1196,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1210,7 +1201,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1246,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1260,7 +1251,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1296,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1310,7 +1301,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1346,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1360,7 +1351,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1396,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1410,7 +1401,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1446,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1460,7 +1451,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1496,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1510,7 +1501,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1546,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1560,7 +1551,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1596,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1610,7 +1601,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1646,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1660,7 +1651,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1696,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1710,7 +1701,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1746,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1760,7 +1751,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1796,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1810,7 +1801,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1846,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1860,7 +1851,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1896,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1910,7 +1901,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1946,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1960,7 +1951,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1996,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2010,7 +2001,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2046,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2060,7 +2051,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2096,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2110,7 +2101,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2146,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2160,7 +2151,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2196,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2210,7 +2201,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2246,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2260,7 +2251,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2296,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2310,7 +2301,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2346,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2360,7 +2351,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2396,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2410,7 +2401,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2446,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2460,7 +2451,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2496,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2510,7 +2501,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2546,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2560,7 +2551,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2596,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2660,7 +2651,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2696,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,7 +2801,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2846,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2860,7 +2851,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2896,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2910,7 +2901,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2946,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2960,7 +2951,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2996,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3010,7 +3001,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3046,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3060,7 +3051,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3096,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3110,7 +3101,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3146,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3160,7 +3151,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3196,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3210,7 +3201,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3246,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3260,7 +3251,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3296,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3310,7 +3301,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3346,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3360,7 +3351,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3396,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3410,7 +3401,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3446,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3460,7 +3451,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3496,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3510,7 +3501,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3546,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3560,7 +3551,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3596,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3610,7 +3601,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3646,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3760,7 +3751,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3796,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3910,7 +3901,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3946,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4060,7 +4051,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4096,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4160,7 +4151,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4196,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4260,7 +4251,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4296,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4360,7 +4351,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4396,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4460,7 +4451,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4496,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4560,7 +4551,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4596,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4610,7 +4601,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4646,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4710,7 +4701,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4746,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4760,7 +4751,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4796,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4860,7 +4851,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4896,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4910,7 +4901,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4946,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5010,7 +5001,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5046,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5060,7 +5051,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5096,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5160,7 +5151,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5196,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5210,7 +5201,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5246,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5310,7 +5301,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5346,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5360,7 +5351,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5396,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5460,7 +5451,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5496,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5510,7 +5501,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5546,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5610,7 +5601,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5646,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5660,7 +5651,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5696,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5760,7 +5751,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5796,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5810,7 +5801,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5846,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5860,7 +5851,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5896,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5910,7 +5901,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5946,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5960,7 +5951,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5996,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6010,7 +6001,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6046,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6060,7 +6051,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6096,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6110,7 +6101,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6146,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6160,7 +6151,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6196,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6210,7 +6201,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6246,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6260,7 +6251,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6296,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6310,7 +6301,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6346,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6360,7 +6351,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6396,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6410,7 +6401,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6446,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6460,7 +6451,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6496,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6510,7 +6501,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6546,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6560,7 +6551,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6596,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6610,7 +6601,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6646,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6660,7 +6651,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6696,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6710,7 +6701,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6746,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6760,7 +6751,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6796,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6810,7 +6801,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6846,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6860,7 +6851,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6896,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6910,7 +6901,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6946,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,7 +6951,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6996,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7010,7 +7001,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7046,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7060,7 +7051,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7096,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7110,7 +7101,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7146,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,7 +7151,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7196,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7210,7 +7201,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7246,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7260,7 +7251,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7296,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7310,7 +7301,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7346,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7360,7 +7351,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7396,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7410,7 +7401,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7446,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7460,7 +7451,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7496,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7510,7 +7501,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7546,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7560,7 +7551,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7596,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7610,7 +7601,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7646,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7660,7 +7651,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7696,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7710,7 +7701,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7746,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7760,7 +7751,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7796,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7810,7 +7801,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7846,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7860,7 +7851,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7896,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7910,7 +7901,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7946,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7960,7 +7951,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7996,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8010,7 +8001,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8046,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8060,7 +8051,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8096,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8110,7 +8101,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8146,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8160,7 +8151,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8196,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8210,7 +8201,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8246,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8260,7 +8251,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8296,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8310,7 +8301,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8346,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8360,7 +8351,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8396,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8410,7 +8401,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8446,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8460,7 +8451,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8496,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8510,7 +8501,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8546,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8560,7 +8551,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8596,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8610,7 +8601,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8646,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8660,7 +8651,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8696,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8710,7 +8701,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8746,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8760,7 +8751,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8796,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8810,7 +8801,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8846,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8860,7 +8851,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8896,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8910,7 +8901,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8960,7 +8951,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8996,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9010,7 +9001,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9046,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9060,7 +9051,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9096,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9110,7 +9101,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9146,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9160,7 +9151,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9196,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9210,7 +9201,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9246,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9260,7 +9251,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9296,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9310,7 +9301,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9346,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9360,7 +9351,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9396,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9410,7 +9401,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9446,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9460,7 +9451,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9496,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9510,7 +9501,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9546,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9560,7 +9551,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9596,7 +9587,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9610,7 +9601,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9646,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9660,7 +9651,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9696,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9710,7 +9701,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9746,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9760,7 +9751,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9796,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9810,7 +9801,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9846,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9860,7 +9851,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9896,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9910,7 +9901,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9946,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9960,7 +9951,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9996,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10010,7 +10001,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10046,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10060,7 +10051,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10096,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10110,7 +10101,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10146,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10160,7 +10151,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10196,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10210,7 +10201,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10246,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10260,7 +10251,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10296,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10310,7 +10301,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10346,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10360,7 +10351,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10396,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10410,7 +10401,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10446,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10460,7 +10451,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10496,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10510,7 +10501,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10546,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10560,7 +10551,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10596,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10610,7 +10601,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10646,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10660,7 +10651,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10696,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10710,7 +10701,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10746,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10760,7 +10751,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10796,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10887,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10910,7 +10901,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10946,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11060,7 +11051,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11096,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11210,7 +11201,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11246,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11310,7 +11301,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11346,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11360,7 +11351,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11396,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11437,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11460,7 +11451,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11496,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11510,7 +11501,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11546,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11610,7 +11601,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11646,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11660,7 +11651,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11696,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11737,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11760,7 +11751,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11796,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11810,7 +11801,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11846,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11910,7 +11901,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11946,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11960,7 +11951,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11996,7 +11987,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12060,7 +12051,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12096,7 +12087,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12110,7 +12101,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12146,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12210,7 +12201,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12246,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12260,7 +12251,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12296,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12360,7 +12351,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12396,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12437,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12460,7 +12451,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12496,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12560,7 +12551,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12596,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12660,7 +12651,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12696,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12760,7 +12751,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12796,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12910,7 +12901,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12946,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12960,7 +12951,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12996,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13010,7 +13001,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13046,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13060,7 +13051,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13096,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13110,7 +13101,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13146,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13160,7 +13151,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13196,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13210,7 +13201,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13246,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13260,7 +13251,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13296,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13310,7 +13301,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13346,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13360,7 +13351,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13396,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13410,7 +13401,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13446,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13460,7 +13451,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13496,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13510,7 +13501,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13546,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13560,7 +13551,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13596,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13610,7 +13601,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13646,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13660,7 +13651,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13696,7 +13687,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13710,7 +13701,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13746,7 +13737,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13760,7 +13751,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13796,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13810,7 +13801,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13860,7 +13851,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13910,7 +13901,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13960,7 +13951,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13996,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14010,7 +14001,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14046,7 +14037,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14060,7 +14051,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14096,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14110,7 +14101,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14146,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14160,7 +14151,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14196,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14210,7 +14201,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14246,7 +14237,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14260,7 +14251,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14296,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14310,7 +14301,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14346,7 +14337,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14360,7 +14351,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14396,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14410,7 +14401,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14446,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14460,7 +14451,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14496,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14510,7 +14501,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14546,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14596,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14646,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14696,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14746,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14796,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14810,7 +14801,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14846,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14860,7 +14851,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14896,7 +14887,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14910,7 +14901,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14946,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14960,7 +14951,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14996,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15010,7 +15001,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15046,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15060,7 +15051,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15096,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15110,7 +15101,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15146,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15160,7 +15151,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15196,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15207,46 +15198,46 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>22.06523254534987</v>
+        <v>11.22473879933428</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E284">
-        <v>21.28634533918734</v>
+        <v>13.45223237636709</v>
       </c>
       <c r="F284">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G284">
-        <v>0.03211476745465013</v>
+        <v>0.03745526120066572</v>
       </c>
       <c r="H284">
-        <v>0.03111365466081266</v>
+        <v>0.04032776762363291</v>
       </c>
       <c r="I284">
-        <v>0.7788872061625298</v>
+        <v>2.227493577032812</v>
       </c>
       <c r="J284">
-        <v>0.246917319638827</v>
+        <v>0.6718883811816456</v>
       </c>
       <c r="K284">
-        <v>20.35</v>
+        <v>19.52</v>
       </c>
       <c r="L284">
-        <v>27.09</v>
+        <v>24.34</v>
       </c>
       <c r="M284">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N284">
-        <v>26.2</v>
+        <v>26.89</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15254,13 +15245,13 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C285">
         <v>11.26988741430018</v>
       </c>
       <c r="D285" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E285">
         <v>13.49849120317641</v>
@@ -15296,7 +15287,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15304,13 +15295,13 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C286">
         <v>11.3975321062961</v>
       </c>
       <c r="D286" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E286">
         <v>13.62927469907388</v>
@@ -15346,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15354,13 +15345,13 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C287">
         <v>11.53224746086446</v>
       </c>
       <c r="D287" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E287">
         <v>13.76730272629556</v>
@@ -15396,57 +15387,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16">
-      <c r="A288" s="1">
-        <v>0</v>
-      </c>
-      <c r="B288" t="s">
-        <v>56</v>
-      </c>
-      <c r="C288">
-        <v>12.35558584102549</v>
-      </c>
-      <c r="D288" t="s">
-        <v>107</v>
-      </c>
-      <c r="E288">
-        <v>13.08876296367507</v>
-      </c>
-      <c r="F288">
-        <v>1</v>
-      </c>
-      <c r="G288">
-        <v>0.03860441415897451</v>
-      </c>
-      <c r="H288">
-        <v>0.03931123703632493</v>
-      </c>
-      <c r="I288">
-        <v>0.7331771226495736</v>
-      </c>
-      <c r="J288">
-        <v>0.6588561324786399</v>
-      </c>
-      <c r="K288">
-        <v>19.92</v>
-      </c>
-      <c r="L288">
-        <v>25.48</v>
-      </c>
-      <c r="M288">
-        <v>19.9</v>
-      </c>
-      <c r="N288">
-        <v>26.2</v>
-      </c>
-      <c r="O288">
-        <v>1</v>
-      </c>
-      <c r="P288" t="s">
-        <v>108</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="223">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,9 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -677,9 +680,6 @@
   </si>
   <si>
     <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-08-27</t>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P287"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1101,7 +1101,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1137,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1151,7 +1151,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1201,7 +1201,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1251,7 +1251,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1301,7 +1301,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1351,7 +1351,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1401,7 +1401,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1437,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1451,7 +1451,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1501,7 +1501,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1537,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1551,7 +1551,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1601,7 +1601,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1651,7 +1651,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1687,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1701,7 +1701,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1751,7 +1751,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1801,7 +1801,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1851,7 +1851,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1901,7 +1901,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1937,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1951,7 +1951,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1987,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2001,7 +2001,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2037,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2051,7 +2051,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2101,7 +2101,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2151,7 +2151,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2201,7 +2201,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2251,7 +2251,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2301,7 +2301,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2337,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2351,7 +2351,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2387,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2401,7 +2401,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2451,7 +2451,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2501,7 +2501,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2551,7 +2551,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2587,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2637,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2651,7 +2651,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2687,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2801,7 +2801,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2837,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2851,7 +2851,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2901,7 +2901,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2937,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2951,7 +2951,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3001,7 +3001,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3051,7 +3051,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3101,7 +3101,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3137,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3151,7 +3151,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3187,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3201,7 +3201,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3237,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3251,7 +3251,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3287,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3301,7 +3301,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3351,7 +3351,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3387,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3401,7 +3401,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3437,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3451,7 +3451,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3487,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3501,7 +3501,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3551,7 +3551,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3587,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3601,7 +3601,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3637,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3687,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3737,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3751,7 +3751,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3787,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3837,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3887,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3901,7 +3901,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3987,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4037,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4051,7 +4051,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4087,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4137,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4151,7 +4151,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4187,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4237,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4251,7 +4251,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4337,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4351,7 +4351,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4437,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4451,7 +4451,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4487,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4537,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4551,7 +4551,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4587,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4601,7 +4601,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4637,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4701,7 +4701,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4737,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4751,7 +4751,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4851,7 +4851,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4901,7 +4901,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4987,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5001,7 +5001,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5037,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5051,7 +5051,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5087,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5137,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5151,7 +5151,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5187,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5201,7 +5201,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5287,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5301,7 +5301,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5337,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5351,7 +5351,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5387,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5437,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5451,7 +5451,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5487,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5501,7 +5501,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5537,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5587,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5601,7 +5601,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5637,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5651,7 +5651,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5687,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5737,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5751,7 +5751,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5787,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5801,7 +5801,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5837,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5851,7 +5851,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5887,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5901,7 +5901,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5937,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5951,7 +5951,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5987,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6001,7 +6001,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6037,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6051,7 +6051,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6087,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6101,7 +6101,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6137,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6151,7 +6151,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6201,7 +6201,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6237,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6251,7 +6251,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6287,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6301,7 +6301,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6337,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6351,7 +6351,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6387,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6401,7 +6401,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6437,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6451,7 +6451,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6487,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6501,7 +6501,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6537,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6551,7 +6551,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6587,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6601,7 +6601,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6637,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6651,7 +6651,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6687,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6701,7 +6701,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6737,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6751,7 +6751,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6801,7 +6801,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6851,7 +6851,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6887,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6901,7 +6901,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6937,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6951,7 +6951,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6987,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7001,7 +7001,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7037,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7051,7 +7051,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7087,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7101,7 +7101,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7137,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7151,7 +7151,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7187,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7201,7 +7201,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7237,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7251,7 +7251,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7287,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7301,7 +7301,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7337,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7351,7 +7351,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7387,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7401,7 +7401,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7437,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7451,7 +7451,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7487,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7501,7 +7501,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7537,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7551,7 +7551,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7587,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7601,7 +7601,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7637,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7651,7 +7651,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7687,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7701,7 +7701,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7737,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7751,7 +7751,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7787,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7801,7 +7801,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7837,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7851,7 +7851,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7901,7 +7901,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7937,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7951,7 +7951,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7987,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8001,7 +8001,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8037,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8051,7 +8051,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8087,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8101,7 +8101,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8137,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8151,7 +8151,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8187,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8201,7 +8201,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8237,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8251,7 +8251,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8287,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8301,7 +8301,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8337,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8351,7 +8351,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8387,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8401,7 +8401,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8437,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8451,7 +8451,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8487,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8501,7 +8501,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8537,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8551,7 +8551,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8587,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8601,7 +8601,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8637,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8651,7 +8651,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8701,7 +8701,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8737,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8751,7 +8751,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8787,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8801,7 +8801,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8837,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8851,7 +8851,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8887,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8901,7 +8901,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8951,7 +8951,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8987,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9001,7 +9001,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9037,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9051,7 +9051,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9101,7 +9101,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9137,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9151,7 +9151,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9187,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9201,7 +9201,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9237,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9251,7 +9251,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9287,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9301,7 +9301,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9337,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9351,7 +9351,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9387,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9401,7 +9401,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9437,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9451,7 +9451,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9487,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9501,7 +9501,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9537,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9551,7 +9551,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9587,7 +9587,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9601,7 +9601,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9637,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9651,7 +9651,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9687,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9701,7 +9701,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9737,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9751,7 +9751,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9787,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9801,7 +9801,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9837,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9851,7 +9851,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9887,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9901,7 +9901,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9937,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9951,7 +9951,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9987,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10001,7 +10001,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10037,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10051,7 +10051,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10087,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10101,7 +10101,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10137,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10151,7 +10151,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10187,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10201,7 +10201,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10237,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10251,7 +10251,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10287,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10301,7 +10301,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10337,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10351,7 +10351,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10387,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10401,7 +10401,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10437,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10451,7 +10451,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10487,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10501,7 +10501,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10537,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10551,7 +10551,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10587,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10601,7 +10601,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10637,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10651,7 +10651,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10687,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10701,7 +10701,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10737,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10751,7 +10751,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10787,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10837,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10887,7 +10887,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10901,7 +10901,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10937,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10987,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11037,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11051,7 +11051,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11087,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11137,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11187,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11201,7 +11201,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11237,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11287,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11301,7 +11301,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11337,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11351,7 +11351,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11387,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11437,7 +11437,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11451,7 +11451,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11487,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11501,7 +11501,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11537,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11587,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11601,7 +11601,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11637,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11651,7 +11651,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11687,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11737,7 +11737,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11751,7 +11751,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11787,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11801,7 +11801,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11837,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11887,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11901,7 +11901,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11937,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11951,7 +11951,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11987,7 +11987,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12037,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12051,7 +12051,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12087,7 +12087,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12101,7 +12101,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12137,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12187,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12201,7 +12201,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12237,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12251,7 +12251,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12287,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12337,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12351,7 +12351,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12387,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12437,7 +12437,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12451,7 +12451,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12487,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12537,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12551,7 +12551,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12587,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12637,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12651,7 +12651,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12687,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12737,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12751,7 +12751,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12787,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12837,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12887,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12901,7 +12901,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12937,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12951,7 +12951,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12987,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13001,7 +13001,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13037,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13051,7 +13051,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13087,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13101,7 +13101,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13137,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13151,7 +13151,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13187,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13201,7 +13201,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13237,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13251,7 +13251,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13287,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13301,7 +13301,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13351,7 +13351,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13387,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13401,7 +13401,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13437,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13451,7 +13451,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13487,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13501,7 +13501,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13537,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13551,7 +13551,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13587,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13601,7 +13601,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13637,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13651,7 +13651,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13687,7 +13687,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13701,7 +13701,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13737,7 +13737,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13751,7 +13751,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13787,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13801,7 +13801,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13851,7 +13851,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13901,7 +13901,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13951,7 +13951,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13987,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14001,7 +14001,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14037,7 +14037,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14051,7 +14051,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14087,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14101,7 +14101,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14137,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14151,7 +14151,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14187,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14201,7 +14201,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14237,7 +14237,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14251,7 +14251,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14287,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14301,7 +14301,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14337,7 +14337,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14351,7 +14351,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14387,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14401,7 +14401,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14437,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14451,7 +14451,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14501,7 +14501,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14537,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14587,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14637,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14687,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14737,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14787,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14801,7 +14801,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14837,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14851,7 +14851,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14887,7 +14887,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14901,7 +14901,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14937,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14951,7 +14951,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14987,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15001,7 +15001,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15037,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15051,7 +15051,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15087,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15101,7 +15101,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15137,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15151,7 +15151,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15187,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15201,7 +15201,7 @@
         <v>11.22473879933428</v>
       </c>
       <c r="D284" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E284">
         <v>13.45223237636709</v>
@@ -15237,7 +15237,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15245,13 +15245,13 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C285">
-        <v>11.26988741430018</v>
+        <v>11.33579779994147</v>
       </c>
       <c r="D285" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E285">
         <v>13.49849120317641</v>
@@ -15260,22 +15260,22 @@
         <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03741011258569982</v>
+        <v>0.03782420220005853</v>
       </c>
       <c r="H285">
         <v>0.04028150879682359</v>
       </c>
       <c r="I285">
-        <v>2.228603788876233</v>
+        <v>2.162693403234943</v>
       </c>
       <c r="J285">
         <v>0.6695754398411793</v>
       </c>
       <c r="K285">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L285">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M285">
         <v>20</v>
@@ -15287,39 +15287,39 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B286" t="s">
         <v>54</v>
       </c>
       <c r="C286">
-        <v>11.3975321062961</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D286" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E286">
-        <v>13.62927469907388</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F286">
         <v>1</v>
       </c>
       <c r="G286">
-        <v>0.0372824678937039</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H286">
-        <v>0.04015072530092613</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I286">
-        <v>2.231742592777774</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J286">
-        <v>0.6630362650463062</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K286">
         <v>19.52</v>
@@ -15348,28 +15348,28 @@
         <v>54</v>
       </c>
       <c r="C287">
-        <v>11.53224746086446</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D287" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E287">
-        <v>13.76730272629556</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03714775253913554</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H287">
-        <v>0.04001269727370445</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I287">
-        <v>2.235055265431093</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J287">
-        <v>0.6561348636852222</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K287">
         <v>19.52</v>
@@ -15387,6 +15387,56 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16">
+      <c r="A288" s="1">
+        <v>0</v>
+      </c>
+      <c r="B288" t="s">
+        <v>54</v>
+      </c>
+      <c r="C288">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D288" t="s">
+        <v>106</v>
+      </c>
+      <c r="E288">
+        <v>13.76730272629556</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>0.03714775253913554</v>
+      </c>
+      <c r="H288">
+        <v>0.04001269727370445</v>
+      </c>
+      <c r="I288">
+        <v>2.235055265431093</v>
+      </c>
+      <c r="J288">
+        <v>0.6561348636852222</v>
+      </c>
+      <c r="K288">
+        <v>19.52</v>
+      </c>
+      <c r="L288">
+        <v>24.34</v>
+      </c>
+      <c r="M288">
+        <v>20</v>
+      </c>
+      <c r="N288">
+        <v>26.89</v>
+      </c>
+      <c r="O288">
+        <v>1</v>
+      </c>
+      <c r="P288" t="s">
         <v>222</v>
       </c>
     </row>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="223">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,10 +178,10 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
     <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
   </si>
   <si>
     <t>2017-12-29</t>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15198,7 +15198,7 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>11.22473879933428</v>
+        <v>11.29004782022705</v>
       </c>
       <c r="D284" t="s">
         <v>106</v>
@@ -15210,22 +15210,22 @@
         <v>1</v>
       </c>
       <c r="G284">
-        <v>0.03745526120066572</v>
+        <v>0.03786995217977295</v>
       </c>
       <c r="H284">
         <v>0.04032776762363291</v>
       </c>
       <c r="I284">
-        <v>2.227493577032812</v>
+        <v>2.162184556140042</v>
       </c>
       <c r="J284">
         <v>0.6718883811816456</v>
       </c>
       <c r="K284">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L284">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M284">
         <v>20</v>
@@ -15242,40 +15242,40 @@
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285">
-        <v>11.33579779994147</v>
+        <v>11.22473879933428</v>
       </c>
       <c r="D285" t="s">
         <v>106</v>
       </c>
       <c r="E285">
-        <v>13.49849120317641</v>
+        <v>13.45223237636709</v>
       </c>
       <c r="F285">
         <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03782420220005853</v>
+        <v>0.03745526120066572</v>
       </c>
       <c r="H285">
-        <v>0.04028150879682359</v>
+        <v>0.04032776762363291</v>
       </c>
       <c r="I285">
-        <v>2.162693403234943</v>
+        <v>2.227493577032812</v>
       </c>
       <c r="J285">
-        <v>0.6695754398411793</v>
+        <v>0.6718883811816456</v>
       </c>
       <c r="K285">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="L285">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="M285">
         <v>20</v>
@@ -15287,18 +15287,18 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B286" t="s">
         <v>54</v>
       </c>
       <c r="C286">
-        <v>11.26988741430018</v>
+        <v>11.33579779994147</v>
       </c>
       <c r="D286" t="s">
         <v>106</v>
@@ -15310,22 +15310,22 @@
         <v>1</v>
       </c>
       <c r="G286">
-        <v>0.03741011258569982</v>
+        <v>0.03782420220005853</v>
       </c>
       <c r="H286">
         <v>0.04028150879682359</v>
       </c>
       <c r="I286">
-        <v>2.228603788876233</v>
+        <v>2.162693403234943</v>
       </c>
       <c r="J286">
         <v>0.6695754398411793</v>
       </c>
       <c r="K286">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L286">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M286">
         <v>20</v>
@@ -15342,34 +15342,34 @@
     </row>
     <row r="287" spans="1:16">
       <c r="A287" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B287" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C287">
-        <v>11.3975321062961</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D287" t="s">
         <v>106</v>
       </c>
       <c r="E287">
-        <v>13.62927469907388</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.0372824678937039</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H287">
-        <v>0.04015072530092613</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I287">
-        <v>2.231742592777774</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J287">
-        <v>0.6630362650463062</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K287">
         <v>19.52</v>
@@ -15387,7 +15387,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15395,31 +15395,31 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C288">
-        <v>11.53224746086446</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D288" t="s">
         <v>106</v>
       </c>
       <c r="E288">
-        <v>13.76730272629556</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288">
-        <v>0.03714775253913554</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H288">
-        <v>0.04001269727370445</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I288">
-        <v>2.235055265431093</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J288">
-        <v>0.6561348636852222</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K288">
         <v>19.52</v>
@@ -15437,6 +15437,56 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16">
+      <c r="A289" s="1">
+        <v>0</v>
+      </c>
+      <c r="B289" t="s">
+        <v>55</v>
+      </c>
+      <c r="C289">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D289" t="s">
+        <v>106</v>
+      </c>
+      <c r="E289">
+        <v>13.76730272629556</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289">
+        <v>0.03714775253913554</v>
+      </c>
+      <c r="H289">
+        <v>0.04001269727370445</v>
+      </c>
+      <c r="I289">
+        <v>2.235055265431093</v>
+      </c>
+      <c r="J289">
+        <v>0.6561348636852222</v>
+      </c>
+      <c r="K289">
+        <v>19.52</v>
+      </c>
+      <c r="L289">
+        <v>24.34</v>
+      </c>
+      <c r="M289">
+        <v>20</v>
+      </c>
+      <c r="N289">
+        <v>26.89</v>
+      </c>
+      <c r="O289">
+        <v>1</v>
+      </c>
+      <c r="P289" t="s">
         <v>222</v>
       </c>
     </row>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="223">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,10 +178,10 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
     <t>2021-08-26</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
   </si>
   <si>
     <t>2017-12-29</t>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P289"/>
+  <dimension ref="A1:P288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15198,7 +15198,7 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>11.29004782022705</v>
+        <v>11.22473879933428</v>
       </c>
       <c r="D284" t="s">
         <v>106</v>
@@ -15210,22 +15210,22 @@
         <v>1</v>
       </c>
       <c r="G284">
-        <v>0.03786995217977295</v>
+        <v>0.03745526120066572</v>
       </c>
       <c r="H284">
         <v>0.04032776762363291</v>
       </c>
       <c r="I284">
-        <v>2.162184556140042</v>
+        <v>2.227493577032812</v>
       </c>
       <c r="J284">
         <v>0.6718883811816456</v>
       </c>
       <c r="K284">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="L284">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="M284">
         <v>20</v>
@@ -15242,40 +15242,40 @@
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285">
-        <v>11.22473879933428</v>
+        <v>11.33579779994147</v>
       </c>
       <c r="D285" t="s">
         <v>106</v>
       </c>
       <c r="E285">
-        <v>13.45223237636709</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F285">
         <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03745526120066572</v>
+        <v>0.03782420220005853</v>
       </c>
       <c r="H285">
-        <v>0.04032776762363291</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I285">
-        <v>2.227493577032812</v>
+        <v>2.162693403234943</v>
       </c>
       <c r="J285">
-        <v>0.6718883811816456</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K285">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L285">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M285">
         <v>20</v>
@@ -15287,18 +15287,18 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B286" t="s">
         <v>54</v>
       </c>
       <c r="C286">
-        <v>11.33579779994147</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D286" t="s">
         <v>106</v>
@@ -15310,22 +15310,22 @@
         <v>1</v>
       </c>
       <c r="G286">
-        <v>0.03782420220005853</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H286">
         <v>0.04028150879682359</v>
       </c>
       <c r="I286">
-        <v>2.162693403234943</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J286">
         <v>0.6695754398411793</v>
       </c>
       <c r="K286">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="L286">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="M286">
         <v>20</v>
@@ -15342,34 +15342,34 @@
     </row>
     <row r="287" spans="1:16">
       <c r="A287" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C287">
-        <v>11.26988741430018</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D287" t="s">
         <v>106</v>
       </c>
       <c r="E287">
-        <v>13.49849120317641</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03741011258569982</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H287">
-        <v>0.04028150879682359</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I287">
-        <v>2.228603788876233</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J287">
-        <v>0.6695754398411793</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K287">
         <v>19.52</v>
@@ -15387,7 +15387,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>221</v>
+        <v>55</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15395,31 +15395,31 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C288">
-        <v>11.3975321062961</v>
+        <v>11.53224746086446</v>
       </c>
       <c r="D288" t="s">
         <v>106</v>
       </c>
       <c r="E288">
-        <v>13.62927469907388</v>
+        <v>13.76730272629556</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288">
-        <v>0.0372824678937039</v>
+        <v>0.03714775253913554</v>
       </c>
       <c r="H288">
-        <v>0.04015072530092613</v>
+        <v>0.04001269727370445</v>
       </c>
       <c r="I288">
-        <v>2.231742592777774</v>
+        <v>2.235055265431093</v>
       </c>
       <c r="J288">
-        <v>0.6630362650463062</v>
+        <v>0.6561348636852222</v>
       </c>
       <c r="K288">
         <v>19.52</v>
@@ -15437,56 +15437,6 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16">
-      <c r="A289" s="1">
-        <v>0</v>
-      </c>
-      <c r="B289" t="s">
-        <v>55</v>
-      </c>
-      <c r="C289">
-        <v>11.53224746086446</v>
-      </c>
-      <c r="D289" t="s">
-        <v>106</v>
-      </c>
-      <c r="E289">
-        <v>13.76730272629556</v>
-      </c>
-      <c r="F289">
-        <v>1</v>
-      </c>
-      <c r="G289">
-        <v>0.03714775253913554</v>
-      </c>
-      <c r="H289">
-        <v>0.04001269727370445</v>
-      </c>
-      <c r="I289">
-        <v>2.235055265431093</v>
-      </c>
-      <c r="J289">
-        <v>0.6561348636852222</v>
-      </c>
-      <c r="K289">
-        <v>19.52</v>
-      </c>
-      <c r="L289">
-        <v>24.34</v>
-      </c>
-      <c r="M289">
-        <v>20</v>
-      </c>
-      <c r="N289">
-        <v>26.89</v>
-      </c>
-      <c r="O289">
-        <v>1</v>
-      </c>
-      <c r="P289" t="s">
         <v>222</v>
       </c>
     </row>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,10 +178,13 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-08-26</t>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2017-12-29</t>
@@ -337,6 +340,9 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-10-11</t>
+  </si>
+  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -683,6 +689,9 @@
   </si>
   <si>
     <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P288"/>
+  <dimension ref="A1:P290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1101,7 +1110,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1137,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1151,7 +1160,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1187,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1201,7 +1210,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1237,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1251,7 +1260,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1287,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1301,7 +1310,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1337,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1351,7 +1360,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1387,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1401,7 +1410,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1437,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1451,7 +1460,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1487,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1501,7 +1510,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1537,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1551,7 +1560,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1587,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1601,7 +1610,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1637,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1651,7 +1660,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1687,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1701,7 +1710,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1737,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1751,7 +1760,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1787,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1801,7 +1810,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1837,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1851,7 +1860,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1887,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1901,7 +1910,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1937,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1951,7 +1960,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1987,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2001,7 +2010,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2037,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2051,7 +2060,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2087,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2101,7 +2110,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2137,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2151,7 +2160,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2187,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2201,7 +2210,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2237,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2251,7 +2260,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2287,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2301,7 +2310,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2337,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2351,7 +2360,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2387,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2401,7 +2410,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2437,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2451,7 +2460,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2487,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2501,7 +2510,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2537,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2551,7 +2560,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2587,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2637,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2651,7 +2660,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2687,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2737,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2787,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2801,7 +2810,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2837,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2851,7 +2860,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2887,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2901,7 +2910,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2937,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2951,7 +2960,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2987,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3001,7 +3010,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3037,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3051,7 +3060,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3087,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3101,7 +3110,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3137,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3151,7 +3160,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3187,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3201,7 +3210,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3237,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3251,7 +3260,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3287,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3301,7 +3310,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3337,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3351,7 +3360,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3387,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3401,7 +3410,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3437,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3451,7 +3460,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3487,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3501,7 +3510,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3537,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3551,7 +3560,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3587,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3601,7 +3610,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3637,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3687,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3737,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3751,7 +3760,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3787,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3837,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3887,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3901,7 +3910,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3937,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3987,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4037,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4051,7 +4060,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4087,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4137,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4151,7 +4160,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4187,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4237,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4251,7 +4260,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4287,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4337,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4351,7 +4360,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4387,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4437,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4451,7 +4460,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4487,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4537,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4551,7 +4560,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4587,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4601,7 +4610,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4637,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4687,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4701,7 +4710,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4737,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4751,7 +4760,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4787,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4837,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4851,7 +4860,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4887,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4901,7 +4910,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4937,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4987,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5001,7 +5010,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5037,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5051,7 +5060,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5087,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5137,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5151,7 +5160,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5187,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5201,7 +5210,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5237,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5287,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5301,7 +5310,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5337,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5351,7 +5360,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5387,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5437,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5451,7 +5460,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5487,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5501,7 +5510,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5537,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5587,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5601,7 +5610,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5637,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5651,7 +5660,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5687,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5737,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5751,7 +5760,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5787,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5801,7 +5810,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5837,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5851,7 +5860,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5887,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5901,7 +5910,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5937,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5951,7 +5960,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5987,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6001,7 +6010,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6037,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6051,7 +6060,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6087,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6101,7 +6110,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6137,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6151,7 +6160,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6187,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6201,7 +6210,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6237,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6251,7 +6260,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6287,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6301,7 +6310,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6337,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6351,7 +6360,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6387,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6401,7 +6410,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6437,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6451,7 +6460,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6487,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6501,7 +6510,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6537,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6551,7 +6560,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6587,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6601,7 +6610,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6637,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6651,7 +6660,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6687,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6701,7 +6710,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6737,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6751,7 +6760,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6787,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6801,7 +6810,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6837,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6851,7 +6860,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6887,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6901,7 +6910,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6937,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6951,7 +6960,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6987,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7001,7 +7010,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7037,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7051,7 +7060,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7087,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7101,7 +7110,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7137,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7151,7 +7160,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7187,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7201,7 +7210,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7237,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7251,7 +7260,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7287,7 +7296,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7301,7 +7310,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7337,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7351,7 +7360,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7387,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7401,7 +7410,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7437,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7451,7 +7460,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7487,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7501,7 +7510,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7537,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7551,7 +7560,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7587,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7601,7 +7610,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7637,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7651,7 +7660,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7687,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7701,7 +7710,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7737,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7751,7 +7760,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7787,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7801,7 +7810,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7837,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7851,7 +7860,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7887,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7901,7 +7910,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7937,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7951,7 +7960,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7987,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8001,7 +8010,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8037,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8051,7 +8060,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8087,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8101,7 +8110,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8137,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8151,7 +8160,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8187,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8201,7 +8210,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8237,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8251,7 +8260,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8287,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8301,7 +8310,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8337,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8351,7 +8360,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8387,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8401,7 +8410,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8437,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8451,7 +8460,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8487,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8501,7 +8510,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8537,7 +8546,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8551,7 +8560,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8587,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8601,7 +8610,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8637,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8651,7 +8660,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8687,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8701,7 +8710,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8737,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8751,7 +8760,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8787,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8801,7 +8810,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8837,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8851,7 +8860,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8887,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8901,7 +8910,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8951,7 +8960,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8987,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9001,7 +9010,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9037,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9051,7 +9060,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9087,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9101,7 +9110,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9137,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9151,7 +9160,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9187,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9201,7 +9210,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9237,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9251,7 +9260,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9287,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9301,7 +9310,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9337,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9351,7 +9360,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9387,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9401,7 +9410,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9437,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9451,7 +9460,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9487,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9501,7 +9510,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9537,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9551,7 +9560,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9587,7 +9596,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9601,7 +9610,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9637,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9651,7 +9660,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9687,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9701,7 +9710,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9737,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9751,7 +9760,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9787,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9801,7 +9810,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9837,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9851,7 +9860,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9887,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9901,7 +9910,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9937,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9951,7 +9960,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9987,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10001,7 +10010,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10037,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10051,7 +10060,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10087,7 +10096,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10101,7 +10110,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10137,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10151,7 +10160,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10187,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10201,7 +10210,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10237,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10251,7 +10260,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10287,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10301,7 +10310,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10337,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10351,7 +10360,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10387,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10401,7 +10410,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10437,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10451,7 +10460,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10487,7 +10496,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10501,7 +10510,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10537,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10551,7 +10560,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10587,7 +10596,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10601,7 +10610,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10637,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10651,7 +10660,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10687,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10701,7 +10710,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10737,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10751,7 +10760,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10787,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10837,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10887,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10901,7 +10910,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10937,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10987,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11037,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11051,7 +11060,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11087,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11137,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11187,7 +11196,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11201,7 +11210,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11237,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11287,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11301,7 +11310,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11337,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11351,7 +11360,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11387,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11437,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11451,7 +11460,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11487,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11501,7 +11510,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11537,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11587,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11601,7 +11610,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11637,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11651,7 +11660,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11687,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11737,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11751,7 +11760,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11787,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11801,7 +11810,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11837,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11887,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11901,7 +11910,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11937,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11951,7 +11960,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11987,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12037,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12051,7 +12060,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12087,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12101,7 +12110,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12137,7 +12146,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12187,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12201,7 +12210,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12237,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12251,7 +12260,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12287,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12337,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12351,7 +12360,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12387,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12437,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12451,7 +12460,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12487,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12537,7 +12546,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12551,7 +12560,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12587,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12637,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12651,7 +12660,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12687,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12737,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12751,7 +12760,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12787,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12837,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12887,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12901,7 +12910,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12937,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12951,7 +12960,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12987,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13001,7 +13010,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13037,7 +13046,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13051,7 +13060,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13087,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13101,7 +13110,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13137,7 +13146,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13151,7 +13160,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13187,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13201,7 +13210,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13237,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13251,7 +13260,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13287,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13301,7 +13310,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13337,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13351,7 +13360,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13387,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13401,7 +13410,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13437,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13451,7 +13460,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13487,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13501,7 +13510,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13537,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13551,7 +13560,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13587,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13601,7 +13610,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13637,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13651,7 +13660,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13687,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13701,7 +13710,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13737,7 +13746,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13751,7 +13760,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13787,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13801,7 +13810,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13851,7 +13860,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13901,7 +13910,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13951,7 +13960,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13987,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14001,7 +14010,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14037,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14051,7 +14060,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14087,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14101,7 +14110,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14137,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14151,7 +14160,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14187,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14201,7 +14210,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14237,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14251,7 +14260,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14287,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14301,7 +14310,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14337,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14351,7 +14360,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14387,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14401,7 +14410,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14437,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14451,7 +14460,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14487,7 +14496,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14501,7 +14510,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14537,7 +14546,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14587,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14637,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14687,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14737,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14787,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14801,7 +14810,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14837,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14851,7 +14860,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14887,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14901,7 +14910,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14937,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14951,7 +14960,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14987,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15001,7 +15010,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15037,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15051,7 +15060,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15087,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15101,7 +15110,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15137,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15151,7 +15160,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15187,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15198,10 +15207,10 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>11.22473879933428</v>
+        <v>11.29004782022705</v>
       </c>
       <c r="D284" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E284">
         <v>13.45223237636709</v>
@@ -15210,22 +15219,22 @@
         <v>1</v>
       </c>
       <c r="G284">
-        <v>0.03745526120066572</v>
+        <v>0.03786995217977295</v>
       </c>
       <c r="H284">
         <v>0.04032776762363291</v>
       </c>
       <c r="I284">
-        <v>2.227493577032812</v>
+        <v>2.162184556140042</v>
       </c>
       <c r="J284">
         <v>0.6718883811816456</v>
       </c>
       <c r="K284">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L284">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M284">
         <v>20</v>
@@ -15237,45 +15246,45 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285">
-        <v>11.33579779994147</v>
+        <v>11.22473879933428</v>
       </c>
       <c r="D285" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E285">
-        <v>13.49849120317641</v>
+        <v>13.45223237636709</v>
       </c>
       <c r="F285">
         <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03782420220005853</v>
+        <v>0.03745526120066572</v>
       </c>
       <c r="H285">
-        <v>0.04028150879682359</v>
+        <v>0.04032776762363291</v>
       </c>
       <c r="I285">
-        <v>2.162693403234943</v>
+        <v>2.227493577032812</v>
       </c>
       <c r="J285">
-        <v>0.6695754398411793</v>
+        <v>0.6718883811816456</v>
       </c>
       <c r="K285">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="L285">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="M285">
         <v>20</v>
@@ -15287,21 +15296,21 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B286" t="s">
         <v>54</v>
       </c>
       <c r="C286">
-        <v>11.26988741430018</v>
+        <v>11.33579779994147</v>
       </c>
       <c r="D286" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E286">
         <v>13.49849120317641</v>
@@ -15310,22 +15319,22 @@
         <v>1</v>
       </c>
       <c r="G286">
-        <v>0.03741011258569982</v>
+        <v>0.03782420220005853</v>
       </c>
       <c r="H286">
         <v>0.04028150879682359</v>
       </c>
       <c r="I286">
-        <v>2.228603788876233</v>
+        <v>2.162693403234943</v>
       </c>
       <c r="J286">
         <v>0.6695754398411793</v>
       </c>
       <c r="K286">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L286">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M286">
         <v>20</v>
@@ -15337,39 +15346,39 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="1:16">
       <c r="A287" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B287" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C287">
-        <v>11.3975321062961</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D287" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E287">
-        <v>13.62927469907388</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F287">
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.0372824678937039</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H287">
-        <v>0.04015072530092613</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I287">
-        <v>2.231742592777774</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J287">
-        <v>0.6630362650463062</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K287">
         <v>19.52</v>
@@ -15387,7 +15396,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15395,31 +15404,31 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C288">
-        <v>11.53224746086446</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D288" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E288">
-        <v>13.76730272629556</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288">
-        <v>0.03714775253913554</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H288">
-        <v>0.04001269727370445</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I288">
-        <v>2.235055265431093</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J288">
-        <v>0.6561348636852222</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K288">
         <v>19.52</v>
@@ -15437,7 +15446,107 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>222</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16">
+      <c r="A289" s="1">
+        <v>0</v>
+      </c>
+      <c r="B289" t="s">
+        <v>55</v>
+      </c>
+      <c r="C289">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D289" t="s">
+        <v>107</v>
+      </c>
+      <c r="E289">
+        <v>13.76730272629556</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289">
+        <v>0.03714775253913554</v>
+      </c>
+      <c r="H289">
+        <v>0.04001269727370445</v>
+      </c>
+      <c r="I289">
+        <v>2.235055265431093</v>
+      </c>
+      <c r="J289">
+        <v>0.6561348636852222</v>
+      </c>
+      <c r="K289">
+        <v>19.52</v>
+      </c>
+      <c r="L289">
+        <v>24.34</v>
+      </c>
+      <c r="M289">
+        <v>20</v>
+      </c>
+      <c r="N289">
+        <v>26.89</v>
+      </c>
+      <c r="O289">
+        <v>1</v>
+      </c>
+      <c r="P289" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16">
+      <c r="A290" s="1">
+        <v>0</v>
+      </c>
+      <c r="B290" t="s">
+        <v>56</v>
+      </c>
+      <c r="C290">
+        <v>10.9244311529636</v>
+      </c>
+      <c r="D290" t="s">
+        <v>108</v>
+      </c>
+      <c r="E290">
+        <v>11.33337383209069</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290">
+        <v>0.0396355688470364</v>
+      </c>
+      <c r="H290">
+        <v>0.03998662616790932</v>
+      </c>
+      <c r="I290">
+        <v>0.4089426791270867</v>
+      </c>
+      <c r="J290">
+        <v>0.723566978177238</v>
+      </c>
+      <c r="K290">
+        <v>19.84</v>
+      </c>
+      <c r="L290">
+        <v>25.28</v>
+      </c>
+      <c r="M290">
+        <v>19.8</v>
+      </c>
+      <c r="N290">
+        <v>25.66</v>
+      </c>
+      <c r="O290">
+        <v>1</v>
+      </c>
+      <c r="P290" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -340,7 +340,7 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-10-11</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15513,7 +15513,7 @@
         <v>108</v>
       </c>
       <c r="E290">
-        <v>11.33337383209069</v>
+        <v>11.50295358284819</v>
       </c>
       <c r="F290">
         <v>1</v>
@@ -15522,10 +15522,10 @@
         <v>0.0396355688470364</v>
       </c>
       <c r="H290">
-        <v>0.03998662616790932</v>
+        <v>0.03821704641715182</v>
       </c>
       <c r="I290">
-        <v>0.4089426791270867</v>
+        <v>0.5785224298845861</v>
       </c>
       <c r="J290">
         <v>0.723566978177238</v>
@@ -15537,10 +15537,10 @@
         <v>25.28</v>
       </c>
       <c r="M290">
-        <v>19.8</v>
+        <v>18.46</v>
       </c>
       <c r="N290">
-        <v>25.66</v>
+        <v>24.86</v>
       </c>
       <c r="O290">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -340,7 +340,7 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-10-12</t>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -15513,7 +15513,7 @@
         <v>108</v>
       </c>
       <c r="E290">
-        <v>11.50295358284819</v>
+        <v>11.37694081026793</v>
       </c>
       <c r="F290">
         <v>1</v>
@@ -15522,10 +15522,10 @@
         <v>0.0396355688470364</v>
       </c>
       <c r="H290">
-        <v>0.03821704641715182</v>
+        <v>0.03858305918973207</v>
       </c>
       <c r="I290">
-        <v>0.5785224298845861</v>
+        <v>0.4525096573043257</v>
       </c>
       <c r="J290">
         <v>0.723566978177238</v>
@@ -15537,10 +15537,10 @@
         <v>25.28</v>
       </c>
       <c r="M290">
-        <v>18.46</v>
+        <v>18.8</v>
       </c>
       <c r="N290">
-        <v>24.86</v>
+        <v>24.98</v>
       </c>
       <c r="O290">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
   <si>
     <t>trade_time</t>
   </si>
@@ -178,6 +178,9 @@
     <t>2021-04-01</t>
   </si>
   <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
     <t>2021-08-26</t>
   </si>
   <si>
@@ -337,10 +340,13 @@
     <t>2021-04-26</t>
   </si>
   <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2017-06-07</t>
@@ -680,6 +686,9 @@
   </si>
   <si>
     <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
   </si>
   <si>
     <t>2021-08-24</t>
@@ -1049,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P290"/>
+  <dimension ref="A1:P291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1110,7 +1119,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1146,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1160,7 +1169,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1196,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1210,7 +1219,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1246,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1260,7 +1269,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1296,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1310,7 +1319,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1346,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1360,7 +1369,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1396,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1410,7 +1419,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1446,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1460,7 +1469,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1496,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1510,7 +1519,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1546,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1560,7 +1569,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1596,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1610,7 +1619,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1646,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1660,7 +1669,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1696,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1710,7 +1719,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1746,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1760,7 +1769,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1796,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1810,7 +1819,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1846,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1860,7 +1869,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1896,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1910,7 +1919,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1946,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1960,7 +1969,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -1996,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2010,7 +2019,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2046,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2060,7 +2069,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2096,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2110,7 +2119,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2146,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2160,7 +2169,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2196,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2210,7 +2219,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2246,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2260,7 +2269,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2296,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2310,7 +2319,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2346,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2360,7 +2369,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2396,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2410,7 +2419,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2446,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2460,7 +2469,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2496,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2510,7 +2519,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2546,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2560,7 +2569,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2596,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2646,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2660,7 +2669,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2696,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2746,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2796,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,7 +2819,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2846,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2860,7 +2869,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2896,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2910,7 +2919,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2946,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2960,7 +2969,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -2996,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3010,7 +3019,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3046,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3060,7 +3069,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3096,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3110,7 +3119,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3146,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3160,7 +3169,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3196,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3210,7 +3219,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3246,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3260,7 +3269,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3296,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3310,7 +3319,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3346,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3360,7 +3369,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3396,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3410,7 +3419,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3446,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3460,7 +3469,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3496,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3510,7 +3519,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3546,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3560,7 +3569,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3596,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3610,7 +3619,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3646,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3696,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3746,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3760,7 +3769,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3796,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3846,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3896,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3910,7 +3919,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3946,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3996,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4046,7 +4055,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4060,7 +4069,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4096,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4146,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4160,7 +4169,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4196,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4246,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4260,7 +4269,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4296,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4346,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4360,7 +4369,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4396,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4446,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4460,7 +4469,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4496,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4546,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4560,7 +4569,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4596,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4610,7 +4619,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4646,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4696,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4710,7 +4719,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4746,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4760,7 +4769,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4796,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4846,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4860,7 +4869,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4896,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4910,7 +4919,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4946,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4996,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5010,7 +5019,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5046,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5060,7 +5069,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5096,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5146,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5160,7 +5169,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5196,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5210,7 +5219,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5246,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5296,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5310,7 +5319,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5346,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5360,7 +5369,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5396,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5446,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5460,7 +5469,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5496,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5510,7 +5519,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5546,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5596,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5610,7 +5619,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5646,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5660,7 +5669,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5696,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5746,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5760,7 +5769,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5796,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5810,7 +5819,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5846,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5860,7 +5869,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5896,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5910,7 +5919,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5946,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5960,7 +5969,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -5996,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6010,7 +6019,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6046,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6060,7 +6069,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6096,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6110,7 +6119,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6146,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6160,7 +6169,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6196,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6210,7 +6219,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6246,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6260,7 +6269,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6296,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6310,7 +6319,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6346,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6360,7 +6369,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6396,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6410,7 +6419,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6446,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6460,7 +6469,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6496,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6510,7 +6519,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6546,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6560,7 +6569,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6596,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6610,7 +6619,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6646,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6660,7 +6669,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6696,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6710,7 +6719,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6746,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6760,7 +6769,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6796,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6810,7 +6819,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6846,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6860,7 +6869,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6896,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6910,7 +6919,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6946,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,7 +6969,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -6996,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7010,7 +7019,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7046,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7060,7 +7069,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7096,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7110,7 +7119,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7146,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,7 +7169,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7196,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7210,7 +7219,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7246,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7260,7 +7269,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7296,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7310,7 +7319,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7346,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7360,7 +7369,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7396,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7410,7 +7419,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7446,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7460,7 +7469,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7496,7 +7505,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7510,7 +7519,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7546,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7560,7 +7569,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7596,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7610,7 +7619,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7646,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7660,7 +7669,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7696,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7710,7 +7719,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7746,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7760,7 +7769,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7796,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7810,7 +7819,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7846,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7860,7 +7869,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7896,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7910,7 +7919,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7946,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7960,7 +7969,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -7996,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8010,7 +8019,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8046,7 +8055,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8060,7 +8069,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8096,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8110,7 +8119,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8146,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8160,7 +8169,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8196,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8210,7 +8219,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8246,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8260,7 +8269,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8296,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8310,7 +8319,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8346,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8360,7 +8369,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8396,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8410,7 +8419,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8446,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8460,7 +8469,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8496,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8510,7 +8519,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8546,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8560,7 +8569,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8596,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8610,7 +8619,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8646,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8660,7 +8669,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8696,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8710,7 +8719,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8746,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8760,7 +8769,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8796,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8810,7 +8819,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8846,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8860,7 +8869,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8896,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8910,7 +8919,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8960,7 +8969,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -8996,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9010,7 +9019,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9046,7 +9055,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9060,7 +9069,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9096,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9110,7 +9119,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9146,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9160,7 +9169,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9196,7 +9205,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9210,7 +9219,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9246,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9260,7 +9269,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9296,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9310,7 +9319,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9346,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9360,7 +9369,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9396,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9410,7 +9419,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9446,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9460,7 +9469,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9496,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9510,7 +9519,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9546,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9560,7 +9569,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9596,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9610,7 +9619,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9646,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9660,7 +9669,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9696,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9710,7 +9719,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9746,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9760,7 +9769,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9796,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9810,7 +9819,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9846,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9860,7 +9869,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9896,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9910,7 +9919,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9946,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9960,7 +9969,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -9996,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10010,7 +10019,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10046,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10060,7 +10069,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10096,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10110,7 +10119,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10146,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10160,7 +10169,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10196,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10210,7 +10219,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10246,7 +10255,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10260,7 +10269,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10296,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10310,7 +10319,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10346,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10360,7 +10369,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10396,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10410,7 +10419,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10446,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10460,7 +10469,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10496,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10510,7 +10519,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10546,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10560,7 +10569,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10596,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10610,7 +10619,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10646,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10660,7 +10669,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10696,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10710,7 +10719,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10746,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10760,7 +10769,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10796,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10846,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10896,7 +10905,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10910,7 +10919,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10946,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10996,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11046,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11060,7 +11069,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11096,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11146,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11196,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11210,7 +11219,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11246,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11296,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11310,7 +11319,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11346,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11360,7 +11369,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11396,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11446,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11460,7 +11469,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11496,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11510,7 +11519,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11546,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11596,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11610,7 +11619,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11646,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11660,7 +11669,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11696,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11746,7 +11755,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11760,7 +11769,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11796,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11810,7 +11819,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11846,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11896,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11910,7 +11919,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11946,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11960,7 +11969,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -11996,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12046,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12060,7 +12069,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12096,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12110,7 +12119,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12146,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12196,7 +12205,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12210,7 +12219,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12246,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12260,7 +12269,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12296,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12360,7 +12369,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12396,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12446,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12460,7 +12469,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12496,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12546,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12560,7 +12569,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12596,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12646,7 +12655,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12660,7 +12669,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12696,7 +12705,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12746,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12760,7 +12769,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12796,7 +12805,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12846,7 +12855,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12896,7 +12905,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12910,7 +12919,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12946,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12960,7 +12969,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -12996,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13010,7 +13019,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13046,7 +13055,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13060,7 +13069,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13096,7 +13105,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13110,7 +13119,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13146,7 +13155,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13160,7 +13169,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13196,7 +13205,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13210,7 +13219,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13246,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13260,7 +13269,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13296,7 +13305,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13310,7 +13319,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13346,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13360,7 +13369,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13396,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13410,7 +13419,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13446,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13460,7 +13469,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13496,7 +13505,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13510,7 +13519,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13546,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13560,7 +13569,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13596,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13610,7 +13619,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13646,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13660,7 +13669,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13696,7 +13705,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13710,7 +13719,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13746,7 +13755,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13760,7 +13769,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13796,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13810,7 +13819,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13860,7 +13869,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13910,7 +13919,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13960,7 +13969,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -13996,7 +14005,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14010,7 +14019,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14046,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14060,7 +14069,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14096,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14110,7 +14119,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14146,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14160,7 +14169,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14196,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14210,7 +14219,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14246,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14260,7 +14269,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14296,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14310,7 +14319,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14346,7 +14355,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14360,7 +14369,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14396,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14410,7 +14419,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14446,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14460,7 +14469,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14496,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14510,7 +14519,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14546,7 +14555,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14596,7 +14605,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14646,7 +14655,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14696,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14746,7 +14755,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14796,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14810,7 +14819,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14846,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14860,7 +14869,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14896,7 +14905,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14910,7 +14919,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14946,7 +14955,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14960,7 +14969,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -14996,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15010,7 +15019,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15046,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15060,7 +15069,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15096,7 +15105,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15110,7 +15119,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15146,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15160,7 +15169,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15196,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15207,60 +15216,60 @@
         <v>54</v>
       </c>
       <c r="C284">
-        <v>11.29004782022705</v>
+        <v>22.06523254534987</v>
       </c>
       <c r="D284" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E284">
-        <v>13.45223237636709</v>
+        <v>20.29931077014897</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G284">
-        <v>0.03786995217977295</v>
+        <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.04032776762363291</v>
+        <v>0.02980068922985103</v>
       </c>
       <c r="I284">
-        <v>2.162184556140042</v>
+        <v>1.765921775200901</v>
       </c>
       <c r="J284">
-        <v>0.6718883811816456</v>
+        <v>0.246917319638827</v>
       </c>
       <c r="K284">
-        <v>19.78</v>
+        <v>20.35</v>
       </c>
       <c r="L284">
-        <v>24.58</v>
+        <v>27.09</v>
       </c>
       <c r="M284">
-        <v>20</v>
+        <v>19.24</v>
       </c>
       <c r="N284">
-        <v>26.89</v>
+        <v>25.05</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285">
-        <v>11.22473879933428</v>
+        <v>11.29004782022705</v>
       </c>
       <c r="D285" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E285">
         <v>13.45223237636709</v>
@@ -15269,22 +15278,22 @@
         <v>1</v>
       </c>
       <c r="G285">
-        <v>0.03745526120066572</v>
+        <v>0.03786995217977295</v>
       </c>
       <c r="H285">
         <v>0.04032776762363291</v>
       </c>
       <c r="I285">
-        <v>2.227493577032812</v>
+        <v>2.162184556140042</v>
       </c>
       <c r="J285">
         <v>0.6718883811816456</v>
       </c>
       <c r="K285">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L285">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M285">
         <v>20</v>
@@ -15296,45 +15305,45 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B286" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C286">
-        <v>11.33579779994147</v>
+        <v>11.22473879933428</v>
       </c>
       <c r="D286" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E286">
-        <v>13.49849120317641</v>
+        <v>13.45223237636709</v>
       </c>
       <c r="F286">
         <v>1</v>
       </c>
       <c r="G286">
-        <v>0.03782420220005853</v>
+        <v>0.03745526120066572</v>
       </c>
       <c r="H286">
-        <v>0.04028150879682359</v>
+        <v>0.04032776762363291</v>
       </c>
       <c r="I286">
-        <v>2.162693403234943</v>
+        <v>2.227493577032812</v>
       </c>
       <c r="J286">
-        <v>0.6695754398411793</v>
+        <v>0.6718883811816456</v>
       </c>
       <c r="K286">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="L286">
-        <v>24.58</v>
+        <v>24.34</v>
       </c>
       <c r="M286">
         <v>20</v>
@@ -15346,21 +15355,21 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="287" spans="1:16">
       <c r="A287" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B287" t="s">
         <v>55</v>
       </c>
       <c r="C287">
-        <v>11.26988741430018</v>
+        <v>11.33579779994147</v>
       </c>
       <c r="D287" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E287">
         <v>13.49849120317641</v>
@@ -15369,22 +15378,22 @@
         <v>1</v>
       </c>
       <c r="G287">
-        <v>0.03741011258569982</v>
+        <v>0.03782420220005853</v>
       </c>
       <c r="H287">
         <v>0.04028150879682359</v>
       </c>
       <c r="I287">
-        <v>2.228603788876233</v>
+        <v>2.162693403234943</v>
       </c>
       <c r="J287">
         <v>0.6695754398411793</v>
       </c>
       <c r="K287">
-        <v>19.52</v>
+        <v>19.78</v>
       </c>
       <c r="L287">
-        <v>24.34</v>
+        <v>24.58</v>
       </c>
       <c r="M287">
         <v>20</v>
@@ -15396,39 +15405,39 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="288" spans="1:16">
       <c r="A288" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B288" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C288">
-        <v>11.3975321062961</v>
+        <v>11.26988741430018</v>
       </c>
       <c r="D288" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E288">
-        <v>13.62927469907388</v>
+        <v>13.49849120317641</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288">
-        <v>0.0372824678937039</v>
+        <v>0.03741011258569982</v>
       </c>
       <c r="H288">
-        <v>0.04015072530092613</v>
+        <v>0.04028150879682359</v>
       </c>
       <c r="I288">
-        <v>2.231742592777774</v>
+        <v>2.228603788876233</v>
       </c>
       <c r="J288">
-        <v>0.6630362650463062</v>
+        <v>0.6695754398411793</v>
       </c>
       <c r="K288">
         <v>19.52</v>
@@ -15446,7 +15455,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15454,31 +15463,31 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C289">
-        <v>11.53224746086446</v>
+        <v>11.3975321062961</v>
       </c>
       <c r="D289" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E289">
-        <v>13.76730272629556</v>
+        <v>13.62927469907388</v>
       </c>
       <c r="F289">
         <v>1</v>
       </c>
       <c r="G289">
-        <v>0.03714775253913554</v>
+        <v>0.0372824678937039</v>
       </c>
       <c r="H289">
-        <v>0.04001269727370445</v>
+        <v>0.04015072530092613</v>
       </c>
       <c r="I289">
-        <v>2.235055265431093</v>
+        <v>2.231742592777774</v>
       </c>
       <c r="J289">
-        <v>0.6561348636852222</v>
+        <v>0.6630362650463062</v>
       </c>
       <c r="K289">
         <v>19.52</v>
@@ -15496,7 +15505,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>224</v>
+        <v>55</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15507,46 +15516,96 @@
         <v>56</v>
       </c>
       <c r="C290">
+        <v>11.53224746086446</v>
+      </c>
+      <c r="D290" t="s">
+        <v>109</v>
+      </c>
+      <c r="E290">
+        <v>13.76730272629556</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290">
+        <v>0.03714775253913554</v>
+      </c>
+      <c r="H290">
+        <v>0.04001269727370445</v>
+      </c>
+      <c r="I290">
+        <v>2.235055265431093</v>
+      </c>
+      <c r="J290">
+        <v>0.6561348636852222</v>
+      </c>
+      <c r="K290">
+        <v>19.52</v>
+      </c>
+      <c r="L290">
+        <v>24.34</v>
+      </c>
+      <c r="M290">
+        <v>20</v>
+      </c>
+      <c r="N290">
+        <v>26.89</v>
+      </c>
+      <c r="O290">
+        <v>1</v>
+      </c>
+      <c r="P290" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16">
+      <c r="A291" s="1">
+        <v>0</v>
+      </c>
+      <c r="B291" t="s">
+        <v>57</v>
+      </c>
+      <c r="C291">
         <v>10.9244311529636</v>
       </c>
-      <c r="D290" t="s">
-        <v>108</v>
-      </c>
-      <c r="E290">
-        <v>11.37694081026793</v>
-      </c>
-      <c r="F290">
-        <v>1</v>
-      </c>
-      <c r="G290">
+      <c r="D291" t="s">
+        <v>110</v>
+      </c>
+      <c r="E291">
+        <v>11.50295358284819</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+      <c r="G291">
         <v>0.0396355688470364</v>
       </c>
-      <c r="H290">
-        <v>0.03858305918973207</v>
-      </c>
-      <c r="I290">
-        <v>0.4525096573043257</v>
-      </c>
-      <c r="J290">
+      <c r="H291">
+        <v>0.03821704641715182</v>
+      </c>
+      <c r="I291">
+        <v>0.5785224298845861</v>
+      </c>
+      <c r="J291">
         <v>0.723566978177238</v>
       </c>
-      <c r="K290">
+      <c r="K291">
         <v>19.84</v>
       </c>
-      <c r="L290">
+      <c r="L291">
         <v>25.28</v>
       </c>
-      <c r="M290">
-        <v>18.8</v>
-      </c>
-      <c r="N290">
-        <v>24.98</v>
-      </c>
-      <c r="O290">
-        <v>1</v>
-      </c>
-      <c r="P290" t="s">
-        <v>225</v>
+      <c r="M291">
+        <v>18.46</v>
+      </c>
+      <c r="N291">
+        <v>24.86</v>
+      </c>
+      <c r="O291">
+        <v>1</v>
+      </c>
+      <c r="P291" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="227">
   <si>
     <t>trade_time</t>
   </si>
@@ -187,9 +187,6 @@
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
     <t>2017-12-29</t>
   </si>
   <si>
@@ -340,15 +337,15 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-10-20</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-10-12</t>
-  </si>
-  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -698,9 +695,6 @@
   </si>
   <si>
     <t>2021-08-27</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P291"/>
+  <dimension ref="A1:P290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1119,7 +1113,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1155,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1169,7 +1163,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1205,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1219,7 +1213,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1255,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1269,7 +1263,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1305,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1319,7 +1313,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1355,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1369,7 +1363,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1405,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1419,7 +1413,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1455,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1469,7 +1463,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1505,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1519,7 +1513,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1555,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1569,7 +1563,7 @@
         <v>9.139320836557681</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>8.732550953037995</v>
@@ -1605,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1619,7 +1613,7 @@
         <v>9.357190156927155</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>8.732550953037995</v>
@@ -1655,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1669,7 +1663,7 @@
         <v>9.200798118035582</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>8.732550953037995</v>
@@ -1705,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1719,7 +1713,7 @@
         <v>13.375061537059</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10.40925031148389</v>
@@ -1755,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1769,7 +1763,7 @@
         <v>13.57040189017536</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>10.40925031148389</v>
@@ -1805,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1819,7 +1813,7 @@
         <v>13.3507433068952</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>10.40925031148389</v>
@@ -1855,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1869,7 +1863,7 @@
         <v>13.30047506237557</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>10.34482093802768</v>
@@ -1905,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1919,7 +1913,7 @@
         <v>13.4836117341667</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>10.34482093802768</v>
@@ -1955,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1969,7 +1963,7 @@
         <v>13.27509564253132</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>10.34482093802768</v>
@@ -2005,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2019,7 +2013,7 @@
         <v>11.67248547055419</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>8.938529115824251</v>
@@ -2055,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2069,7 +2063,7 @@
         <v>11.58925392661031</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>8.938529115824251</v>
@@ -2105,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2119,7 +2113,7 @@
         <v>11.76883873651334</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>8.938529115824251</v>
@@ -2155,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2169,7 +2163,7 @@
         <v>11.62394359716777</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>8.938529115824251</v>
@@ -2205,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2219,7 +2213,7 @@
         <v>11.9238394452668</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>8.938529115824251</v>
@@ -2255,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2269,7 +2263,7 @@
         <v>9.5904863607528</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>7.14005427504053</v>
@@ -2305,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2319,7 +2313,7 @@
         <v>9.814334249665182</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>7.14005427504053</v>
@@ -2355,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2369,7 +2363,7 @@
         <v>6.965621767215941</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>4.559031214361749</v>
@@ -2405,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2419,7 +2413,7 @@
         <v>4.49838613720719</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>2.635057228862159</v>
@@ -2455,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2469,7 +2463,7 @@
         <v>2.243144426267811</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>-0.2012473708810596</v>
@@ -2505,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2519,7 +2513,7 @@
         <v>0.9126319445853106</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>-1.144541844992997</v>
@@ -2555,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2569,7 +2563,7 @@
         <v>-0.4676348205514245</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31">
         <v>-2.60277105267765</v>
@@ -2605,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2655,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2669,7 +2663,7 @@
         <v>-1.944780710946013</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>-4.365582855780129</v>
@@ -2705,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2755,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2805,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2819,7 +2813,7 @@
         <v>-2.910160173573079</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36">
         <v>-5.517657489882193</v>
@@ -2855,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2869,7 +2863,7 @@
         <v>-8.150787513759084</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>-4.659398777539032</v>
@@ -2905,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2919,7 +2913,7 @@
         <v>-7.50966486037991</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>-4.659398777539032</v>
@@ -2955,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2969,7 +2963,7 @@
         <v>-3.701845811283643</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39">
         <v>-6.462447571605328</v>
@@ -3005,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3019,7 +3013,7 @@
         <v>-9.260310225116001</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>-5.559614147714203</v>
@@ -3055,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3069,7 +3063,7 @@
         <v>-8.575581875657296</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41">
         <v>-5.559614147714203</v>
@@ -3105,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3119,7 +3113,7 @@
         <v>-4.215243565878026</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42">
         <v>-7.075131550466434</v>
@@ -3155,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3169,7 +3163,7 @@
         <v>-9.266815082577516</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>-6.143392010649553</v>
@@ -3205,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3219,7 +3213,7 @@
         <v>-5.035609435385091</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>-8.054148347001792</v>
@@ -3255,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3269,7 +3263,7 @@
         <v>-10.37134685302766</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45">
         <v>-7.07621929678427</v>
@@ -3305,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3319,7 +3313,7 @@
         <v>-5.61860772472965</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46">
         <v>-8.74989293954885</v>
@@ -3355,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3369,7 +3363,7 @@
         <v>-4.561730003088883</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47">
         <v>-7.488625156685018</v>
@@ -3405,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3419,7 +3413,7 @@
         <v>-9.733320689593352</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48">
         <v>-6.537377200574749</v>
@@ -3455,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3469,7 +3463,7 @@
         <v>-3.000995209941514</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49">
         <v>-5.626059155070962</v>
@@ -3505,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3519,7 +3513,7 @@
         <v>-8.278089982108973</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50">
         <v>-4.762686107754792</v>
@@ -3555,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3569,7 +3563,7 @@
         <v>-7.631964174951857</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E51">
         <v>-4.762686107754792</v>
@@ -3605,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3619,7 +3613,7 @@
         <v>-2.668227916934544</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E52">
         <v>-5.228937844566932</v>
@@ -3655,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3705,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3755,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3769,7 +3763,7 @@
         <v>-2.841973877385694</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>-5.43628461499517</v>
@@ -3805,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3855,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3905,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3919,7 +3913,7 @@
         <v>-2.593739613585424</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>-5.140044214499131</v>
@@ -3955,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4005,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4055,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4069,7 +4063,7 @@
         <v>-2.292481693031814</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E61">
         <v>-4.78052588825706</v>
@@ -4105,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4155,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4169,7 +4163,7 @@
         <v>-1.840449550676606</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>-4.241075045177102</v>
@@ -4205,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4255,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4269,7 +4263,7 @@
         <v>-1.324627048908336</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65">
         <v>-3.625497396188038</v>
@@ -4305,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4355,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4369,7 +4363,7 @@
         <v>-0.9516531783789333</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>-3.424126713831772</v>
@@ -4405,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4455,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4469,7 +4463,7 @@
         <v>-0.4427615172323343</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>-2.801871182025831</v>
@@ -4505,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4555,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4569,7 +4563,7 @@
         <v>-0.2224377705994698</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E71">
         <v>-2.532466747648556</v>
@@ -4605,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4619,7 +4613,7 @@
         <v>-0.5793598922352103</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E72">
         <v>-2.532466747648556</v>
@@ -4655,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4705,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4719,7 +4713,7 @@
         <v>-0.4730502200786759</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E74">
         <v>-2.83890718464945</v>
@@ -4755,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4769,7 +4763,7 @@
         <v>-0.8281318586093072</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>-2.83890718464945</v>
@@ -4805,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4855,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4869,7 +4863,7 @@
         <v>-0.7312571770121252</v>
       </c>
       <c r="D77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E77">
         <v>-3.154633928806749</v>
@@ -4905,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4919,7 +4913,7 @@
         <v>-1.084442558821092</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E78">
         <v>-3.154633928806749</v>
@@ -4955,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5005,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5019,7 +5013,7 @@
         <v>-1.310912331834935</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E80">
         <v>-3.863416670138434</v>
@@ -5055,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5069,7 +5063,7 @@
         <v>-1.65984076024251</v>
       </c>
       <c r="D81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E81">
         <v>-3.863416670138434</v>
@@ -5105,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5155,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5169,7 +5163,7 @@
         <v>-1.739254947547035</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>-4.387179550305373</v>
@@ -5205,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5219,7 +5213,7 @@
         <v>-2.085037652950604</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E84">
         <v>-4.387179550305373</v>
@@ -5255,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5305,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5319,7 +5313,7 @@
         <v>-1.707231801223266</v>
       </c>
       <c r="D86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E86">
         <v>-4.348022728790756</v>
@@ -5355,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5369,7 +5363,7 @@
         <v>-2.05324968273203</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87">
         <v>-4.348022728790756</v>
@@ -5405,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5455,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5469,7 +5463,7 @@
         <v>-1.016148834044301</v>
       </c>
       <c r="D89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>-3.502989822778776</v>
@@ -5505,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5519,7 +5513,7 @@
         <v>-1.367241988261846</v>
       </c>
       <c r="D90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>-3.502989822778776</v>
@@ -5555,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5605,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5619,7 +5613,7 @@
         <v>-0.4118803526124637</v>
       </c>
       <c r="D92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>-2.764110737160166</v>
@@ -5655,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5669,7 +5663,7 @@
         <v>-0.7674112190559477</v>
       </c>
       <c r="D93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E93">
         <v>-2.764110737160166</v>
@@ -5705,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5755,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5769,7 +5763,7 @@
         <v>-0.2876287466436551</v>
       </c>
       <c r="D95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E95">
         <v>-2.612180070865378</v>
@@ -5805,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5819,7 +5813,7 @@
         <v>-0.6440721095813977</v>
       </c>
       <c r="D96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E96">
         <v>-2.612180070865378</v>
@@ -5855,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5869,7 +5863,7 @@
         <v>0.05201378340070306</v>
       </c>
       <c r="D97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E97">
         <v>-2.956922689786758</v>
@@ -5905,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5919,7 +5913,7 @@
         <v>-0.3069238943231696</v>
       </c>
       <c r="D98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E98">
         <v>-2.956922689786758</v>
@@ -5955,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5969,7 +5963,7 @@
         <v>0.2922547492769958</v>
       </c>
       <c r="D99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>-2.654783653755068</v>
@@ -6005,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6019,7 +6013,7 @@
         <v>-0.06844724398574797</v>
       </c>
       <c r="D100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E100">
         <v>-2.654783653755068</v>
@@ -6055,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6069,7 +6063,7 @@
         <v>0.6232420313783926</v>
       </c>
       <c r="D101" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E101">
         <v>-2.238517518676506</v>
@@ -6105,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6119,7 +6113,7 @@
         <v>0.2601092869619066</v>
       </c>
       <c r="D102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E102">
         <v>-2.238517518676506</v>
@@ -6155,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6169,7 +6163,7 @@
         <v>4.141754536953039</v>
       </c>
       <c r="D103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E103">
         <v>2.186539518628205</v>
@@ -6205,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6219,7 +6213,7 @@
         <v>7.557003841136609</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>5.174300201916912</v>
@@ -6255,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6269,7 +6263,7 @@
         <v>7.508620354483716</v>
       </c>
       <c r="D105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>5.174300201916912</v>
@@ -6305,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6319,7 +6313,7 @@
         <v>7.536178290808042</v>
       </c>
       <c r="D106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>5.152633472688905</v>
@@ -6355,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6369,7 +6363,7 @@
         <v>7.483206555612748</v>
       </c>
       <c r="D107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E107">
         <v>5.152633472688905</v>
@@ -6405,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6419,7 +6413,7 @@
         <v>7.440504266578895</v>
       </c>
       <c r="D108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>5.053095014188569</v>
@@ -6455,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6469,7 +6463,7 @@
         <v>9.365811399267564</v>
       </c>
       <c r="D109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E109">
         <v>6.757662677409661</v>
@@ -6505,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6519,7 +6513,7 @@
         <v>9.829042892415874</v>
       </c>
       <c r="D110" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E110">
         <v>7.152594241277328</v>
@@ -6555,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6569,7 +6563,7 @@
         <v>9.950215330818077</v>
       </c>
       <c r="D111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E111">
         <v>7.450795763409925</v>
@@ -6605,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6619,7 +6613,7 @@
         <v>9.939801850309847</v>
       </c>
       <c r="D112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E112">
         <v>7.450795763409925</v>
@@ -6655,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6669,7 +6663,7 @@
         <v>10.1788157366114</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>7.450795763409925</v>
@@ -6705,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6719,7 +6713,7 @@
         <v>10.19010941205158</v>
       </c>
       <c r="D114" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>7.658021341711224</v>
@@ -6755,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6769,7 +6763,7 @@
         <v>10.19456741422145</v>
       </c>
       <c r="D115" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E115">
         <v>7.658021341711224</v>
@@ -6805,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6819,7 +6813,7 @@
         <v>10.42187915021893</v>
       </c>
       <c r="D116" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E116">
         <v>7.658021341711224</v>
@@ -6855,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6869,7 +6863,7 @@
         <v>11.00576633616056</v>
       </c>
       <c r="D117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E117">
         <v>8.362603034285035</v>
@@ -6905,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6919,7 +6913,7 @@
         <v>11.06078843626807</v>
       </c>
       <c r="D118" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E118">
         <v>8.362603034285035</v>
@@ -6955,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6969,7 +6963,7 @@
         <v>10.94773862143113</v>
       </c>
       <c r="D119" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>8.362603034285035</v>
@@ -7005,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7019,7 +7013,7 @@
         <v>11.24831202962609</v>
       </c>
       <c r="D120" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E120">
         <v>8.362603034285035</v>
@@ -7055,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7069,7 +7063,7 @@
         <v>11.09208759542391</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>8.437169162713746</v>
@@ -7105,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7119,7 +7113,7 @@
         <v>11.00546199497746</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E122">
         <v>8.437169162713746</v>
@@ -7155,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7169,7 +7163,7 @@
         <v>11.1524609118069</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E123">
         <v>8.437169162713746</v>
@@ -7205,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7219,7 +7213,7 @@
         <v>11.03528802869214</v>
       </c>
       <c r="D124" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E124">
         <v>8.437169162713746</v>
@@ -7255,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7269,7 +7263,7 @@
         <v>11.33577371203012</v>
       </c>
       <c r="D125" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E125">
         <v>8.437169162713746</v>
@@ -7305,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7319,7 +7313,7 @@
         <v>11.13516606080816</v>
       </c>
       <c r="D126" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E126">
         <v>8.474381251714366</v>
@@ -7355,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7369,7 +7363,7 @@
         <v>11.05274323747237</v>
       </c>
       <c r="D127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>8.474381251714366</v>
@@ -7405,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7419,7 +7413,7 @@
         <v>11.19820989181354</v>
       </c>
       <c r="D128" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>8.474381251714366</v>
@@ -7455,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7469,7 +7463,7 @@
         <v>11.07897939907169</v>
       </c>
       <c r="D129" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E129">
         <v>8.474381251714366</v>
@@ -7505,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7519,7 +7513,7 @@
         <v>11.37942130348144</v>
       </c>
       <c r="D130" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E130">
         <v>8.474381251714366</v>
@@ -7555,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7569,7 +7563,7 @@
         <v>11.21514005893636</v>
       </c>
       <c r="D131" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>8.543464481804783</v>
@@ -7605,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7619,7 +7613,7 @@
         <v>11.14051957688137</v>
       </c>
       <c r="D132" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E132">
         <v>8.543464481804783</v>
@@ -7655,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7669,7 +7663,7 @@
         <v>11.28314162763058</v>
       </c>
       <c r="D133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E133">
         <v>8.543464481804783</v>
@@ -7705,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7719,7 +7713,7 @@
         <v>11.16009123863667</v>
       </c>
       <c r="D134" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>8.543464481804783</v>
@@ -7755,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7769,7 +7763,7 @@
         <v>11.46045186865808</v>
       </c>
       <c r="D135" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>8.543464481804783</v>
@@ -7805,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7819,7 +7813,7 @@
         <v>11.36455331954346</v>
       </c>
       <c r="D136" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>8.672530814646279</v>
@@ -7855,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7869,7 +7863,7 @@
         <v>11.30450974096233</v>
       </c>
       <c r="D137" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E137">
         <v>8.672530814646279</v>
@@ -7905,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7919,7 +7913,7 @@
         <v>11.44181729565337</v>
       </c>
       <c r="D138" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E138">
         <v>8.672530814646279</v>
@@ -7955,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7969,7 +7963,7 @@
         <v>11.31163029766704</v>
       </c>
       <c r="D139" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>8.672530814646279</v>
@@ -8005,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8019,7 +8013,7 @@
         <v>11.61183908494393</v>
       </c>
       <c r="D140" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E140">
         <v>8.672530814646279</v>
@@ -8055,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8069,7 +8063,7 @@
         <v>0.8480932702092439</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E141">
         <v>3.305848053378067</v>
@@ -8105,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8119,7 +8113,7 @@
         <v>0.3713990780811081</v>
       </c>
       <c r="D142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E142">
         <v>2.93519301420058</v>
@@ -8155,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8169,7 +8163,7 @@
         <v>0.09370238403359465</v>
       </c>
       <c r="D143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E143">
         <v>2.719269093348668</v>
@@ -8205,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8219,7 +8213,7 @@
         <v>-0.3002649679542344</v>
       </c>
       <c r="D144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E144">
         <v>2.412938563845493</v>
@@ -8255,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8269,7 +8263,7 @@
         <v>-0.7441268264907208</v>
       </c>
       <c r="D145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E145">
         <v>2.067812406904586</v>
@@ -8305,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8319,7 +8313,7 @@
         <v>-0.9366600356356365</v>
       </c>
       <c r="D146" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E146">
         <v>1.697880329395359</v>
@@ -8355,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8369,7 +8363,7 @@
         <v>-1.045770570759764</v>
       </c>
       <c r="D147" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E147">
         <v>1.609465153936503</v>
@@ -8405,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8419,7 +8413,7 @@
         <v>-1.197366407452137</v>
       </c>
       <c r="D148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E148">
         <v>1.48662300597398</v>
@@ -8455,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8469,7 +8463,7 @@
         <v>-1.433328196163565</v>
       </c>
       <c r="D149" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>1.29541687792436</v>
@@ -8505,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8519,7 +8513,7 @@
         <v>-1.733732538243757</v>
       </c>
       <c r="D150" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E150">
         <v>1.051991230864648</v>
@@ -8555,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8569,7 +8563,7 @@
         <v>-2.287391621311837</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E151">
         <v>0.6033465155017872</v>
@@ -8605,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8619,7 +8613,7 @@
         <v>-2.526607700588286</v>
       </c>
       <c r="D152" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E152">
         <v>0.4095033490491105</v>
@@ -8655,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8669,7 +8663,7 @@
         <v>-2.302950288058071</v>
       </c>
       <c r="D153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E153">
         <v>0.4095033490491105</v>
@@ -8705,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8719,7 +8713,7 @@
         <v>-2.305521784381465</v>
       </c>
       <c r="D154" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E154">
         <v>0.7176635024188069</v>
@@ -8755,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8769,7 +8763,7 @@
         <v>-2.078369863165154</v>
       </c>
       <c r="D155" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>0.7176635024188069</v>
@@ -8805,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8819,7 +8813,7 @@
         <v>14.54454576797096</v>
       </c>
       <c r="D156" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E156">
         <v>12.97537728339032</v>
@@ -8855,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8869,7 +8863,7 @@
         <v>16.89725645616409</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E157">
         <v>12.09038257047715</v>
@@ -8905,7 +8899,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8919,7 +8913,7 @@
         <v>1.844161097357947</v>
       </c>
       <c r="D158" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>4.438276215616288</v>
@@ -8969,7 +8963,7 @@
         <v>9.319411866804192</v>
       </c>
       <c r="D159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>8.178274452147054</v>
@@ -9005,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9019,7 +9013,7 @@
         <v>9.335040373209631</v>
       </c>
       <c r="D160" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E160">
         <v>8.178274452147054</v>
@@ -9055,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9069,7 +9063,7 @@
         <v>7.119114103616456</v>
       </c>
       <c r="D161" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>8.411091169742999</v>
@@ -9105,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9119,7 +9113,7 @@
         <v>9.180210440362462</v>
       </c>
       <c r="D162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E162">
         <v>8.035029830746435</v>
@@ -9155,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9169,7 +9163,7 @@
         <v>9.198919476260389</v>
       </c>
       <c r="D163" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>8.035029830746435</v>
@@ -9205,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9219,7 +9213,7 @@
         <v>6.958541503820602</v>
       </c>
       <c r="D164" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>8.237233786510796</v>
@@ -9255,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9269,7 +9263,7 @@
         <v>9.138411223866905</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>7.992016529124452</v>
@@ -9305,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9319,7 +9313,7 @@
         <v>9.158045277004016</v>
       </c>
       <c r="D166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E166">
         <v>7.992016529124452</v>
@@ -9355,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9369,7 +9363,7 @@
         <v>6.910324980228218</v>
       </c>
       <c r="D167" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E167">
         <v>8.185028126074439</v>
@@ -9405,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9419,7 +9413,7 @@
         <v>8.974671573452897</v>
       </c>
       <c r="D168" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E168">
         <v>7.823520955254436</v>
@@ -9455,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9469,7 +9463,7 @@
         <v>8.997929187318395</v>
       </c>
       <c r="D169" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E169">
         <v>7.823520955254436</v>
@@ -9505,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9519,7 +9513,7 @@
         <v>6.72144687726102</v>
       </c>
       <c r="D170" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E170">
         <v>7.98052341746607</v>
@@ -9555,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9569,7 +9563,7 @@
         <v>8.842656913370059</v>
       </c>
       <c r="D171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E171">
         <v>7.687671844463797</v>
@@ -9605,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9619,7 +9613,7 @@
         <v>8.868836013489117</v>
       </c>
       <c r="D172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E172">
         <v>7.687671844463797</v>
@@ -9655,7 +9649,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9669,7 +9663,7 @@
         <v>6.569164406294096</v>
       </c>
       <c r="D173" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E173">
         <v>7.815642037030656</v>
@@ -9705,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9719,7 +9713,7 @@
         <v>9.455479871941058</v>
       </c>
       <c r="D174" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E174">
         <v>9.077830145711916</v>
@@ -9755,7 +9749,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9769,7 +9763,7 @@
         <v>9.446349888131271</v>
       </c>
       <c r="D175" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E175">
         <v>9.077830145711916</v>
@@ -9805,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9819,7 +9813,7 @@
         <v>9.483265153807022</v>
       </c>
       <c r="D176" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E176">
         <v>9.077830145711916</v>
@@ -9855,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9869,7 +9863,7 @@
         <v>13.4619601181134</v>
       </c>
       <c r="D177" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E177">
         <v>12.34452367191913</v>
@@ -9905,7 +9899,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9919,7 +9913,7 @@
         <v>12.92939656430767</v>
       </c>
       <c r="D178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E178">
         <v>12.34452367191913</v>
@@ -9955,7 +9949,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9969,7 +9963,7 @@
         <v>13.32068800981388</v>
       </c>
       <c r="D179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E179">
         <v>12.26278179180369</v>
@@ -10005,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10019,7 +10013,7 @@
         <v>12.78603153588519</v>
       </c>
       <c r="D180" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E180">
         <v>12.26278179180369</v>
@@ -10055,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10069,7 +10063,7 @@
         <v>13.1054754777184</v>
       </c>
       <c r="D181" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E181">
         <v>12.0720456563318</v>
@@ -10105,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10119,7 +10113,7 @@
         <v>12.86527844472554</v>
       </c>
       <c r="D182" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E182">
         <v>12.0720456563318</v>
@@ -10155,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10169,7 +10163,7 @@
         <v>12.78397754178392</v>
       </c>
       <c r="D183" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E183">
         <v>11.04627431338637</v>
@@ -10205,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10219,7 +10213,7 @@
         <v>12.54105883314293</v>
       </c>
       <c r="D184" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E184">
         <v>11.04627431338637</v>
@@ -10255,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10269,7 +10263,7 @@
         <v>12.65691764634175</v>
       </c>
       <c r="D185" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E185">
         <v>10.59662737561003</v>
@@ -10305,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10319,7 +10313,7 @@
         <v>12.41292329837428</v>
       </c>
       <c r="D186" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E186">
         <v>10.59662737561003</v>
@@ -10355,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10369,7 +10363,7 @@
         <v>12.50588234232934</v>
       </c>
       <c r="D187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E187">
         <v>11.08515654148158</v>
@@ -10405,7 +10399,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10419,7 +10413,7 @@
         <v>12.26060938861361</v>
       </c>
       <c r="D188" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E188">
         <v>11.08515654148158</v>
@@ -10455,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10469,7 +10463,7 @@
         <v>12.49472126196415</v>
       </c>
       <c r="D189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E189">
         <v>11.21992123177482</v>
@@ -10505,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10519,7 +10513,7 @@
         <v>12.24935382291199</v>
       </c>
       <c r="D190" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E190">
         <v>11.21992123177482</v>
@@ -10555,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10569,7 +10563,7 @@
         <v>11.81218185501084</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>9.535970599248831</v>
@@ -10605,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10619,7 +10613,7 @@
         <v>11.56103630457707</v>
       </c>
       <c r="D192" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>9.535970599248831</v>
@@ -10655,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10669,7 +10663,7 @@
         <v>11.56465149912584</v>
       </c>
       <c r="D193" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>9.675839188592356</v>
@@ -10705,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10719,7 +10713,7 @@
         <v>7.636982242247004</v>
       </c>
       <c r="D194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>8.781566940761209</v>
@@ -10755,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10769,7 +10763,7 @@
         <v>7.500597222451283</v>
       </c>
       <c r="D195" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>5.221675206137377</v>
@@ -10805,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10855,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10905,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10919,7 +10913,7 @@
         <v>6.038896587632429</v>
       </c>
       <c r="D198" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E198">
         <v>3.619665518887551</v>
@@ -10955,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11005,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11055,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11069,7 +11063,7 @@
         <v>5.113180307292243</v>
       </c>
       <c r="D201" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>2.605089474091869</v>
@@ -11105,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11155,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11205,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11219,7 +11213,7 @@
         <v>4.469818487753336</v>
       </c>
       <c r="D204" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.899971173698074</v>
@@ -11255,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11305,7 +11299,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11319,7 +11313,7 @@
         <v>-0.07832045460795456</v>
       </c>
       <c r="D206" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>-0.004639904864621514</v>
@@ -11355,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11369,7 +11363,7 @@
         <v>3.78645081212834</v>
       </c>
       <c r="D207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E207">
         <v>1.151006843912235</v>
@@ -11405,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11455,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11469,7 +11463,7 @@
         <v>-0.7998836503772395</v>
       </c>
       <c r="D209" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>-0.2850143797265261</v>
@@ -11505,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11519,7 +11513,7 @@
         <v>3.212377199546523</v>
       </c>
       <c r="D210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>0.5218277448249928</v>
@@ -11555,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11605,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11619,7 +11613,7 @@
         <v>-1.406044001936898</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E212">
         <v>-0.9867534196829375</v>
@@ -11655,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11669,7 +11663,7 @@
         <v>3.016902946366145</v>
       </c>
       <c r="D213" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E213">
         <v>0.3075898634535434</v>
@@ -11705,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11755,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11769,7 +11763,7 @@
         <v>-1.715473191569199</v>
       </c>
       <c r="D215" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E215">
         <v>-1.588175900302144</v>
@@ -11805,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11819,7 +11813,7 @@
         <v>2.926828084162654</v>
       </c>
       <c r="D216" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>0.2088686900543344</v>
@@ -11855,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -11905,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11919,7 +11913,7 @@
         <v>-1.810692061699257</v>
       </c>
       <c r="D218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>-1.171715130422566</v>
@@ -11955,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11969,7 +11963,7 @@
         <v>2.807702230613152</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>0.07830791253106639</v>
@@ -12005,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12055,7 +12049,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12069,7 +12063,7 @@
         <v>-1.936620971283784</v>
       </c>
       <c r="D221" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E221">
         <v>-1.353038333187715</v>
@@ -12105,7 +12099,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12119,7 +12113,7 @@
         <v>2.904864220142379</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.1847965085886152</v>
@@ -12155,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12205,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12219,7 +12213,7 @@
         <v>-1.833910241161757</v>
       </c>
       <c r="D224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>-1.452902725583563</v>
@@ -12255,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12269,7 +12263,7 @@
         <v>2.747341418541836</v>
       </c>
       <c r="D225" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.01215304924026483</v>
@@ -12305,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12355,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12369,7 +12363,7 @@
         <v>2.525808061495567</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E227">
         <v>-0.230645356659771</v>
@@ -12405,7 +12399,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12455,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12469,7 +12463,7 @@
         <v>2.510259318857806</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E229">
         <v>-0.2476866274486689</v>
@@ -12505,7 +12499,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12555,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12569,7 +12563,7 @@
         <v>2.386297626557326</v>
       </c>
       <c r="D231" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E231">
         <v>-0.383547437236075</v>
@@ -12605,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12655,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12669,7 +12663,7 @@
         <v>2.385442882237758</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E233">
         <v>-0.3844842287017478</v>
@@ -12705,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12755,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12769,7 +12763,7 @@
         <v>2.40148945952356</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E235">
         <v>-0.3668973359778178</v>
@@ -12805,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12855,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12905,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12919,7 +12913,7 @@
         <v>2.400509689252775</v>
       </c>
       <c r="D238" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E238">
         <v>-0.3679711546707054</v>
@@ -12955,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -12969,7 +12963,7 @@
         <v>-3.581575319657137</v>
       </c>
       <c r="D239" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>-2.92193383368587</v>
@@ -13005,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13019,7 +13013,7 @@
         <v>-3.172611558422112</v>
       </c>
       <c r="D240" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E240">
         <v>-2.92193383368587</v>
@@ -13055,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13069,7 +13063,7 @@
         <v>2.308805102477052</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>-0.4684784903592885</v>
@@ -13105,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13119,7 +13113,7 @@
         <v>-3.693838225096432</v>
       </c>
       <c r="D242" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E242">
         <v>-2.705636234594518</v>
@@ -13155,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13169,7 +13163,7 @@
         <v>-3.266767543629264</v>
       </c>
       <c r="D243" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E243">
         <v>-2.705636234594518</v>
@@ -13205,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13219,7 +13213,7 @@
         <v>2.199196971453233</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E244">
         <v>-0.5886079365117602</v>
@@ -13255,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13269,7 +13263,7 @@
         <v>-3.828018288287804</v>
       </c>
       <c r="D245" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E245">
         <v>-2.440117620458789</v>
@@ -13305,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13319,7 +13313,7 @@
         <v>-3.37930566114461</v>
       </c>
       <c r="D246" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E246">
         <v>-2.440117620458789</v>
@@ -13355,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13369,7 +13363,7 @@
         <v>2.194413896805312</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>-0.5938501398318401</v>
@@ -13405,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13419,7 +13413,7 @@
         <v>-3.833873631796653</v>
       </c>
       <c r="D248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E248">
         <v>-2.690267803380642</v>
@@ -13455,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13469,7 +13463,7 @@
         <v>-3.384216594410091</v>
       </c>
       <c r="D249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E249">
         <v>-2.690267803380642</v>
@@ -13505,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13519,7 +13513,7 @@
         <v>2.175984487542404</v>
       </c>
       <c r="D250" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E250">
         <v>-0.6140485932402768</v>
@@ -13555,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13569,7 +13563,7 @@
         <v>-3.856434542893108</v>
       </c>
       <c r="D251" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E251">
         <v>-2.563360826372787</v>
@@ -13605,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13619,7 +13613,7 @@
         <v>-3.403138648878087</v>
       </c>
       <c r="D252" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E252">
         <v>-2.563360826372787</v>
@@ -13655,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13669,7 +13663,7 @@
         <v>2.082257842825086</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E253">
         <v>-0.7167720847773573</v>
@@ -13705,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13719,7 +13713,7 @@
         <v>-3.97117281087937</v>
       </c>
       <c r="D254" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E254">
         <v>-2.755309661269902</v>
@@ -13755,7 +13749,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13769,7 +13763,7 @@
         <v>-3.499370744608502</v>
       </c>
       <c r="D255" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E255">
         <v>-2.755309661269902</v>
@@ -13805,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13819,7 +13813,7 @@
         <v>1.887361513324546</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E256">
         <v>-0.9303765674134326</v>
@@ -13869,7 +13863,7 @@
         <v>-4.209760966373654</v>
       </c>
       <c r="D257" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E257">
         <v>-3.053363328805407</v>
@@ -13919,7 +13913,7 @@
         <v>-3.699476939539188</v>
       </c>
       <c r="D258" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E258">
         <v>-3.053363328805407</v>
@@ -13969,7 +13963,7 @@
         <v>1.583234529354392</v>
       </c>
       <c r="D259" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>-1.263696785567841</v>
@@ -14005,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14019,7 +14013,7 @@
         <v>-4.582067085875391</v>
       </c>
       <c r="D260" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E260">
         <v>-3.68774391221184</v>
@@ -14055,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14069,7 +14063,7 @@
         <v>-4.011733684927744</v>
       </c>
       <c r="D261" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E261">
         <v>-3.68774391221184</v>
@@ -14105,7 +14099,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14119,7 +14113,7 @@
         <v>1.492437753485213</v>
       </c>
       <c r="D262" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E262">
         <v>-1.363209169327256</v>
@@ -14155,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14169,7 +14163,7 @@
         <v>-4.693218667513538</v>
       </c>
       <c r="D263" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E263">
         <v>-3.703008342092328</v>
@@ -14205,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14219,7 +14213,7 @@
         <v>-4.104957592108128</v>
       </c>
       <c r="D264" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E264">
         <v>-3.703008342092328</v>
@@ -14255,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14269,7 +14263,7 @@
         <v>1.38713246822714</v>
       </c>
       <c r="D265" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>-1.478622738346431</v>
@@ -14305,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14319,7 +14313,7 @@
         <v>-4.822131273707353</v>
       </c>
       <c r="D266" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E266">
         <v>-3.632446910390104</v>
@@ -14355,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14369,7 +14363,7 @@
         <v>-4.21307784246423</v>
       </c>
       <c r="D267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E267">
         <v>-3.632446910390104</v>
@@ -14405,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14419,7 +14413,7 @@
         <v>1.322229117025856</v>
       </c>
       <c r="D268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E268">
         <v>-1.62537513076974</v>
@@ -14455,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14469,7 +14463,7 @@
         <v>-4.901584647140279</v>
       </c>
       <c r="D269" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E269">
         <v>-3.924234023534328</v>
@@ -14505,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14519,7 +14513,7 @@
         <v>-4.279716155666037</v>
       </c>
       <c r="D270" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E270">
         <v>-3.924234023534328</v>
@@ -14555,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14605,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14655,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -14705,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -14755,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -14805,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -14819,7 +14813,7 @@
         <v>-8.738325618777875</v>
       </c>
       <c r="D276" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E276">
         <v>-10.96911537303974</v>
@@ -14855,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -14869,7 +14863,7 @@
         <v>-9.552131432870056</v>
       </c>
       <c r="D277" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E277">
         <v>-11.9919655017791</v>
@@ -14905,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -14919,7 +14913,7 @@
         <v>-9.766561937606845</v>
       </c>
       <c r="D278" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E278">
         <v>-12.22005247441533</v>
@@ -14955,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -14969,7 +14963,7 @@
         <v>-10.00240391200717</v>
       </c>
       <c r="D279" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E279">
         <v>-12.47091455221322</v>
@@ -15005,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15019,7 +15013,7 @@
         <v>-11.49656577386733</v>
       </c>
       <c r="D280" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E280">
         <v>-13.09249134332418</v>
@@ -15055,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15069,7 +15063,7 @@
         <v>-11.61661597808293</v>
       </c>
       <c r="D281" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E281">
         <v>-13.21626502980956</v>
@@ -15105,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15119,7 +15113,7 @@
         <v>-11.80793914135153</v>
       </c>
       <c r="D282" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E282">
         <v>-11.83703984329198</v>
@@ -15155,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15169,7 +15163,7 @@
         <v>-12.17975455415064</v>
       </c>
       <c r="D283" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E283">
         <v>-12.70676383937817</v>
@@ -15205,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15219,10 +15213,10 @@
         <v>22.06523254534987</v>
       </c>
       <c r="D284" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E284">
-        <v>20.29931077014897</v>
+        <v>20.17523557425732</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15231,10 +15225,10 @@
         <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.02980068922985103</v>
+        <v>0.02982476442574268</v>
       </c>
       <c r="I284">
-        <v>1.765921775200901</v>
+        <v>1.88999697109255</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15246,16 +15240,16 @@
         <v>27.09</v>
       </c>
       <c r="M284">
-        <v>19.24</v>
+        <v>19.54</v>
       </c>
       <c r="N284">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="O284">
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15269,10 +15263,10 @@
         <v>11.29004782022705</v>
       </c>
       <c r="D285" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E285">
-        <v>13.45223237636709</v>
+        <v>12.44379889072158</v>
       </c>
       <c r="F285">
         <v>1</v>
@@ -15281,10 +15275,10 @@
         <v>0.03786995217977295</v>
       </c>
       <c r="H285">
-        <v>0.04032776762363291</v>
+        <v>0.03891620110927842</v>
       </c>
       <c r="I285">
-        <v>2.162184556140042</v>
+        <v>1.153751070494534</v>
       </c>
       <c r="J285">
         <v>0.6718883811816456</v>
@@ -15296,16 +15290,16 @@
         <v>24.58</v>
       </c>
       <c r="M285">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N285">
-        <v>26.89</v>
+        <v>25.68</v>
       </c>
       <c r="O285">
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15319,10 +15313,10 @@
         <v>11.22473879933428</v>
       </c>
       <c r="D286" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E286">
-        <v>13.45223237636709</v>
+        <v>12.44379889072158</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -15331,10 +15325,10 @@
         <v>0.03745526120066572</v>
       </c>
       <c r="H286">
-        <v>0.04032776762363291</v>
+        <v>0.03891620110927842</v>
       </c>
       <c r="I286">
-        <v>2.227493577032812</v>
+        <v>1.219060091387304</v>
       </c>
       <c r="J286">
         <v>0.6718883811816456</v>
@@ -15346,16 +15340,16 @@
         <v>24.34</v>
       </c>
       <c r="M286">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N286">
-        <v>26.89</v>
+        <v>25.68</v>
       </c>
       <c r="O286">
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15405,7 +15399,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15455,7 +15449,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15555,57 +15549,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16">
-      <c r="A291" s="1">
-        <v>0</v>
-      </c>
-      <c r="B291" t="s">
-        <v>57</v>
-      </c>
-      <c r="C291">
-        <v>10.9244311529636</v>
-      </c>
-      <c r="D291" t="s">
-        <v>110</v>
-      </c>
-      <c r="E291">
-        <v>11.50295358284819</v>
-      </c>
-      <c r="F291">
-        <v>1</v>
-      </c>
-      <c r="G291">
-        <v>0.0396355688470364</v>
-      </c>
-      <c r="H291">
-        <v>0.03821704641715182</v>
-      </c>
-      <c r="I291">
-        <v>0.5785224298845861</v>
-      </c>
-      <c r="J291">
-        <v>0.723566978177238</v>
-      </c>
-      <c r="K291">
-        <v>19.84</v>
-      </c>
-      <c r="L291">
-        <v>25.28</v>
-      </c>
-      <c r="M291">
-        <v>18.46</v>
-      </c>
-      <c r="N291">
-        <v>24.86</v>
-      </c>
-      <c r="O291">
-        <v>1</v>
-      </c>
-      <c r="P291" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -337,7 +337,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2021-08-31</t>
@@ -15216,7 +15216,7 @@
         <v>107</v>
       </c>
       <c r="E284">
-        <v>20.17523557425732</v>
+        <v>20.275975417544</v>
       </c>
       <c r="F284">
         <v>-1</v>
@@ -15225,10 +15225,10 @@
         <v>0.03211476745465013</v>
       </c>
       <c r="H284">
-        <v>0.02982476442574268</v>
+        <v>0.030044024582456</v>
       </c>
       <c r="I284">
-        <v>1.88999697109255</v>
+        <v>1.789257127805868</v>
       </c>
       <c r="J284">
         <v>0.246917319638827</v>
@@ -15240,10 +15240,10 @@
         <v>27.09</v>
       </c>
       <c r="M284">
-        <v>19.54</v>
+        <v>19.78</v>
       </c>
       <c r="N284">
-        <v>25</v>
+        <v>25.16</v>
       </c>
       <c r="O284">
         <v>1</v>
@@ -15363,10 +15363,10 @@
         <v>11.33579779994147</v>
       </c>
       <c r="D287" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E287">
-        <v>13.49849120317641</v>
+        <v>12.48936383512877</v>
       </c>
       <c r="F287">
         <v>1</v>
@@ -15375,10 +15375,10 @@
         <v>0.03782420220005853</v>
       </c>
       <c r="H287">
-        <v>0.04028150879682359</v>
+        <v>0.03887063616487123</v>
       </c>
       <c r="I287">
-        <v>2.162693403234943</v>
+        <v>1.153566035187298</v>
       </c>
       <c r="J287">
         <v>0.6695754398411793</v>
@@ -15390,10 +15390,10 @@
         <v>24.58</v>
       </c>
       <c r="M287">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N287">
-        <v>26.89</v>
+        <v>25.68</v>
       </c>
       <c r="O287">
         <v>1</v>
@@ -15413,10 +15413,10 @@
         <v>11.26988741430018</v>
       </c>
       <c r="D288" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E288">
-        <v>13.49849120317641</v>
+        <v>12.48936383512877</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -15425,10 +15425,10 @@
         <v>0.03741011258569982</v>
       </c>
       <c r="H288">
-        <v>0.04028150879682359</v>
+        <v>0.03887063616487123</v>
       </c>
       <c r="I288">
-        <v>2.228603788876233</v>
+        <v>1.219476420828588</v>
       </c>
       <c r="J288">
         <v>0.6695754398411793</v>
@@ -15440,10 +15440,10 @@
         <v>24.34</v>
       </c>
       <c r="M288">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N288">
-        <v>26.89</v>
+        <v>25.68</v>
       </c>
       <c r="O288">
         <v>1</v>

--- a/s60_signal/position-06030-600030.xlsx
+++ b/s60_signal/position-06030-600030.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="231">
   <si>
     <t>trade_time</t>
   </si>
@@ -181,6 +181,9 @@
     <t>2021-09-02</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-08-26</t>
   </si>
   <si>
@@ -337,15 +340,18 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-10-25</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>2017-06-07</t>
   </si>
   <si>
@@ -686,6 +692,12 @@
   </si>
   <si>
     <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-08-13</t>
   </si>
   <si>
     <t>2021-08-24</t>
@@ -1052,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P290"/>
+  <dimension ref="A1:P292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1113,7 +1125,7 @@
         <v>10.08483438961823</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>9.410445525878979</v>
@@ -1149,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1163,7 +1175,7 @@
         <v>9.995296702882149</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>9.410445525878979</v>
@@ -1199,7 +1211,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1213,7 +1225,7 @@
         <v>10.203107552437</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>9.410445525878979</v>
@@ -1249,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1263,7 +1275,7 @@
         <v>10.01654010110155</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>9.410445525878979</v>
@@ -1299,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1313,7 +1325,7 @@
         <v>9.537355512755463</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>8.86716700080291</v>
@@ -1349,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1363,7 +1375,7 @@
         <v>9.471808473432473</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7">
         <v>8.86716700080291</v>
@@ -1399,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1413,7 +1425,7 @@
         <v>9.685770771041961</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>8.86716700080291</v>
@@ -1449,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1463,7 +1475,7 @@
         <v>9.51765766387043</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>8.86716700080291</v>
@@ -1499,7 +1511,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1513,7 +1525,7 @@
         <v>9.189630487116727</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>8.732550953037995</v>
@@ -1549,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </r